--- a/Financial Analysis/LMT.xlsx
+++ b/Financial Analysis/LMT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A460589F-6CBB-4C40-BD69-90A5D0E2F402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC494DBA-103B-4273-A2FA-4B446C6E796A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4D34CE10-A2B1-43BA-A8EF-FB8FB8D75171}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="69">
   <si>
     <t>LMT</t>
   </si>
@@ -203,6 +203,36 @@
   </si>
   <si>
     <t>F-35 Lightning II – international multi-role, multi-variant, fifth generation stealth fighter.</t>
+  </si>
+  <si>
+    <t>Maturity</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Net cash</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Per share</t>
+  </si>
+  <si>
+    <t>Current price</t>
+  </si>
+  <si>
+    <t>Variance</t>
+  </si>
+  <si>
+    <t>Consensus</t>
+  </si>
+  <si>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -720,7 +750,7 @@
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45770</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="5">
         <v>45769</v>
@@ -799,12 +829,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A3F992-CF1A-49DF-A7A3-B2026107AC3A}">
-  <dimension ref="B2:AN33"/>
+  <dimension ref="B2:EH34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="41" width="8.88671875" style="1"/>
+    <col min="42" max="42" width="14.109375" style="1" customWidth="1"/>
+    <col min="43" max="43" width="17.109375" style="1" customWidth="1"/>
+    <col min="44" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:40" x14ac:dyDescent="0.3">
@@ -942,6 +975,50 @@
       <c r="AC3" s="6">
         <v>59277</v>
       </c>
+      <c r="AD3" s="6">
+        <f>AC3*1.02</f>
+        <v>60462.54</v>
+      </c>
+      <c r="AE3" s="6">
+        <f>AD3*1.01</f>
+        <v>61067.165399999998</v>
+      </c>
+      <c r="AF3" s="6">
+        <f t="shared" ref="AF3:AN3" si="0">AE3*1.01</f>
+        <v>61677.837053999996</v>
+      </c>
+      <c r="AG3" s="6">
+        <f t="shared" si="0"/>
+        <v>62294.615424539996</v>
+      </c>
+      <c r="AH3" s="6">
+        <f t="shared" si="0"/>
+        <v>62917.561578785397</v>
+      </c>
+      <c r="AI3" s="6">
+        <f t="shared" si="0"/>
+        <v>63546.737194573252</v>
+      </c>
+      <c r="AJ3" s="6">
+        <f t="shared" si="0"/>
+        <v>64182.204566518987</v>
+      </c>
+      <c r="AK3" s="6">
+        <f t="shared" si="0"/>
+        <v>64824.026612184178</v>
+      </c>
+      <c r="AL3" s="6">
+        <f t="shared" si="0"/>
+        <v>65472.266878306022</v>
+      </c>
+      <c r="AM3" s="6">
+        <f t="shared" si="0"/>
+        <v>66126.989547089077</v>
+      </c>
+      <c r="AN3" s="6">
+        <f t="shared" si="0"/>
+        <v>66788.259442559967</v>
+      </c>
     </row>
     <row r="4" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -965,34 +1042,122 @@
       <c r="AC4" s="6">
         <v>11766</v>
       </c>
+      <c r="AD4" s="6">
+        <f>AC4*1.03</f>
+        <v>12118.98</v>
+      </c>
+      <c r="AE4" s="6">
+        <f>AD4*1.03</f>
+        <v>12482.5494</v>
+      </c>
+      <c r="AF4" s="6">
+        <f t="shared" ref="AF4:AN4" si="1">AE4*1.03</f>
+        <v>12857.025882</v>
+      </c>
+      <c r="AG4" s="6">
+        <f t="shared" si="1"/>
+        <v>13242.73665846</v>
+      </c>
+      <c r="AH4" s="6">
+        <f t="shared" si="1"/>
+        <v>13640.018758213801</v>
+      </c>
+      <c r="AI4" s="6">
+        <f t="shared" si="1"/>
+        <v>14049.219320960216</v>
+      </c>
+      <c r="AJ4" s="6">
+        <f t="shared" si="1"/>
+        <v>14470.695900589022</v>
+      </c>
+      <c r="AK4" s="6">
+        <f t="shared" si="1"/>
+        <v>14904.816777606693</v>
+      </c>
+      <c r="AL4" s="6">
+        <f t="shared" si="1"/>
+        <v>15351.961280934895</v>
+      </c>
+      <c r="AM4" s="6">
+        <f t="shared" si="1"/>
+        <v>15812.520119362942</v>
+      </c>
+      <c r="AN4" s="6">
+        <f t="shared" si="1"/>
+        <v>16286.895722943831</v>
+      </c>
     </row>
     <row r="5" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X5" s="9">
-        <f t="shared" ref="X5:AC5" si="0">X3+X4</f>
+        <f t="shared" ref="X5:AN5" si="2">X3+X4</f>
         <v>59812</v>
       </c>
       <c r="Y5" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>65398</v>
       </c>
       <c r="Z5" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>67044</v>
       </c>
       <c r="AA5" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>65984</v>
       </c>
       <c r="AB5" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>67571</v>
       </c>
       <c r="AC5" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>71043</v>
+      </c>
+      <c r="AD5" s="9">
+        <f t="shared" si="2"/>
+        <v>72581.52</v>
+      </c>
+      <c r="AE5" s="9">
+        <f t="shared" si="2"/>
+        <v>73549.714800000002</v>
+      </c>
+      <c r="AF5" s="9">
+        <f t="shared" si="2"/>
+        <v>74534.86293599999</v>
+      </c>
+      <c r="AG5" s="9">
+        <f t="shared" si="2"/>
+        <v>75537.352082999991</v>
+      </c>
+      <c r="AH5" s="9">
+        <f t="shared" si="2"/>
+        <v>76557.580336999192</v>
+      </c>
+      <c r="AI5" s="9">
+        <f t="shared" si="2"/>
+        <v>77595.956515533471</v>
+      </c>
+      <c r="AJ5" s="9">
+        <f t="shared" si="2"/>
+        <v>78652.900467108004</v>
+      </c>
+      <c r="AK5" s="9">
+        <f t="shared" si="2"/>
+        <v>79728.843389790869</v>
+      </c>
+      <c r="AL5" s="9">
+        <f t="shared" si="2"/>
+        <v>80824.228159240913</v>
+      </c>
+      <c r="AM5" s="9">
+        <f t="shared" si="2"/>
+        <v>81939.509666452024</v>
+      </c>
+      <c r="AN5" s="9">
+        <f t="shared" si="2"/>
+        <v>83075.155165503791</v>
       </c>
     </row>
     <row r="6" spans="2:40" x14ac:dyDescent="0.3">
@@ -1017,6 +1182,50 @@
       <c r="AC6" s="6">
         <v>54852</v>
       </c>
+      <c r="AD6" s="6">
+        <f>AD3*0.89</f>
+        <v>53811.660600000003</v>
+      </c>
+      <c r="AE6" s="6">
+        <f t="shared" ref="AE6:AN6" si="3">AE3*0.89</f>
+        <v>54349.777205999999</v>
+      </c>
+      <c r="AF6" s="6">
+        <f t="shared" si="3"/>
+        <v>54893.274978059999</v>
+      </c>
+      <c r="AG6" s="6">
+        <f t="shared" si="3"/>
+        <v>55442.2077278406</v>
+      </c>
+      <c r="AH6" s="6">
+        <f t="shared" si="3"/>
+        <v>55996.629805119002</v>
+      </c>
+      <c r="AI6" s="6">
+        <f t="shared" si="3"/>
+        <v>56556.596103170195</v>
+      </c>
+      <c r="AJ6" s="6">
+        <f t="shared" si="3"/>
+        <v>57122.162064201897</v>
+      </c>
+      <c r="AK6" s="6">
+        <f t="shared" si="3"/>
+        <v>57693.383684843917</v>
+      </c>
+      <c r="AL6" s="6">
+        <f t="shared" si="3"/>
+        <v>58270.317521692363</v>
+      </c>
+      <c r="AM6" s="6">
+        <f t="shared" si="3"/>
+        <v>58853.020696909276</v>
+      </c>
+      <c r="AN6" s="6">
+        <f t="shared" si="3"/>
+        <v>59441.550903878371</v>
+      </c>
     </row>
     <row r="7" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -1040,34 +1249,122 @@
       <c r="AC7" s="6">
         <v>10217</v>
       </c>
+      <c r="AD7" s="6">
+        <f>AD4*0.88</f>
+        <v>10664.7024</v>
+      </c>
+      <c r="AE7" s="6">
+        <f t="shared" ref="AE7:AN7" si="4">AE4*0.88</f>
+        <v>10984.643472</v>
+      </c>
+      <c r="AF7" s="6">
+        <f t="shared" si="4"/>
+        <v>11314.18277616</v>
+      </c>
+      <c r="AG7" s="6">
+        <f t="shared" si="4"/>
+        <v>11653.6082594448</v>
+      </c>
+      <c r="AH7" s="6">
+        <f t="shared" si="4"/>
+        <v>12003.216507228144</v>
+      </c>
+      <c r="AI7" s="6">
+        <f t="shared" si="4"/>
+        <v>12363.313002444989</v>
+      </c>
+      <c r="AJ7" s="6">
+        <f t="shared" si="4"/>
+        <v>12734.212392518339</v>
+      </c>
+      <c r="AK7" s="6">
+        <f t="shared" si="4"/>
+        <v>13116.23876429389</v>
+      </c>
+      <c r="AL7" s="6">
+        <f t="shared" si="4"/>
+        <v>13509.725927222707</v>
+      </c>
+      <c r="AM7" s="6">
+        <f t="shared" si="4"/>
+        <v>13915.017705039389</v>
+      </c>
+      <c r="AN7" s="6">
+        <f t="shared" si="4"/>
+        <v>14332.468236190571</v>
+      </c>
     </row>
     <row r="8" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>37</v>
       </c>
       <c r="X8" s="6">
-        <f t="shared" ref="X8:AC8" si="1">X6+X7</f>
+        <f t="shared" ref="X8:AC8" si="5">X6+X7</f>
         <v>53320</v>
       </c>
       <c r="Y8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>58367</v>
       </c>
       <c r="Z8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>59736</v>
       </c>
       <c r="AA8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>58609</v>
       </c>
       <c r="AB8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>60233</v>
       </c>
       <c r="AC8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>65069</v>
+      </c>
+      <c r="AD8" s="6">
+        <f t="shared" ref="AD8:AN8" si="6">AD6+AD7</f>
+        <v>64476.363000000005</v>
+      </c>
+      <c r="AE8" s="6">
+        <f t="shared" si="6"/>
+        <v>65334.420677999995</v>
+      </c>
+      <c r="AF8" s="6">
+        <f t="shared" si="6"/>
+        <v>66207.457754219999</v>
+      </c>
+      <c r="AG8" s="6">
+        <f t="shared" si="6"/>
+        <v>67095.815987285401</v>
+      </c>
+      <c r="AH8" s="6">
+        <f t="shared" si="6"/>
+        <v>67999.846312347145</v>
+      </c>
+      <c r="AI8" s="6">
+        <f t="shared" si="6"/>
+        <v>68919.909105615181</v>
+      </c>
+      <c r="AJ8" s="6">
+        <f t="shared" si="6"/>
+        <v>69856.374456720238</v>
+      </c>
+      <c r="AK8" s="6">
+        <f t="shared" si="6"/>
+        <v>70809.622449137809</v>
+      </c>
+      <c r="AL8" s="6">
+        <f t="shared" si="6"/>
+        <v>71780.043448915065</v>
+      </c>
+      <c r="AM8" s="6">
+        <f t="shared" si="6"/>
+        <v>72768.038401948666</v>
+      </c>
+      <c r="AN8" s="6">
+        <f t="shared" si="6"/>
+        <v>73774.019140068936</v>
       </c>
     </row>
     <row r="9" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1075,28 +1372,72 @@
         <v>12</v>
       </c>
       <c r="X9" s="9">
-        <f t="shared" ref="X9:AC9" si="2">X5-X8</f>
+        <f t="shared" ref="X9:AC9" si="7">X5-X8</f>
         <v>6492</v>
       </c>
       <c r="Y9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>7031</v>
       </c>
       <c r="Z9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>7308</v>
       </c>
       <c r="AA9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>7375</v>
       </c>
       <c r="AB9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>7338</v>
       </c>
       <c r="AC9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>5974</v>
+      </c>
+      <c r="AD9" s="9">
+        <f t="shared" ref="AD9:AN9" si="8">AD5-AD8</f>
+        <v>8105.1569999999992</v>
+      </c>
+      <c r="AE9" s="9">
+        <f t="shared" si="8"/>
+        <v>8215.2941220000066</v>
+      </c>
+      <c r="AF9" s="9">
+        <f t="shared" si="8"/>
+        <v>8327.4051817799918</v>
+      </c>
+      <c r="AG9" s="9">
+        <f t="shared" si="8"/>
+        <v>8441.5360957145895</v>
+      </c>
+      <c r="AH9" s="9">
+        <f t="shared" si="8"/>
+        <v>8557.7340246520471</v>
+      </c>
+      <c r="AI9" s="9">
+        <f t="shared" si="8"/>
+        <v>8676.0474099182902</v>
+      </c>
+      <c r="AJ9" s="9">
+        <f t="shared" si="8"/>
+        <v>8796.5260103877663</v>
+      </c>
+      <c r="AK9" s="9">
+        <f t="shared" si="8"/>
+        <v>8919.2209406530601</v>
+      </c>
+      <c r="AL9" s="9">
+        <f t="shared" si="8"/>
+        <v>9044.1847103258478</v>
+      </c>
+      <c r="AM9" s="9">
+        <f t="shared" si="8"/>
+        <v>9171.4712645033578</v>
+      </c>
+      <c r="AN9" s="9">
+        <f t="shared" si="8"/>
+        <v>9301.1360254348547</v>
       </c>
     </row>
     <row r="10" spans="2:40" x14ac:dyDescent="0.3">
@@ -1121,6 +1462,50 @@
       <c r="AC10" s="6">
         <v>87</v>
       </c>
+      <c r="AD10" s="6">
+        <f>AC10*1.03</f>
+        <v>89.61</v>
+      </c>
+      <c r="AE10" s="6">
+        <f t="shared" ref="AE10:AN10" si="9">AD10*1.03</f>
+        <v>92.298299999999998</v>
+      </c>
+      <c r="AF10" s="6">
+        <f t="shared" si="9"/>
+        <v>95.067249000000004</v>
+      </c>
+      <c r="AG10" s="6">
+        <f t="shared" si="9"/>
+        <v>97.919266470000011</v>
+      </c>
+      <c r="AH10" s="6">
+        <f t="shared" si="9"/>
+        <v>100.85684446410001</v>
+      </c>
+      <c r="AI10" s="6">
+        <f t="shared" si="9"/>
+        <v>103.88254979802301</v>
+      </c>
+      <c r="AJ10" s="6">
+        <f t="shared" si="9"/>
+        <v>106.9990262919637</v>
+      </c>
+      <c r="AK10" s="6">
+        <f t="shared" si="9"/>
+        <v>110.20899708072261</v>
+      </c>
+      <c r="AL10" s="6">
+        <f t="shared" si="9"/>
+        <v>113.51526699314429</v>
+      </c>
+      <c r="AM10" s="6">
+        <f t="shared" si="9"/>
+        <v>116.92072500293862</v>
+      </c>
+      <c r="AN10" s="6">
+        <f t="shared" si="9"/>
+        <v>120.42834675302679</v>
+      </c>
     </row>
     <row r="11" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
@@ -1144,6 +1529,50 @@
       <c r="AC11" s="6">
         <v>-1043</v>
       </c>
+      <c r="AD11" s="6">
+        <f>AC11*1.01</f>
+        <v>-1053.43</v>
+      </c>
+      <c r="AE11" s="6">
+        <f t="shared" ref="AE11:AN11" si="10">AD11*1.01</f>
+        <v>-1063.9643000000001</v>
+      </c>
+      <c r="AF11" s="6">
+        <f t="shared" si="10"/>
+        <v>-1074.6039430000001</v>
+      </c>
+      <c r="AG11" s="6">
+        <f t="shared" si="10"/>
+        <v>-1085.3499824300002</v>
+      </c>
+      <c r="AH11" s="6">
+        <f t="shared" si="10"/>
+        <v>-1096.2034822543003</v>
+      </c>
+      <c r="AI11" s="6">
+        <f t="shared" si="10"/>
+        <v>-1107.1655170768433</v>
+      </c>
+      <c r="AJ11" s="6">
+        <f t="shared" si="10"/>
+        <v>-1118.2371722476119</v>
+      </c>
+      <c r="AK11" s="6">
+        <f t="shared" si="10"/>
+        <v>-1129.4195439700879</v>
+      </c>
+      <c r="AL11" s="6">
+        <f t="shared" si="10"/>
+        <v>-1140.7137394097888</v>
+      </c>
+      <c r="AM11" s="6">
+        <f t="shared" si="10"/>
+        <v>-1152.1208768038866</v>
+      </c>
+      <c r="AN11" s="6">
+        <f t="shared" si="10"/>
+        <v>-1163.6420855719255</v>
+      </c>
     </row>
     <row r="12" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
@@ -1167,34 +1596,122 @@
       <c r="AC12" s="6">
         <v>-83</v>
       </c>
+      <c r="AD12" s="6">
+        <f>AC12*1.01</f>
+        <v>-83.83</v>
+      </c>
+      <c r="AE12" s="6">
+        <f t="shared" ref="AE12:AN12" si="11">AD12*1.01</f>
+        <v>-84.668300000000002</v>
+      </c>
+      <c r="AF12" s="6">
+        <f t="shared" si="11"/>
+        <v>-85.514983000000001</v>
+      </c>
+      <c r="AG12" s="6">
+        <f t="shared" si="11"/>
+        <v>-86.370132830000003</v>
+      </c>
+      <c r="AH12" s="6">
+        <f t="shared" si="11"/>
+        <v>-87.233834158299999</v>
+      </c>
+      <c r="AI12" s="6">
+        <f t="shared" si="11"/>
+        <v>-88.106172499883002</v>
+      </c>
+      <c r="AJ12" s="6">
+        <f t="shared" si="11"/>
+        <v>-88.987234224881831</v>
+      </c>
+      <c r="AK12" s="6">
+        <f t="shared" si="11"/>
+        <v>-89.877106567130653</v>
+      </c>
+      <c r="AL12" s="6">
+        <f t="shared" si="11"/>
+        <v>-90.775877632801965</v>
+      </c>
+      <c r="AM12" s="6">
+        <f t="shared" si="11"/>
+        <v>-91.683636409129988</v>
+      </c>
+      <c r="AN12" s="6">
+        <f t="shared" si="11"/>
+        <v>-92.600472773221284</v>
+      </c>
     </row>
     <row r="13" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>48</v>
       </c>
       <c r="X13" s="6">
-        <f t="shared" ref="X13:AC13" si="3">SUM(X10:X12)</f>
+        <f t="shared" ref="X13:AC13" si="12">SUM(X10:X12)</f>
         <v>-2053</v>
       </c>
       <c r="Y13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>-1613</v>
       </c>
       <c r="Z13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>-1815</v>
       </c>
       <c r="AA13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>-973</v>
       </c>
       <c r="AB13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>-1169</v>
       </c>
       <c r="AC13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>-1039</v>
+      </c>
+      <c r="AD13" s="6">
+        <f t="shared" ref="AD13:AN13" si="13">SUM(AD10:AD12)</f>
+        <v>-1047.6500000000001</v>
+      </c>
+      <c r="AE13" s="6">
+        <f t="shared" si="13"/>
+        <v>-1056.3343</v>
+      </c>
+      <c r="AF13" s="6">
+        <f t="shared" si="13"/>
+        <v>-1065.0516770000002</v>
+      </c>
+      <c r="AG13" s="6">
+        <f t="shared" si="13"/>
+        <v>-1073.8008487900001</v>
+      </c>
+      <c r="AH13" s="6">
+        <f t="shared" si="13"/>
+        <v>-1082.5804719485002</v>
+      </c>
+      <c r="AI13" s="6">
+        <f t="shared" si="13"/>
+        <v>-1091.3891397787033</v>
+      </c>
+      <c r="AJ13" s="6">
+        <f t="shared" si="13"/>
+        <v>-1100.22538018053</v>
+      </c>
+      <c r="AK13" s="6">
+        <f t="shared" si="13"/>
+        <v>-1109.0876534564959</v>
+      </c>
+      <c r="AL13" s="6">
+        <f t="shared" si="13"/>
+        <v>-1117.9743500494465</v>
+      </c>
+      <c r="AM13" s="6">
+        <f t="shared" si="13"/>
+        <v>-1126.8837882100781</v>
+      </c>
+      <c r="AN13" s="6">
+        <f t="shared" si="13"/>
+        <v>-1135.81421159212</v>
       </c>
     </row>
     <row r="14" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1202,28 +1719,72 @@
         <v>40</v>
       </c>
       <c r="X14" s="9">
-        <f t="shared" ref="X14:AC14" si="4">X9-X13</f>
+        <f t="shared" ref="X14:AC14" si="14">X9-X13</f>
         <v>8545</v>
       </c>
       <c r="Y14" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>8644</v>
       </c>
       <c r="Z14" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>9123</v>
       </c>
       <c r="AA14" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>8348</v>
       </c>
       <c r="AB14" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>8507</v>
       </c>
       <c r="AC14" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>7013</v>
+      </c>
+      <c r="AD14" s="9">
+        <f t="shared" ref="AD14:AN14" si="15">AD9-AD13</f>
+        <v>9152.8069999999989</v>
+      </c>
+      <c r="AE14" s="9">
+        <f t="shared" si="15"/>
+        <v>9271.628422000007</v>
+      </c>
+      <c r="AF14" s="9">
+        <f t="shared" si="15"/>
+        <v>9392.4568587799913</v>
+      </c>
+      <c r="AG14" s="9">
+        <f t="shared" si="15"/>
+        <v>9515.3369445045901</v>
+      </c>
+      <c r="AH14" s="9">
+        <f t="shared" si="15"/>
+        <v>9640.3144966005475</v>
+      </c>
+      <c r="AI14" s="9">
+        <f t="shared" si="15"/>
+        <v>9767.4365496969931</v>
+      </c>
+      <c r="AJ14" s="9">
+        <f t="shared" si="15"/>
+        <v>9896.7513905682972</v>
+      </c>
+      <c r="AK14" s="9">
+        <f t="shared" si="15"/>
+        <v>10028.308594109556</v>
+      </c>
+      <c r="AL14" s="9">
+        <f t="shared" si="15"/>
+        <v>10162.159060375294</v>
+      </c>
+      <c r="AM14" s="9">
+        <f t="shared" si="15"/>
+        <v>10298.355052713436</v>
+      </c>
+      <c r="AN14" s="9">
+        <f t="shared" si="15"/>
+        <v>10436.950237026975</v>
       </c>
     </row>
     <row r="15" spans="2:40" x14ac:dyDescent="0.3">
@@ -1248,6 +1809,50 @@
       <c r="AC15" s="6">
         <v>1036</v>
       </c>
+      <c r="AD15" s="6">
+        <f>AC15*1.01</f>
+        <v>1046.3599999999999</v>
+      </c>
+      <c r="AE15" s="6">
+        <f t="shared" ref="AE15:AN15" si="16">AD15*1.01</f>
+        <v>1056.8235999999999</v>
+      </c>
+      <c r="AF15" s="6">
+        <f t="shared" si="16"/>
+        <v>1067.391836</v>
+      </c>
+      <c r="AG15" s="6">
+        <f t="shared" si="16"/>
+        <v>1078.06575436</v>
+      </c>
+      <c r="AH15" s="6">
+        <f t="shared" si="16"/>
+        <v>1088.8464119036</v>
+      </c>
+      <c r="AI15" s="6">
+        <f t="shared" si="16"/>
+        <v>1099.7348760226359</v>
+      </c>
+      <c r="AJ15" s="6">
+        <f t="shared" si="16"/>
+        <v>1110.7322247828622</v>
+      </c>
+      <c r="AK15" s="6">
+        <f t="shared" si="16"/>
+        <v>1121.8395470306909</v>
+      </c>
+      <c r="AL15" s="6">
+        <f t="shared" si="16"/>
+        <v>1133.0579425009978</v>
+      </c>
+      <c r="AM15" s="6">
+        <f t="shared" si="16"/>
+        <v>1144.3885219260078</v>
+      </c>
+      <c r="AN15" s="6">
+        <f t="shared" si="16"/>
+        <v>1155.8324071452678</v>
+      </c>
     </row>
     <row r="16" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
@@ -1271,8 +1876,41 @@
       <c r="AC16" s="6">
         <v>-62</v>
       </c>
-    </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>43</v>
       </c>
@@ -1294,66 +1932,187 @@
       <c r="AC17" s="6">
         <v>-181</v>
       </c>
-    </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
       <c r="X18" s="6">
-        <f t="shared" ref="X18:AC18" si="5">SUM(X15:X17)</f>
+        <f t="shared" ref="X18:AC18" si="17">SUM(X15:X17)</f>
         <v>1304</v>
       </c>
       <c r="Y18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>409</v>
       </c>
       <c r="Z18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>1573</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>1668</v>
       </c>
       <c r="AB18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>409</v>
       </c>
       <c r="AC18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>793</v>
       </c>
-    </row>
-    <row r="19" spans="2:29" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AD18" s="6">
+        <f t="shared" ref="AD18:AN18" si="18">SUM(AD15:AD17)</f>
+        <v>1046.3599999999999</v>
+      </c>
+      <c r="AE18" s="6">
+        <f t="shared" si="18"/>
+        <v>1056.8235999999999</v>
+      </c>
+      <c r="AF18" s="6">
+        <f t="shared" si="18"/>
+        <v>1067.391836</v>
+      </c>
+      <c r="AG18" s="6">
+        <f t="shared" si="18"/>
+        <v>1078.06575436</v>
+      </c>
+      <c r="AH18" s="6">
+        <f t="shared" si="18"/>
+        <v>1088.8464119036</v>
+      </c>
+      <c r="AI18" s="6">
+        <f t="shared" si="18"/>
+        <v>1099.7348760226359</v>
+      </c>
+      <c r="AJ18" s="6">
+        <f t="shared" si="18"/>
+        <v>1110.7322247828622</v>
+      </c>
+      <c r="AK18" s="6">
+        <f t="shared" si="18"/>
+        <v>1121.8395470306909</v>
+      </c>
+      <c r="AL18" s="6">
+        <f t="shared" si="18"/>
+        <v>1133.0579425009978</v>
+      </c>
+      <c r="AM18" s="6">
+        <f t="shared" si="18"/>
+        <v>1144.3885219260078</v>
+      </c>
+      <c r="AN18" s="6">
+        <f t="shared" si="18"/>
+        <v>1155.8324071452678</v>
+      </c>
+    </row>
+    <row r="19" spans="2:138" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" ref="X19:AC19" si="6">X14-X18</f>
+        <f t="shared" ref="X19:AC19" si="19">X14-X18</f>
         <v>7241</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>8235</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>7550</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>6680</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>8098</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>6220</v>
       </c>
-    </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD19" s="9">
+        <f t="shared" ref="AD19:AN19" si="20">AD14-AD18</f>
+        <v>8106.4469999999992</v>
+      </c>
+      <c r="AE19" s="9">
+        <f t="shared" si="20"/>
+        <v>8214.8048220000073</v>
+      </c>
+      <c r="AF19" s="9">
+        <f t="shared" si="20"/>
+        <v>8325.0650227799906</v>
+      </c>
+      <c r="AG19" s="9">
+        <f t="shared" si="20"/>
+        <v>8437.2711901445909</v>
+      </c>
+      <c r="AH19" s="9">
+        <f t="shared" si="20"/>
+        <v>8551.4680846969477</v>
+      </c>
+      <c r="AI19" s="9">
+        <f t="shared" si="20"/>
+        <v>8667.7016736743572</v>
+      </c>
+      <c r="AJ19" s="9">
+        <f t="shared" si="20"/>
+        <v>8786.0191657854357</v>
+      </c>
+      <c r="AK19" s="9">
+        <f t="shared" si="20"/>
+        <v>8906.4690470788646</v>
+      </c>
+      <c r="AL19" s="9">
+        <f t="shared" si="20"/>
+        <v>9029.1011178742956</v>
+      </c>
+      <c r="AM19" s="9">
+        <f t="shared" si="20"/>
+        <v>9153.9665307874275</v>
+      </c>
+      <c r="AN19" s="9">
+        <f t="shared" si="20"/>
+        <v>9281.1178298817067</v>
+      </c>
+    </row>
+    <row r="20" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>45</v>
       </c>
@@ -1375,344 +2134,1370 @@
       <c r="AC20" s="6">
         <v>884</v>
       </c>
-    </row>
-    <row r="21" spans="2:29" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AD20" s="6">
+        <f>AD19*0.15</f>
+        <v>1215.9670499999997</v>
+      </c>
+      <c r="AE20" s="6">
+        <f t="shared" ref="AE20:AN20" si="21">AE19*0.15</f>
+        <v>1232.2207233000011</v>
+      </c>
+      <c r="AF20" s="6">
+        <f t="shared" si="21"/>
+        <v>1248.7597534169986</v>
+      </c>
+      <c r="AG20" s="6">
+        <f t="shared" si="21"/>
+        <v>1265.5906785216887</v>
+      </c>
+      <c r="AH20" s="6">
+        <f t="shared" si="21"/>
+        <v>1282.7202127045421</v>
+      </c>
+      <c r="AI20" s="6">
+        <f t="shared" si="21"/>
+        <v>1300.1552510511535</v>
+      </c>
+      <c r="AJ20" s="6">
+        <f t="shared" si="21"/>
+        <v>1317.9028748678154</v>
+      </c>
+      <c r="AK20" s="6">
+        <f t="shared" si="21"/>
+        <v>1335.9703570618296</v>
+      </c>
+      <c r="AL20" s="6">
+        <f t="shared" si="21"/>
+        <v>1354.3651676811444</v>
+      </c>
+      <c r="AM20" s="6">
+        <f t="shared" si="21"/>
+        <v>1373.0949796181142</v>
+      </c>
+      <c r="AN20" s="6">
+        <f t="shared" si="21"/>
+        <v>1392.167674482256</v>
+      </c>
+    </row>
+    <row r="21" spans="2:138" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>46</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" ref="X21:AC21" si="7">X19-X20</f>
+        <f t="shared" ref="X21:AC21" si="22">X19-X20</f>
         <v>6230</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>6888</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>6315</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>5732</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>6920</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>5336</v>
       </c>
-    </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD21" s="9">
+        <f t="shared" ref="AD21:AN21" si="23">AD19-AD20</f>
+        <v>6890.479949999999</v>
+      </c>
+      <c r="AE21" s="9">
+        <f t="shared" si="23"/>
+        <v>6982.5840987000065</v>
+      </c>
+      <c r="AF21" s="9">
+        <f t="shared" si="23"/>
+        <v>7076.3052693629925</v>
+      </c>
+      <c r="AG21" s="9">
+        <f t="shared" si="23"/>
+        <v>7171.6805116229025</v>
+      </c>
+      <c r="AH21" s="9">
+        <f t="shared" si="23"/>
+        <v>7268.7478719924056</v>
+      </c>
+      <c r="AI21" s="9">
+        <f t="shared" si="23"/>
+        <v>7367.5464226232034</v>
+      </c>
+      <c r="AJ21" s="9">
+        <f t="shared" si="23"/>
+        <v>7468.1162909176201</v>
+      </c>
+      <c r="AK21" s="9">
+        <f t="shared" si="23"/>
+        <v>7570.4986900170352</v>
+      </c>
+      <c r="AL21" s="9">
+        <f t="shared" si="23"/>
+        <v>7674.7359501931514</v>
+      </c>
+      <c r="AM21" s="9">
+        <f t="shared" si="23"/>
+        <v>7780.8715511693135</v>
+      </c>
+      <c r="AN21" s="9">
+        <f t="shared" si="23"/>
+        <v>7888.9501553994505</v>
+      </c>
+      <c r="AO21" s="3">
+        <f>AN21*(1+$AQ$26)</f>
+        <v>7810.0606538454558</v>
+      </c>
+      <c r="AP21" s="3">
+        <f t="shared" ref="AP21:DA21" si="24">AO21*(1+$AQ$26)</f>
+        <v>7731.9600473070013</v>
+      </c>
+      <c r="AQ21" s="3">
+        <f t="shared" si="24"/>
+        <v>7654.6404468339315</v>
+      </c>
+      <c r="AR21" s="3">
+        <f t="shared" si="24"/>
+        <v>7578.094042365592</v>
+      </c>
+      <c r="AS21" s="3">
+        <f t="shared" si="24"/>
+        <v>7502.3131019419361</v>
+      </c>
+      <c r="AT21" s="3">
+        <f t="shared" si="24"/>
+        <v>7427.2899709225167</v>
+      </c>
+      <c r="AU21" s="3">
+        <f t="shared" si="24"/>
+        <v>7353.0170712132913</v>
+      </c>
+      <c r="AV21" s="3">
+        <f t="shared" si="24"/>
+        <v>7279.4869005011587</v>
+      </c>
+      <c r="AW21" s="3">
+        <f t="shared" si="24"/>
+        <v>7206.6920314961471</v>
+      </c>
+      <c r="AX21" s="3">
+        <f t="shared" si="24"/>
+        <v>7134.6251111811853</v>
+      </c>
+      <c r="AY21" s="3">
+        <f t="shared" si="24"/>
+        <v>7063.278860069373</v>
+      </c>
+      <c r="AZ21" s="3">
+        <f t="shared" si="24"/>
+        <v>6992.6460714686791</v>
+      </c>
+      <c r="BA21" s="3">
+        <f t="shared" si="24"/>
+        <v>6922.7196107539921</v>
+      </c>
+      <c r="BB21" s="3">
+        <f t="shared" si="24"/>
+        <v>6853.4924146464518</v>
+      </c>
+      <c r="BC21" s="3">
+        <f t="shared" si="24"/>
+        <v>6784.9574904999872</v>
+      </c>
+      <c r="BD21" s="3">
+        <f t="shared" si="24"/>
+        <v>6717.1079155949874</v>
+      </c>
+      <c r="BE21" s="3">
+        <f t="shared" si="24"/>
+        <v>6649.9368364390375</v>
+      </c>
+      <c r="BF21" s="3">
+        <f t="shared" si="24"/>
+        <v>6583.4374680746469</v>
+      </c>
+      <c r="BG21" s="3">
+        <f t="shared" si="24"/>
+        <v>6517.6030933939001</v>
+      </c>
+      <c r="BH21" s="3">
+        <f t="shared" si="24"/>
+        <v>6452.4270624599612</v>
+      </c>
+      <c r="BI21" s="3">
+        <f t="shared" si="24"/>
+        <v>6387.9027918353613</v>
+      </c>
+      <c r="BJ21" s="3">
+        <f t="shared" si="24"/>
+        <v>6324.0237639170073</v>
+      </c>
+      <c r="BK21" s="3">
+        <f t="shared" si="24"/>
+        <v>6260.7835262778372</v>
+      </c>
+      <c r="BL21" s="3">
+        <f t="shared" si="24"/>
+        <v>6198.1756910150589</v>
+      </c>
+      <c r="BM21" s="3">
+        <f t="shared" si="24"/>
+        <v>6136.1939341049083</v>
+      </c>
+      <c r="BN21" s="3">
+        <f t="shared" si="24"/>
+        <v>6074.8319947638593</v>
+      </c>
+      <c r="BO21" s="3">
+        <f t="shared" si="24"/>
+        <v>6014.083674816221</v>
+      </c>
+      <c r="BP21" s="3">
+        <f t="shared" si="24"/>
+        <v>5953.9428380680583</v>
+      </c>
+      <c r="BQ21" s="3">
+        <f t="shared" si="24"/>
+        <v>5894.4034096873775</v>
+      </c>
+      <c r="BR21" s="3">
+        <f t="shared" si="24"/>
+        <v>5835.4593755905034</v>
+      </c>
+      <c r="BS21" s="3">
+        <f t="shared" si="24"/>
+        <v>5777.1047818345987</v>
+      </c>
+      <c r="BT21" s="3">
+        <f t="shared" si="24"/>
+        <v>5719.3337340162525</v>
+      </c>
+      <c r="BU21" s="3">
+        <f t="shared" si="24"/>
+        <v>5662.1403966760899</v>
+      </c>
+      <c r="BV21" s="3">
+        <f t="shared" si="24"/>
+        <v>5605.5189927093288</v>
+      </c>
+      <c r="BW21" s="3">
+        <f t="shared" si="24"/>
+        <v>5549.4638027822357</v>
+      </c>
+      <c r="BX21" s="3">
+        <f t="shared" si="24"/>
+        <v>5493.9691647544132</v>
+      </c>
+      <c r="BY21" s="3">
+        <f t="shared" si="24"/>
+        <v>5439.0294731068689</v>
+      </c>
+      <c r="BZ21" s="3">
+        <f t="shared" si="24"/>
+        <v>5384.6391783757999</v>
+      </c>
+      <c r="CA21" s="3">
+        <f t="shared" si="24"/>
+        <v>5330.7927865920419</v>
+      </c>
+      <c r="CB21" s="3">
+        <f t="shared" si="24"/>
+        <v>5277.4848587261213</v>
+      </c>
+      <c r="CC21" s="3">
+        <f t="shared" si="24"/>
+        <v>5224.7100101388596</v>
+      </c>
+      <c r="CD21" s="3">
+        <f t="shared" si="24"/>
+        <v>5172.4629100374714</v>
+      </c>
+      <c r="CE21" s="3">
+        <f t="shared" si="24"/>
+        <v>5120.7382809370965</v>
+      </c>
+      <c r="CF21" s="3">
+        <f t="shared" si="24"/>
+        <v>5069.5308981277258</v>
+      </c>
+      <c r="CG21" s="3">
+        <f t="shared" si="24"/>
+        <v>5018.8355891464489</v>
+      </c>
+      <c r="CH21" s="3">
+        <f t="shared" si="24"/>
+        <v>4968.6472332549847</v>
+      </c>
+      <c r="CI21" s="3">
+        <f t="shared" si="24"/>
+        <v>4918.9607609224349</v>
+      </c>
+      <c r="CJ21" s="3">
+        <f t="shared" si="24"/>
+        <v>4869.7711533132106</v>
+      </c>
+      <c r="CK21" s="3">
+        <f t="shared" si="24"/>
+        <v>4821.0734417800786</v>
+      </c>
+      <c r="CL21" s="3">
+        <f t="shared" si="24"/>
+        <v>4772.8627073622774</v>
+      </c>
+      <c r="CM21" s="3">
+        <f t="shared" si="24"/>
+        <v>4725.1340802886543</v>
+      </c>
+      <c r="CN21" s="3">
+        <f t="shared" si="24"/>
+        <v>4677.8827394857681</v>
+      </c>
+      <c r="CO21" s="3">
+        <f t="shared" si="24"/>
+        <v>4631.1039120909099</v>
+      </c>
+      <c r="CP21" s="3">
+        <f t="shared" si="24"/>
+        <v>4584.7928729700006</v>
+      </c>
+      <c r="CQ21" s="3">
+        <f t="shared" si="24"/>
+        <v>4538.9449442403002</v>
+      </c>
+      <c r="CR21" s="3">
+        <f t="shared" si="24"/>
+        <v>4493.5554947978972</v>
+      </c>
+      <c r="CS21" s="3">
+        <f t="shared" si="24"/>
+        <v>4448.6199398499184</v>
+      </c>
+      <c r="CT21" s="3">
+        <f t="shared" si="24"/>
+        <v>4404.1337404514188</v>
+      </c>
+      <c r="CU21" s="3">
+        <f t="shared" si="24"/>
+        <v>4360.092403046905</v>
+      </c>
+      <c r="CV21" s="3">
+        <f t="shared" si="24"/>
+        <v>4316.4914790164357</v>
+      </c>
+      <c r="CW21" s="3">
+        <f t="shared" si="24"/>
+        <v>4273.3265642262713</v>
+      </c>
+      <c r="CX21" s="3">
+        <f t="shared" si="24"/>
+        <v>4230.5932985840082</v>
+      </c>
+      <c r="CY21" s="3">
+        <f t="shared" si="24"/>
+        <v>4188.2873655981684</v>
+      </c>
+      <c r="CZ21" s="3">
+        <f t="shared" si="24"/>
+        <v>4146.4044919421867</v>
+      </c>
+      <c r="DA21" s="3">
+        <f t="shared" si="24"/>
+        <v>4104.9404470227646</v>
+      </c>
+      <c r="DB21" s="3">
+        <f t="shared" ref="DB21:EH21" si="25">DA21*(1+$AQ$26)</f>
+        <v>4063.8910425525369</v>
+      </c>
+      <c r="DC21" s="3">
+        <f t="shared" si="25"/>
+        <v>4023.2521321270115</v>
+      </c>
+      <c r="DD21" s="3">
+        <f t="shared" si="25"/>
+        <v>3983.0196108057412</v>
+      </c>
+      <c r="DE21" s="3">
+        <f t="shared" si="25"/>
+        <v>3943.1894146976838</v>
+      </c>
+      <c r="DF21" s="3">
+        <f t="shared" si="25"/>
+        <v>3903.7575205507069</v>
+      </c>
+      <c r="DG21" s="3">
+        <f t="shared" si="25"/>
+        <v>3864.7199453451999</v>
+      </c>
+      <c r="DH21" s="3">
+        <f t="shared" si="25"/>
+        <v>3826.0727458917477</v>
+      </c>
+      <c r="DI21" s="3">
+        <f t="shared" si="25"/>
+        <v>3787.81201843283</v>
+      </c>
+      <c r="DJ21" s="3">
+        <f t="shared" si="25"/>
+        <v>3749.9338982485015</v>
+      </c>
+      <c r="DK21" s="3">
+        <f t="shared" si="25"/>
+        <v>3712.4345592660165</v>
+      </c>
+      <c r="DL21" s="3">
+        <f t="shared" si="25"/>
+        <v>3675.3102136733564</v>
+      </c>
+      <c r="DM21" s="3">
+        <f t="shared" si="25"/>
+        <v>3638.5571115366229</v>
+      </c>
+      <c r="DN21" s="3">
+        <f t="shared" si="25"/>
+        <v>3602.1715404212564</v>
+      </c>
+      <c r="DO21" s="3">
+        <f t="shared" si="25"/>
+        <v>3566.1498250170439</v>
+      </c>
+      <c r="DP21" s="3">
+        <f t="shared" si="25"/>
+        <v>3530.4883267668733</v>
+      </c>
+      <c r="DQ21" s="3">
+        <f t="shared" si="25"/>
+        <v>3495.1834434992047</v>
+      </c>
+      <c r="DR21" s="3">
+        <f t="shared" si="25"/>
+        <v>3460.2316090642125</v>
+      </c>
+      <c r="DS21" s="3">
+        <f t="shared" si="25"/>
+        <v>3425.6292929735705</v>
+      </c>
+      <c r="DT21" s="3">
+        <f t="shared" si="25"/>
+        <v>3391.373000043835</v>
+      </c>
+      <c r="DU21" s="3">
+        <f t="shared" si="25"/>
+        <v>3357.4592700433964</v>
+      </c>
+      <c r="DV21" s="3">
+        <f t="shared" si="25"/>
+        <v>3323.8846773429623</v>
+      </c>
+      <c r="DW21" s="3">
+        <f t="shared" si="25"/>
+        <v>3290.6458305695328</v>
+      </c>
+      <c r="DX21" s="3">
+        <f t="shared" si="25"/>
+        <v>3257.7393722638376</v>
+      </c>
+      <c r="DY21" s="3">
+        <f t="shared" si="25"/>
+        <v>3225.161978541199</v>
+      </c>
+      <c r="DZ21" s="3">
+        <f t="shared" si="25"/>
+        <v>3192.910358755787</v>
+      </c>
+      <c r="EA21" s="3">
+        <f t="shared" si="25"/>
+        <v>3160.9812551682289</v>
+      </c>
+      <c r="EB21" s="3">
+        <f t="shared" si="25"/>
+        <v>3129.3714426165466</v>
+      </c>
+      <c r="EC21" s="3">
+        <f t="shared" si="25"/>
+        <v>3098.0777281903811</v>
+      </c>
+      <c r="ED21" s="3">
+        <f t="shared" si="25"/>
+        <v>3067.0969509084771</v>
+      </c>
+      <c r="EE21" s="3">
+        <f t="shared" si="25"/>
+        <v>3036.4259813993922</v>
+      </c>
+      <c r="EF21" s="3">
+        <f t="shared" si="25"/>
+        <v>3006.0617215853981</v>
+      </c>
+      <c r="EG21" s="3">
+        <f t="shared" si="25"/>
+        <v>2976.001104369544</v>
+      </c>
+      <c r="EH21" s="3">
+        <f t="shared" si="25"/>
+        <v>2946.2410933258484</v>
+      </c>
+    </row>
+    <row r="22" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>2</v>
       </c>
       <c r="X22" s="6">
-        <f t="shared" ref="X22:AC22" si="8">235.4</f>
+        <f t="shared" ref="X22:AN22" si="26">235.4</f>
         <v>235.4</v>
       </c>
       <c r="Y22" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="26"/>
         <v>235.4</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="26"/>
         <v>235.4</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="26"/>
         <v>235.4</v>
       </c>
       <c r="AB22" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="26"/>
         <v>235.4</v>
       </c>
       <c r="AC22" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="26"/>
         <v>235.4</v>
       </c>
-    </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD22" s="6">
+        <f t="shared" si="26"/>
+        <v>235.4</v>
+      </c>
+      <c r="AE22" s="6">
+        <f t="shared" si="26"/>
+        <v>235.4</v>
+      </c>
+      <c r="AF22" s="6">
+        <f t="shared" si="26"/>
+        <v>235.4</v>
+      </c>
+      <c r="AG22" s="6">
+        <f t="shared" si="26"/>
+        <v>235.4</v>
+      </c>
+      <c r="AH22" s="6">
+        <f t="shared" si="26"/>
+        <v>235.4</v>
+      </c>
+      <c r="AI22" s="6">
+        <f t="shared" si="26"/>
+        <v>235.4</v>
+      </c>
+      <c r="AJ22" s="6">
+        <f t="shared" si="26"/>
+        <v>235.4</v>
+      </c>
+      <c r="AK22" s="6">
+        <f t="shared" si="26"/>
+        <v>235.4</v>
+      </c>
+      <c r="AL22" s="6">
+        <f t="shared" si="26"/>
+        <v>235.4</v>
+      </c>
+      <c r="AM22" s="6">
+        <f t="shared" si="26"/>
+        <v>235.4</v>
+      </c>
+      <c r="AN22" s="6">
+        <f t="shared" si="26"/>
+        <v>235.4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>47</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" ref="X23:AC23" si="9">X21/X22</f>
+        <f t="shared" ref="X23:AC23" si="27">X21/X22</f>
         <v>26.465590484282071</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="27"/>
         <v>29.260832625318606</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="27"/>
         <v>26.826677994902294</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="27"/>
         <v>24.350042480883602</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="27"/>
         <v>29.396771452846217</v>
       </c>
       <c r="AC23" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="27"/>
         <v>22.667799490229395</v>
       </c>
-    </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD23" s="10">
+        <f t="shared" ref="AD23:AN23" si="28">AD21/AD22</f>
+        <v>29.271367672047575</v>
+      </c>
+      <c r="AE23" s="10">
+        <f t="shared" si="28"/>
+        <v>29.662634234069696</v>
+      </c>
+      <c r="AF23" s="10">
+        <f t="shared" si="28"/>
+        <v>30.060770048270996</v>
+      </c>
+      <c r="AG23" s="10">
+        <f t="shared" si="28"/>
+        <v>30.465932504770187</v>
+      </c>
+      <c r="AH23" s="10">
+        <f t="shared" si="28"/>
+        <v>30.878283228514892</v>
+      </c>
+      <c r="AI23" s="10">
+        <f t="shared" si="28"/>
+        <v>31.297988201457958</v>
+      </c>
+      <c r="AJ23" s="10">
+        <f t="shared" si="28"/>
+        <v>31.725217888350127</v>
+      </c>
+      <c r="AK23" s="10">
+        <f t="shared" si="28"/>
+        <v>32.160147366257583</v>
+      </c>
+      <c r="AL23" s="10">
+        <f t="shared" si="28"/>
+        <v>32.602956457914829</v>
+      </c>
+      <c r="AM23" s="10">
+        <f t="shared" si="28"/>
+        <v>33.053829869028519</v>
+      </c>
+      <c r="AN23" s="10">
+        <f t="shared" si="28"/>
+        <v>33.512957329649325</v>
+      </c>
+    </row>
+    <row r="25" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>50</v>
       </c>
       <c r="X25" s="11"/>
       <c r="Y25" s="11">
-        <f t="shared" ref="Y25:AB27" si="10">Y3/X3-1</f>
+        <f t="shared" ref="Y25:AB27" si="29">Y3/X3-1</f>
         <v>9.7396759434998925E-2</v>
       </c>
       <c r="Z25" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="29"/>
         <v>2.7435916108359937E-2</v>
       </c>
       <c r="AA25" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="29"/>
         <v>-1.7170195800478405E-2</v>
       </c>
       <c r="AB25" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="29"/>
         <v>1.4405221216601261E-2</v>
       </c>
       <c r="AC25" s="11">
         <f>AC3/AB3-1</f>
         <v>5.3532391362303366E-2</v>
       </c>
-    </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD25" s="11">
+        <f t="shared" ref="AD25:AN27" si="30">AD3/AC3-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE25" s="11">
+        <f t="shared" si="30"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AF25" s="11">
+        <f t="shared" si="30"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AG25" s="11">
+        <f t="shared" si="30"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH25" s="11">
+        <f t="shared" si="30"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AI25" s="11">
+        <f t="shared" si="30"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AJ25" s="11">
+        <f t="shared" si="30"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AK25" s="11">
+        <f t="shared" si="30"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AL25" s="11">
+        <f t="shared" si="30"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AM25" s="11">
+        <f t="shared" si="30"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AN25" s="11">
+        <f t="shared" si="30"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>51</v>
       </c>
       <c r="X26" s="11"/>
       <c r="Y26" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="29"/>
         <v>7.2855825391945794E-2</v>
       </c>
       <c r="Z26" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="29"/>
         <v>1.3276026743075375E-2</v>
       </c>
       <c r="AA26" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="29"/>
         <v>-8.5776227731171328E-3</v>
       </c>
       <c r="AB26" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="29"/>
         <v>7.4919186157064166E-2</v>
       </c>
       <c r="AC26" s="11">
-        <f t="shared" ref="AC26:AC27" si="11">AC4/AB4-1</f>
+        <f t="shared" ref="AC26:AC27" si="31">AC4/AB4-1</f>
         <v>4.0686361224128831E-2</v>
       </c>
-    </row>
-    <row r="27" spans="2:29" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AD26" s="11">
+        <f t="shared" si="30"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AE26" s="11">
+        <f t="shared" si="30"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AF26" s="11">
+        <f t="shared" si="30"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AG26" s="11">
+        <f t="shared" si="30"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AH26" s="11">
+        <f t="shared" si="30"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AI26" s="11">
+        <f t="shared" si="30"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AJ26" s="11">
+        <f t="shared" si="30"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AK26" s="11">
+        <f t="shared" si="30"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AL26" s="11">
+        <f t="shared" si="30"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AM26" s="11">
+        <f t="shared" si="30"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AN26" s="11">
+        <f t="shared" si="30"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AP26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AQ26" s="11">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="27" spans="2:138" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>52</v>
       </c>
       <c r="X27" s="12"/>
       <c r="Y27" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="29"/>
         <v>9.3392630241423191E-2</v>
       </c>
       <c r="Z27" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="29"/>
         <v>2.516896541178637E-2</v>
       </c>
       <c r="AA27" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="29"/>
         <v>-1.5810512499254248E-2</v>
       </c>
       <c r="AB27" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="29"/>
         <v>2.4051285160038738E-2</v>
       </c>
       <c r="AC27" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="31"/>
         <v>5.1382989744120922E-2</v>
       </c>
-    </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD27" s="12">
+        <f t="shared" si="30"/>
+        <v>2.1656180059963726E-2</v>
+      </c>
+      <c r="AE27" s="12">
+        <f t="shared" si="30"/>
+        <v>1.33394120156205E-2</v>
+      </c>
+      <c r="AF27" s="12">
+        <f t="shared" si="30"/>
+        <v>1.3394316193867661E-2</v>
+      </c>
+      <c r="AG27" s="12">
+        <f t="shared" si="30"/>
+        <v>1.3449936144120933E-2</v>
+      </c>
+      <c r="AH27" s="12">
+        <f t="shared" si="30"/>
+        <v>1.3506275052879602E-2</v>
+      </c>
+      <c r="AI27" s="12">
+        <f t="shared" si="30"/>
+        <v>1.356333590956571E-2</v>
+      </c>
+      <c r="AJ27" s="12">
+        <f t="shared" si="30"/>
+        <v>1.3621121499584277E-2</v>
+      </c>
+      <c r="AK27" s="12">
+        <f t="shared" si="30"/>
+        <v>1.3679634397371299E-2</v>
+      </c>
+      <c r="AL27" s="12">
+        <f t="shared" si="30"/>
+        <v>1.3738876959430435E-2</v>
+      </c>
+      <c r="AM27" s="12">
+        <f t="shared" si="30"/>
+        <v>1.3798851317376792E-2</v>
+      </c>
+      <c r="AN27" s="12">
+        <f t="shared" si="30"/>
+        <v>1.3859559370987151E-2</v>
+      </c>
+      <c r="AP27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ27" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>53</v>
       </c>
       <c r="X28" s="11">
-        <f t="shared" ref="X28:AB28" si="12">(X3-X6)/X3</f>
+        <f t="shared" ref="X28:AB28" si="32">(X3-X6)/X3</f>
         <v>0.10916428585699159</v>
       </c>
       <c r="Y28" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="32"/>
         <v>0.10799592193416836</v>
       </c>
       <c r="Z28" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="32"/>
         <v>0.10918756091078231</v>
       </c>
       <c r="AA28" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="32"/>
         <v>0.11013954494645369</v>
       </c>
       <c r="AB28" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="32"/>
         <v>0.10768683906513818</v>
       </c>
       <c r="AC28" s="11">
         <f>(AC3-AC6)/AC3</f>
         <v>7.4649526797914881E-2</v>
       </c>
-    </row>
-    <row r="29" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD28" s="11">
+        <f t="shared" ref="AD28:AN28" si="33">(AD3-AD6)/AD3</f>
+        <v>0.10999999999999996</v>
+      </c>
+      <c r="AE28" s="11">
+        <f t="shared" si="33"/>
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="AF28" s="11">
+        <f t="shared" si="33"/>
+        <v>0.10999999999999996</v>
+      </c>
+      <c r="AG28" s="11">
+        <f t="shared" si="33"/>
+        <v>0.10999999999999995</v>
+      </c>
+      <c r="AH28" s="11">
+        <f t="shared" si="33"/>
+        <v>0.11000000000000001</v>
+      </c>
+      <c r="AI28" s="11">
+        <f t="shared" si="33"/>
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="AJ28" s="11">
+        <f t="shared" si="33"/>
+        <v>0.11000000000000003</v>
+      </c>
+      <c r="AK28" s="11">
+        <f t="shared" si="33"/>
+        <v>0.11000000000000001</v>
+      </c>
+      <c r="AL28" s="11">
+        <f t="shared" si="33"/>
+        <v>0.10999999999999995</v>
+      </c>
+      <c r="AM28" s="11">
+        <f t="shared" si="33"/>
+        <v>0.11000000000000004</v>
+      </c>
+      <c r="AN28" s="11">
+        <f t="shared" si="33"/>
+        <v>0.11</v>
+      </c>
+      <c r="AP28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ28" s="6">
+        <f>NPV(AQ27,AD21:EH21)</f>
+        <v>101171.23586137164</v>
+      </c>
+    </row>
+    <row r="29" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>54</v>
       </c>
       <c r="X29" s="11">
-        <f t="shared" ref="X29:AB29" si="13">(X4-X7)/X4</f>
+        <f t="shared" ref="X29:AB29" si="34">(X4-X7)/X4</f>
         <v>0.10533866174812993</v>
       </c>
       <c r="Y29" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="34"/>
         <v>0.10496657115568291</v>
       </c>
       <c r="Z29" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="34"/>
         <v>0.10802149118672826</v>
       </c>
       <c r="AA29" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="34"/>
         <v>0.12036508841985168</v>
       </c>
       <c r="AB29" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="34"/>
         <v>0.11312577392534937</v>
       </c>
       <c r="AC29" s="11">
         <f>(AC4-AC7)/AC4</f>
         <v>0.13165051844297126</v>
       </c>
-    </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD29" s="11">
+        <f t="shared" ref="AD29:AN29" si="35">(AD4-AD7)/AD4</f>
+        <v>0.11999999999999995</v>
+      </c>
+      <c r="AE29" s="11">
+        <f t="shared" si="35"/>
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="AF29" s="11">
+        <f t="shared" si="35"/>
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="AG29" s="11">
+        <f t="shared" si="35"/>
+        <v>0.12000000000000004</v>
+      </c>
+      <c r="AH29" s="11">
+        <f t="shared" si="35"/>
+        <v>0.12000000000000002</v>
+      </c>
+      <c r="AI29" s="11">
+        <f t="shared" si="35"/>
+        <v>0.12000000000000004</v>
+      </c>
+      <c r="AJ29" s="11">
+        <f t="shared" si="35"/>
+        <v>0.12000000000000005</v>
+      </c>
+      <c r="AK29" s="11">
+        <f t="shared" si="35"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="AL29" s="11">
+        <f t="shared" si="35"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="AM29" s="11">
+        <f t="shared" si="35"/>
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="AN29" s="11">
+        <f t="shared" si="35"/>
+        <v>0.12000000000000004</v>
+      </c>
+      <c r="AP29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AQ29" s="6">
+        <f>Main!D8</f>
+        <v>-17787</v>
+      </c>
+    </row>
+    <row r="30" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>55</v>
       </c>
       <c r="X30" s="11">
-        <f t="shared" ref="X30:AB30" si="14">X9/X5</f>
+        <f t="shared" ref="X30:AB30" si="36">X9/X5</f>
         <v>0.10854009228917275</v>
       </c>
       <c r="Y30" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.10751093305605676</v>
       </c>
       <c r="Z30" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.10900304277787722</v>
       </c>
       <c r="AA30" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.11176951988360814</v>
       </c>
       <c r="AB30" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.10859688327832946</v>
       </c>
       <c r="AC30" s="11">
         <f>AC9/AC5</f>
         <v>8.4089917373984774E-2</v>
       </c>
-    </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD30" s="11">
+        <f t="shared" ref="AD30:AN30" si="37">AD9/AD5</f>
+        <v>0.11166970600781023</v>
+      </c>
+      <c r="AE30" s="11">
+        <f t="shared" si="37"/>
+        <v>0.11169715809693399</v>
+      </c>
+      <c r="AF30" s="11">
+        <f t="shared" si="37"/>
+        <v>0.11172496807206032</v>
+      </c>
+      <c r="AG30" s="11">
+        <f t="shared" si="37"/>
+        <v>0.11175313752643963</v>
+      </c>
+      <c r="AH30" s="11">
+        <f t="shared" si="37"/>
+        <v>0.11178166795478273</v>
+      </c>
+      <c r="AI30" s="11">
+        <f t="shared" si="37"/>
+        <v>0.11181056074979222</v>
+      </c>
+      <c r="AJ30" s="11">
+        <f t="shared" si="37"/>
+        <v>0.11183981719868552</v>
+      </c>
+      <c r="AK30" s="11">
+        <f t="shared" si="37"/>
+        <v>0.11186943847971523</v>
+      </c>
+      <c r="AL30" s="11">
+        <f t="shared" si="37"/>
+        <v>0.11189942565868839</v>
+      </c>
+      <c r="AM30" s="11">
+        <f t="shared" si="37"/>
+        <v>0.11192977968549371</v>
+      </c>
+      <c r="AN30" s="11">
+        <f t="shared" si="37"/>
+        <v>0.111960501390638</v>
+      </c>
+      <c r="AP30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AQ30" s="6">
+        <f>AQ28+AQ29</f>
+        <v>83384.235861371635</v>
+      </c>
+    </row>
+    <row r="31" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>56</v>
       </c>
       <c r="X31" s="11">
-        <f t="shared" ref="X31:AB31" si="15">X14/X5</f>
+        <f t="shared" ref="X31:AB31" si="38">X14/X5</f>
         <v>0.14286430816558551</v>
       </c>
       <c r="Y31" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0.13217529588060797</v>
       </c>
       <c r="Z31" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0.13607481653839271</v>
       </c>
       <c r="AA31" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0.12651551891367604</v>
       </c>
       <c r="AB31" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0.12589720442201535</v>
       </c>
       <c r="AC31" s="11">
         <f>AC14/AC5</f>
         <v>9.8714862829553926E-2</v>
       </c>
-    </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD31" s="11">
+        <f t="shared" ref="AD31:AN31" si="39">AD14/AD5</f>
+        <v>0.12610382091750075</v>
+      </c>
+      <c r="AE31" s="11">
+        <f t="shared" si="39"/>
+        <v>0.12605933887319448</v>
+      </c>
+      <c r="AF31" s="11">
+        <f t="shared" si="39"/>
+        <v>0.12601427692762923</v>
+      </c>
+      <c r="AG31" s="11">
+        <f t="shared" si="39"/>
+        <v>0.12596863249917994</v>
+      </c>
+      <c r="AH31" s="11">
+        <f t="shared" si="39"/>
+        <v>0.12592240316588899</v>
+      </c>
+      <c r="AI31" s="11">
+        <f t="shared" si="39"/>
+        <v>0.12587558667108781</v>
+      </c>
+      <c r="AJ31" s="11">
+        <f t="shared" si="39"/>
+        <v>0.12582818092903056</v>
+      </c>
+      <c r="AK31" s="11">
+        <f t="shared" si="39"/>
+        <v>0.12578018403053445</v>
+      </c>
+      <c r="AL31" s="11">
+        <f t="shared" si="39"/>
+        <v>0.12573159424861663</v>
+      </c>
+      <c r="AM31" s="11">
+        <f t="shared" si="39"/>
+        <v>0.12568241004412339</v>
+      </c>
+      <c r="AN31" s="11">
+        <f t="shared" si="39"/>
+        <v>0.12563263007134079</v>
+      </c>
+      <c r="AP31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ31" s="4">
+        <f>AQ30/AN22</f>
+        <v>354.22360179002391</v>
+      </c>
+    </row>
+    <row r="32" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>45</v>
       </c>
       <c r="X32" s="11">
-        <f t="shared" ref="X32:AB32" si="16">X20/X19</f>
+        <f t="shared" ref="X32:AB32" si="40">X20/X19</f>
         <v>0.13962159922662615</v>
       </c>
       <c r="Y32" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="40"/>
         <v>0.16357012750455374</v>
       </c>
       <c r="Z32" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="40"/>
         <v>0.16357615894039734</v>
       </c>
       <c r="AA32" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="40"/>
         <v>0.14191616766467066</v>
       </c>
       <c r="AB32" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="40"/>
         <v>0.14546801679427018</v>
       </c>
       <c r="AC32" s="11">
         <f>AC20/AC19</f>
         <v>0.14212218649517686</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD32" s="11">
+        <f t="shared" ref="AD32:AN32" si="41">AD20/AD19</f>
+        <v>0.15</v>
+      </c>
+      <c r="AE32" s="11">
+        <f t="shared" si="41"/>
+        <v>0.15</v>
+      </c>
+      <c r="AF32" s="11">
+        <f t="shared" si="41"/>
+        <v>0.15</v>
+      </c>
+      <c r="AG32" s="11">
+        <f t="shared" si="41"/>
+        <v>0.15</v>
+      </c>
+      <c r="AH32" s="11">
+        <f t="shared" si="41"/>
+        <v>0.15</v>
+      </c>
+      <c r="AI32" s="11">
+        <f t="shared" si="41"/>
+        <v>0.15</v>
+      </c>
+      <c r="AJ32" s="11">
+        <f t="shared" si="41"/>
+        <v>0.15</v>
+      </c>
+      <c r="AK32" s="11">
+        <f t="shared" si="41"/>
+        <v>0.15</v>
+      </c>
+      <c r="AL32" s="11">
+        <f t="shared" si="41"/>
+        <v>0.15</v>
+      </c>
+      <c r="AM32" s="11">
+        <f t="shared" si="41"/>
+        <v>0.15</v>
+      </c>
+      <c r="AN32" s="11">
+        <f t="shared" si="41"/>
+        <v>0.15</v>
+      </c>
+      <c r="AP32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AQ32" s="4">
+        <f>Main!D3</f>
+        <v>462.5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>57</v>
       </c>
       <c r="X33" s="11">
-        <f t="shared" ref="X33:AB33" si="17">X21/X5</f>
+        <f t="shared" ref="X33:AB33" si="42">X21/X5</f>
         <v>0.10415970039456965</v>
       </c>
       <c r="Y33" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>0.10532432184470474</v>
       </c>
       <c r="Z33" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>9.4191873993198491E-2</v>
       </c>
       <c r="AA33" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>8.6869544131910767E-2</v>
       </c>
       <c r="AB33" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>0.1024107975314854</v>
       </c>
       <c r="AC33" s="11">
         <f>AC21/AC5</f>
         <v>7.5109440761229121E-2</v>
+      </c>
+      <c r="AD33" s="11">
+        <f t="shared" ref="AD33:AN33" si="43">AD21/AD5</f>
+        <v>9.4934357257880506E-2</v>
+      </c>
+      <c r="AE33" s="11">
+        <f t="shared" si="43"/>
+        <v>9.4936929635789785E-2</v>
+      </c>
+      <c r="AF33" s="11">
+        <f t="shared" si="43"/>
+        <v>9.493953554914461E-2</v>
+      </c>
+      <c r="AG33" s="11">
+        <f t="shared" si="43"/>
+        <v>9.494217514723978E-2</v>
+      </c>
+      <c r="AH33" s="11">
+        <f t="shared" si="43"/>
+        <v>9.4944848570135951E-2</v>
+      </c>
+      <c r="AI33" s="11">
+        <f t="shared" si="43"/>
+        <v>9.4947555948335247E-2</v>
+      </c>
+      <c r="AJ33" s="11">
+        <f t="shared" si="43"/>
+        <v>9.4950297402455294E-2</v>
+      </c>
+      <c r="AK33" s="11">
+        <f t="shared" si="43"/>
+        <v>9.495307304290361E-2</v>
+      </c>
+      <c r="AL33" s="11">
+        <f t="shared" si="43"/>
+        <v>9.4955882969550792E-2</v>
+      </c>
+      <c r="AM33" s="11">
+        <f t="shared" si="43"/>
+        <v>9.4958727271405516E-2</v>
+      </c>
+      <c r="AN33" s="11">
+        <f t="shared" si="43"/>
+        <v>9.4961606026289627E-2</v>
+      </c>
+      <c r="AP33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AQ33" s="12">
+        <f>AQ31/AQ32-1</f>
+        <v>-0.2341111312648132</v>
+      </c>
+    </row>
+    <row r="34" spans="2:43" x14ac:dyDescent="0.3">
+      <c r="AP34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ34" s="8" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/LMT.xlsx
+++ b/Financial Analysis/LMT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC494DBA-103B-4273-A2FA-4B446C6E796A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA73989-42A1-4F2F-96D1-DFF6648958AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4D34CE10-A2B1-43BA-A8EF-FB8FB8D75171}"/>
   </bookViews>
@@ -394,6 +394,56 @@
         <a:xfrm>
           <a:off x="18554700" y="7620"/>
           <a:ext cx="0" cy="8145780"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{559E68FC-5552-55D2-1470-DA65AB1929AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13075920" y="15240"/>
+          <a:ext cx="0" cy="6515100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -743,17 +793,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>462.5</v>
+        <v>421.42</v>
       </c>
       <c r="E3" s="5">
-        <v>45723</v>
+        <v>45862</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45869</v>
       </c>
       <c r="G3" s="5">
-        <v>45769</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
@@ -761,11 +811,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>235.4</f>
-        <v>235.4</v>
+        <f>233.5</f>
+        <v>233.5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
@@ -774,7 +824,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>108872.5</v>
+        <v>98401.57</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -819,7 +869,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>126659.5</v>
+        <v>116188.57</v>
       </c>
     </row>
   </sheetData>
@@ -957,6 +1007,38 @@
       <c r="B3" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="K3" s="6">
+        <v>12526</v>
+      </c>
+      <c r="L3" s="6">
+        <v>13758</v>
+      </c>
+      <c r="M3" s="6">
+        <v>14014</v>
+      </c>
+      <c r="N3" s="6">
+        <f>AB3-M3-L3-K3</f>
+        <v>15967</v>
+      </c>
+      <c r="O3" s="6">
+        <v>14196</v>
+      </c>
+      <c r="P3" s="6">
+        <v>15109</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>14472</v>
+      </c>
+      <c r="R3" s="6">
+        <f>AC3-Q3-P3-O3</f>
+        <v>15500</v>
+      </c>
+      <c r="S3" s="6">
+        <v>14936</v>
+      </c>
+      <c r="T3" s="6">
+        <v>15149</v>
+      </c>
       <c r="X3" s="6">
         <v>50053</v>
       </c>
@@ -980,50 +1062,82 @@
         <v>60462.54</v>
       </c>
       <c r="AE3" s="6">
-        <f>AD3*1.01</f>
-        <v>61067.165399999998</v>
+        <f>AD3*1.02</f>
+        <v>61671.790800000002</v>
       </c>
       <c r="AF3" s="6">
         <f t="shared" ref="AF3:AN3" si="0">AE3*1.01</f>
-        <v>61677.837053999996</v>
+        <v>62288.508708000001</v>
       </c>
       <c r="AG3" s="6">
         <f t="shared" si="0"/>
-        <v>62294.615424539996</v>
+        <v>62911.393795080003</v>
       </c>
       <c r="AH3" s="6">
         <f t="shared" si="0"/>
-        <v>62917.561578785397</v>
+        <v>63540.507733030805</v>
       </c>
       <c r="AI3" s="6">
         <f t="shared" si="0"/>
-        <v>63546.737194573252</v>
+        <v>64175.912810361115</v>
       </c>
       <c r="AJ3" s="6">
         <f t="shared" si="0"/>
-        <v>64182.204566518987</v>
+        <v>64817.671938464729</v>
       </c>
       <c r="AK3" s="6">
         <f t="shared" si="0"/>
-        <v>64824.026612184178</v>
+        <v>65465.848657849376</v>
       </c>
       <c r="AL3" s="6">
         <f t="shared" si="0"/>
-        <v>65472.266878306022</v>
+        <v>66120.507144427873</v>
       </c>
       <c r="AM3" s="6">
         <f t="shared" si="0"/>
-        <v>66126.989547089077</v>
+        <v>66781.712215872147</v>
       </c>
       <c r="AN3" s="6">
         <f t="shared" si="0"/>
-        <v>66788.259442559967</v>
+        <v>67449.529338030872</v>
       </c>
     </row>
     <row r="4" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="K4" s="6">
+        <v>2600</v>
+      </c>
+      <c r="L4" s="6">
+        <v>2935</v>
+      </c>
+      <c r="M4" s="6">
+        <v>2864</v>
+      </c>
+      <c r="N4" s="6">
+        <f>AB4-M4-L4-K4</f>
+        <v>2907</v>
+      </c>
+      <c r="O4" s="6">
+        <v>2999</v>
+      </c>
+      <c r="P4" s="6">
+        <v>3013</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>2632</v>
+      </c>
+      <c r="R4" s="6">
+        <f>AC4-Q4-P4-O4</f>
+        <v>3122</v>
+      </c>
+      <c r="S4" s="6">
+        <v>3027</v>
+      </c>
+      <c r="T4" s="6">
+        <v>3006</v>
+      </c>
       <c r="X4" s="6">
         <v>9759</v>
       </c>
@@ -1091,79 +1205,151 @@
       <c r="B5" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="K5" s="9">
+        <f t="shared" ref="K5" si="2">K3+K4</f>
+        <v>15126</v>
+      </c>
+      <c r="L5" s="9">
+        <f t="shared" ref="L5:M5" si="3">L3+L4</f>
+        <v>16693</v>
+      </c>
+      <c r="M5" s="9">
+        <f t="shared" si="3"/>
+        <v>16878</v>
+      </c>
+      <c r="N5" s="9">
+        <f t="shared" ref="N5" si="4">N3+N4</f>
+        <v>18874</v>
+      </c>
+      <c r="O5" s="9">
+        <f t="shared" ref="O5" si="5">O3+O4</f>
+        <v>17195</v>
+      </c>
+      <c r="P5" s="9">
+        <f t="shared" ref="P5:Q5" si="6">P3+P4</f>
+        <v>18122</v>
+      </c>
+      <c r="Q5" s="9">
+        <f t="shared" si="6"/>
+        <v>17104</v>
+      </c>
+      <c r="R5" s="9">
+        <f t="shared" ref="R5" si="7">R3+R4</f>
+        <v>18622</v>
+      </c>
+      <c r="S5" s="9">
+        <f t="shared" ref="S5:T5" si="8">S3+S4</f>
+        <v>17963</v>
+      </c>
+      <c r="T5" s="9">
+        <f t="shared" si="8"/>
+        <v>18155</v>
+      </c>
       <c r="X5" s="9">
-        <f t="shared" ref="X5:AN5" si="2">X3+X4</f>
+        <f t="shared" ref="X5:AN5" si="9">X3+X4</f>
         <v>59812</v>
       </c>
       <c r="Y5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>65398</v>
       </c>
       <c r="Z5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>67044</v>
       </c>
       <c r="AA5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>65984</v>
       </c>
       <c r="AB5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>67571</v>
       </c>
       <c r="AC5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>71043</v>
       </c>
       <c r="AD5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>72581.52</v>
       </c>
       <c r="AE5" s="9">
-        <f t="shared" si="2"/>
-        <v>73549.714800000002</v>
+        <f t="shared" si="9"/>
+        <v>74154.340200000006</v>
       </c>
       <c r="AF5" s="9">
-        <f t="shared" si="2"/>
-        <v>74534.86293599999</v>
+        <f t="shared" si="9"/>
+        <v>75145.534589999996</v>
       </c>
       <c r="AG5" s="9">
-        <f t="shared" si="2"/>
-        <v>75537.352082999991</v>
+        <f t="shared" si="9"/>
+        <v>76154.130453539998</v>
       </c>
       <c r="AH5" s="9">
-        <f t="shared" si="2"/>
-        <v>76557.580336999192</v>
+        <f t="shared" si="9"/>
+        <v>77180.5264912446</v>
       </c>
       <c r="AI5" s="9">
-        <f t="shared" si="2"/>
-        <v>77595.956515533471</v>
+        <f t="shared" si="9"/>
+        <v>78225.132131321327</v>
       </c>
       <c r="AJ5" s="9">
-        <f t="shared" si="2"/>
-        <v>78652.900467108004</v>
+        <f t="shared" si="9"/>
+        <v>79288.367839053753</v>
       </c>
       <c r="AK5" s="9">
-        <f t="shared" si="2"/>
-        <v>79728.843389790869</v>
+        <f t="shared" si="9"/>
+        <v>80370.665435456074</v>
       </c>
       <c r="AL5" s="9">
-        <f t="shared" si="2"/>
-        <v>80824.228159240913</v>
+        <f t="shared" si="9"/>
+        <v>81472.468425362764</v>
       </c>
       <c r="AM5" s="9">
-        <f t="shared" si="2"/>
-        <v>81939.509666452024</v>
+        <f t="shared" si="9"/>
+        <v>82594.232335235094</v>
       </c>
       <c r="AN5" s="9">
-        <f t="shared" si="2"/>
-        <v>83075.155165503791</v>
+        <f t="shared" si="9"/>
+        <v>83736.425060974696</v>
       </c>
     </row>
     <row r="6" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="K6" s="6">
+        <v>11151</v>
+      </c>
+      <c r="L6" s="6">
+        <v>12238</v>
+      </c>
+      <c r="M6" s="6">
+        <v>12571</v>
+      </c>
+      <c r="N6" s="6">
+        <f t="shared" ref="N6:N7" si="10">AB6-M6-L6-K6</f>
+        <v>14246</v>
+      </c>
+      <c r="O6" s="6">
+        <v>12884</v>
+      </c>
+      <c r="P6" s="6">
+        <v>13520</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>12964</v>
+      </c>
+      <c r="R6" s="6">
+        <f t="shared" ref="R6:R7" si="11">AC6-Q6-P6-O6</f>
+        <v>15484</v>
+      </c>
+      <c r="S6" s="6">
+        <v>13284</v>
+      </c>
+      <c r="T6" s="6">
+        <v>14469</v>
+      </c>
       <c r="X6" s="6">
         <v>44589</v>
       </c>
@@ -1187,50 +1373,82 @@
         <v>53811.660600000003</v>
       </c>
       <c r="AE6" s="6">
-        <f t="shared" ref="AE6:AN6" si="3">AE3*0.89</f>
-        <v>54349.777205999999</v>
+        <f t="shared" ref="AE6:AN6" si="12">AE3*0.89</f>
+        <v>54887.893812000002</v>
       </c>
       <c r="AF6" s="6">
-        <f t="shared" si="3"/>
-        <v>54893.274978059999</v>
+        <f t="shared" si="12"/>
+        <v>55436.772750119999</v>
       </c>
       <c r="AG6" s="6">
-        <f t="shared" si="3"/>
-        <v>55442.2077278406</v>
+        <f t="shared" si="12"/>
+        <v>55991.1404776212</v>
       </c>
       <c r="AH6" s="6">
-        <f t="shared" si="3"/>
-        <v>55996.629805119002</v>
+        <f t="shared" si="12"/>
+        <v>56551.05188239742</v>
       </c>
       <c r="AI6" s="6">
-        <f t="shared" si="3"/>
-        <v>56556.596103170195</v>
+        <f t="shared" si="12"/>
+        <v>57116.562401221396</v>
       </c>
       <c r="AJ6" s="6">
-        <f t="shared" si="3"/>
-        <v>57122.162064201897</v>
+        <f t="shared" si="12"/>
+        <v>57687.728025233613</v>
       </c>
       <c r="AK6" s="6">
-        <f t="shared" si="3"/>
-        <v>57693.383684843917</v>
+        <f t="shared" si="12"/>
+        <v>58264.605305485944</v>
       </c>
       <c r="AL6" s="6">
-        <f t="shared" si="3"/>
-        <v>58270.317521692363</v>
+        <f t="shared" si="12"/>
+        <v>58847.251358540809</v>
       </c>
       <c r="AM6" s="6">
-        <f t="shared" si="3"/>
-        <v>58853.020696909276</v>
+        <f t="shared" si="12"/>
+        <v>59435.723872126211</v>
       </c>
       <c r="AN6" s="6">
-        <f t="shared" si="3"/>
-        <v>59441.550903878371</v>
+        <f t="shared" si="12"/>
+        <v>60030.081110847474</v>
       </c>
     </row>
     <row r="7" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="K7" s="6">
+        <v>2284</v>
+      </c>
+      <c r="L7" s="6">
+        <v>2642</v>
+      </c>
+      <c r="M7" s="6">
+        <v>2510</v>
+      </c>
+      <c r="N7" s="6">
+        <f t="shared" si="10"/>
+        <v>2591</v>
+      </c>
+      <c r="O7" s="6">
+        <v>2603</v>
+      </c>
+      <c r="P7" s="6">
+        <v>2582</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>2272</v>
+      </c>
+      <c r="R7" s="6">
+        <f t="shared" si="11"/>
+        <v>2760</v>
+      </c>
+      <c r="S7" s="6">
+        <v>2640</v>
+      </c>
+      <c r="T7" s="6">
+        <v>3130</v>
+      </c>
       <c r="X7" s="6">
         <v>8731</v>
       </c>
@@ -1254,43 +1472,43 @@
         <v>10664.7024</v>
       </c>
       <c r="AE7" s="6">
-        <f t="shared" ref="AE7:AN7" si="4">AE4*0.88</f>
+        <f t="shared" ref="AE7:AN7" si="13">AE4*0.88</f>
         <v>10984.643472</v>
       </c>
       <c r="AF7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>11314.18277616</v>
       </c>
       <c r="AG7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>11653.6082594448</v>
       </c>
       <c r="AH7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>12003.216507228144</v>
       </c>
       <c r="AI7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>12363.313002444989</v>
       </c>
       <c r="AJ7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>12734.212392518339</v>
       </c>
       <c r="AK7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>13116.23876429389</v>
       </c>
       <c r="AL7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>13509.725927222707</v>
       </c>
       <c r="AM7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>13915.017705039389</v>
       </c>
       <c r="AN7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>14332.468236190571</v>
       </c>
     </row>
@@ -1298,152 +1516,249 @@
       <c r="B8" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="K8" s="6">
+        <f t="shared" ref="K8" si="14">K6+K7</f>
+        <v>13435</v>
+      </c>
+      <c r="L8" s="6">
+        <f t="shared" ref="L8:M8" si="15">L6+L7</f>
+        <v>14880</v>
+      </c>
+      <c r="M8" s="6">
+        <f t="shared" si="15"/>
+        <v>15081</v>
+      </c>
+      <c r="N8" s="6">
+        <f t="shared" ref="N8" si="16">N6+N7</f>
+        <v>16837</v>
+      </c>
+      <c r="O8" s="6">
+        <f t="shared" ref="O8" si="17">O6+O7</f>
+        <v>15487</v>
+      </c>
+      <c r="P8" s="6">
+        <f t="shared" ref="P8:Q8" si="18">P6+P7</f>
+        <v>16102</v>
+      </c>
+      <c r="Q8" s="6">
+        <f t="shared" si="18"/>
+        <v>15236</v>
+      </c>
+      <c r="R8" s="6">
+        <f t="shared" ref="R8" si="19">R6+R7</f>
+        <v>18244</v>
+      </c>
+      <c r="S8" s="6">
+        <f t="shared" ref="S8:T8" si="20">S6+S7</f>
+        <v>15924</v>
+      </c>
+      <c r="T8" s="6">
+        <f t="shared" si="20"/>
+        <v>17599</v>
+      </c>
       <c r="X8" s="6">
-        <f t="shared" ref="X8:AC8" si="5">X6+X7</f>
+        <f t="shared" ref="X8:AC8" si="21">X6+X7</f>
         <v>53320</v>
       </c>
       <c r="Y8" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="21"/>
         <v>58367</v>
       </c>
       <c r="Z8" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="21"/>
         <v>59736</v>
       </c>
       <c r="AA8" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="21"/>
         <v>58609</v>
       </c>
       <c r="AB8" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="21"/>
         <v>60233</v>
       </c>
       <c r="AC8" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="21"/>
         <v>65069</v>
       </c>
       <c r="AD8" s="6">
-        <f t="shared" ref="AD8:AN8" si="6">AD6+AD7</f>
+        <f t="shared" ref="AD8:AN8" si="22">AD6+AD7</f>
         <v>64476.363000000005</v>
       </c>
       <c r="AE8" s="6">
-        <f t="shared" si="6"/>
-        <v>65334.420677999995</v>
+        <f t="shared" si="22"/>
+        <v>65872.537284000005</v>
       </c>
       <c r="AF8" s="6">
-        <f t="shared" si="6"/>
-        <v>66207.457754219999</v>
+        <f t="shared" si="22"/>
+        <v>66750.955526279999</v>
       </c>
       <c r="AG8" s="6">
-        <f t="shared" si="6"/>
-        <v>67095.815987285401</v>
+        <f t="shared" si="22"/>
+        <v>67644.748737065995</v>
       </c>
       <c r="AH8" s="6">
-        <f t="shared" si="6"/>
-        <v>67999.846312347145</v>
+        <f t="shared" si="22"/>
+        <v>68554.268389625562</v>
       </c>
       <c r="AI8" s="6">
-        <f t="shared" si="6"/>
-        <v>68919.909105615181</v>
+        <f t="shared" si="22"/>
+        <v>69479.875403666389</v>
       </c>
       <c r="AJ8" s="6">
-        <f t="shared" si="6"/>
-        <v>69856.374456720238</v>
+        <f t="shared" si="22"/>
+        <v>70421.940417751946</v>
       </c>
       <c r="AK8" s="6">
-        <f t="shared" si="6"/>
-        <v>70809.622449137809</v>
+        <f t="shared" si="22"/>
+        <v>71380.844069779836</v>
       </c>
       <c r="AL8" s="6">
-        <f t="shared" si="6"/>
-        <v>71780.043448915065</v>
+        <f t="shared" si="22"/>
+        <v>72356.977285763511</v>
       </c>
       <c r="AM8" s="6">
-        <f t="shared" si="6"/>
-        <v>72768.038401948666</v>
+        <f t="shared" si="22"/>
+        <v>73350.741577165594</v>
       </c>
       <c r="AN8" s="6">
-        <f t="shared" si="6"/>
-        <v>73774.019140068936</v>
+        <f t="shared" si="22"/>
+        <v>74362.549347038046</v>
       </c>
     </row>
     <row r="9" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="K9" s="9">
+        <f t="shared" ref="K9" si="23">K5-K8</f>
+        <v>1691</v>
+      </c>
+      <c r="L9" s="9">
+        <f t="shared" ref="L9:M9" si="24">L5-L8</f>
+        <v>1813</v>
+      </c>
+      <c r="M9" s="9">
+        <f t="shared" si="24"/>
+        <v>1797</v>
+      </c>
+      <c r="N9" s="9">
+        <f t="shared" ref="N9" si="25">N5-N8</f>
+        <v>2037</v>
+      </c>
+      <c r="O9" s="9">
+        <f t="shared" ref="O9" si="26">O5-O8</f>
+        <v>1708</v>
+      </c>
+      <c r="P9" s="9">
+        <f t="shared" ref="P9:Q9" si="27">P5-P8</f>
+        <v>2020</v>
+      </c>
+      <c r="Q9" s="9">
+        <f t="shared" si="27"/>
+        <v>1868</v>
+      </c>
+      <c r="R9" s="9">
+        <f t="shared" ref="R9" si="28">R5-R8</f>
+        <v>378</v>
+      </c>
+      <c r="S9" s="9">
+        <f t="shared" ref="S9:T9" si="29">S5-S8</f>
+        <v>2039</v>
+      </c>
+      <c r="T9" s="9">
+        <f t="shared" si="29"/>
+        <v>556</v>
+      </c>
       <c r="X9" s="9">
-        <f t="shared" ref="X9:AC9" si="7">X5-X8</f>
+        <f t="shared" ref="X9:AC9" si="30">X5-X8</f>
         <v>6492</v>
       </c>
       <c r="Y9" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="30"/>
         <v>7031</v>
       </c>
       <c r="Z9" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="30"/>
         <v>7308</v>
       </c>
       <c r="AA9" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="30"/>
         <v>7375</v>
       </c>
       <c r="AB9" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="30"/>
         <v>7338</v>
       </c>
       <c r="AC9" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="30"/>
         <v>5974</v>
       </c>
       <c r="AD9" s="9">
-        <f t="shared" ref="AD9:AN9" si="8">AD5-AD8</f>
+        <f t="shared" ref="AD9:AN9" si="31">AD5-AD8</f>
         <v>8105.1569999999992</v>
       </c>
       <c r="AE9" s="9">
-        <f t="shared" si="8"/>
-        <v>8215.2941220000066</v>
+        <f t="shared" si="31"/>
+        <v>8281.8029160000006</v>
       </c>
       <c r="AF9" s="9">
-        <f t="shared" si="8"/>
-        <v>8327.4051817799918</v>
+        <f t="shared" si="31"/>
+        <v>8394.5790637199971</v>
       </c>
       <c r="AG9" s="9">
-        <f t="shared" si="8"/>
-        <v>8441.5360957145895</v>
+        <f t="shared" si="31"/>
+        <v>8509.381716474003</v>
       </c>
       <c r="AH9" s="9">
-        <f t="shared" si="8"/>
-        <v>8557.7340246520471</v>
+        <f t="shared" si="31"/>
+        <v>8626.2581016190379</v>
       </c>
       <c r="AI9" s="9">
-        <f t="shared" si="8"/>
-        <v>8676.0474099182902</v>
+        <f t="shared" si="31"/>
+        <v>8745.256727654938</v>
       </c>
       <c r="AJ9" s="9">
-        <f t="shared" si="8"/>
-        <v>8796.5260103877663</v>
+        <f t="shared" si="31"/>
+        <v>8866.427421301807</v>
       </c>
       <c r="AK9" s="9">
-        <f t="shared" si="8"/>
-        <v>8919.2209406530601</v>
+        <f t="shared" si="31"/>
+        <v>8989.8213656762382</v>
       </c>
       <c r="AL9" s="9">
-        <f t="shared" si="8"/>
-        <v>9044.1847103258478</v>
+        <f t="shared" si="31"/>
+        <v>9115.4911395992531</v>
       </c>
       <c r="AM9" s="9">
-        <f t="shared" si="8"/>
-        <v>9171.4712645033578</v>
+        <f t="shared" si="31"/>
+        <v>9243.4907580694999</v>
       </c>
       <c r="AN9" s="9">
-        <f t="shared" si="8"/>
-        <v>9301.1360254348547</v>
+        <f t="shared" si="31"/>
+        <v>9373.8757139366498</v>
       </c>
     </row>
     <row r="10" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6">
+        <v>87</v>
+      </c>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6">
+        <f t="shared" ref="R10:R12" si="32">AC10-Q10-P10-O10</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6">
+        <v>66</v>
+      </c>
       <c r="X10" s="6">
         <v>0</v>
       </c>
@@ -1467,43 +1782,43 @@
         <v>89.61</v>
       </c>
       <c r="AE10" s="6">
-        <f t="shared" ref="AE10:AN10" si="9">AD10*1.03</f>
+        <f t="shared" ref="AE10:AN10" si="33">AD10*1.03</f>
         <v>92.298299999999998</v>
       </c>
       <c r="AF10" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="33"/>
         <v>95.067249000000004</v>
       </c>
       <c r="AG10" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="33"/>
         <v>97.919266470000011</v>
       </c>
       <c r="AH10" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="33"/>
         <v>100.85684446410001</v>
       </c>
       <c r="AI10" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="33"/>
         <v>103.88254979802301</v>
       </c>
       <c r="AJ10" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="33"/>
         <v>106.9990262919637</v>
       </c>
       <c r="AK10" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="33"/>
         <v>110.20899708072261</v>
       </c>
       <c r="AL10" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="33"/>
         <v>113.51526699314429</v>
       </c>
       <c r="AM10" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="33"/>
         <v>116.92072500293862</v>
       </c>
       <c r="AN10" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="33"/>
         <v>120.42834675302679</v>
       </c>
     </row>
@@ -1511,6 +1826,38 @@
       <c r="B11" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="K11" s="6">
+        <v>-355</v>
+      </c>
+      <c r="L11" s="6">
+        <v>-277</v>
+      </c>
+      <c r="M11" s="6">
+        <v>-251</v>
+      </c>
+      <c r="N11" s="6">
+        <f t="shared" ref="N11:N12" si="34">AB11-M11-L11-K11</f>
+        <v>-350</v>
+      </c>
+      <c r="O11" s="6">
+        <v>-285</v>
+      </c>
+      <c r="P11" s="6">
+        <v>-197</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>-249</v>
+      </c>
+      <c r="R11" s="6">
+        <f t="shared" si="32"/>
+        <v>-312</v>
+      </c>
+      <c r="S11" s="6">
+        <v>-284</v>
+      </c>
+      <c r="T11" s="6">
+        <v>-244</v>
+      </c>
       <c r="X11" s="6">
         <v>-1875</v>
       </c>
@@ -1534,43 +1881,43 @@
         <v>-1053.43</v>
       </c>
       <c r="AE11" s="6">
-        <f t="shared" ref="AE11:AN11" si="10">AD11*1.01</f>
+        <f t="shared" ref="AE11:AN11" si="35">AD11*1.01</f>
         <v>-1063.9643000000001</v>
       </c>
       <c r="AF11" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="35"/>
         <v>-1074.6039430000001</v>
       </c>
       <c r="AG11" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="35"/>
         <v>-1085.3499824300002</v>
       </c>
       <c r="AH11" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="35"/>
         <v>-1096.2034822543003</v>
       </c>
       <c r="AI11" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="35"/>
         <v>-1107.1655170768433</v>
       </c>
       <c r="AJ11" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="35"/>
         <v>-1118.2371722476119</v>
       </c>
       <c r="AK11" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="35"/>
         <v>-1129.4195439700879</v>
       </c>
       <c r="AL11" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="35"/>
         <v>-1140.7137394097888</v>
       </c>
       <c r="AM11" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="35"/>
         <v>-1152.1208768038866</v>
       </c>
       <c r="AN11" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="35"/>
         <v>-1163.6420855719255</v>
       </c>
     </row>
@@ -1578,6 +1925,38 @@
       <c r="B12" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="K12" s="6">
+        <v>9</v>
+      </c>
+      <c r="L12" s="6">
+        <v>-45</v>
+      </c>
+      <c r="M12" s="6">
+        <v>6</v>
+      </c>
+      <c r="N12" s="6">
+        <f t="shared" si="34"/>
+        <v>2</v>
+      </c>
+      <c r="O12" s="6">
+        <v>-36</v>
+      </c>
+      <c r="P12" s="6">
+        <v>-18</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>-23</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="32"/>
+        <v>-6</v>
+      </c>
+      <c r="S12" s="6">
+        <v>-49</v>
+      </c>
+      <c r="T12" s="6">
+        <v>-14</v>
+      </c>
       <c r="X12" s="6">
         <v>-178</v>
       </c>
@@ -1601,43 +1980,43 @@
         <v>-83.83</v>
       </c>
       <c r="AE12" s="6">
-        <f t="shared" ref="AE12:AN12" si="11">AD12*1.01</f>
+        <f t="shared" ref="AE12:AN12" si="36">AD12*1.01</f>
         <v>-84.668300000000002</v>
       </c>
       <c r="AF12" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="36"/>
         <v>-85.514983000000001</v>
       </c>
       <c r="AG12" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="36"/>
         <v>-86.370132830000003</v>
       </c>
       <c r="AH12" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="36"/>
         <v>-87.233834158299999</v>
       </c>
       <c r="AI12" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="36"/>
         <v>-88.106172499883002</v>
       </c>
       <c r="AJ12" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="36"/>
         <v>-88.987234224881831</v>
       </c>
       <c r="AK12" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="36"/>
         <v>-89.877106567130653</v>
       </c>
       <c r="AL12" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="36"/>
         <v>-90.775877632801965</v>
       </c>
       <c r="AM12" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="36"/>
         <v>-91.683636409129988</v>
       </c>
       <c r="AN12" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="36"/>
         <v>-92.600472773221284</v>
       </c>
     </row>
@@ -1645,72 +2024,112 @@
       <c r="B13" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="K13" s="6">
+        <f t="shared" ref="K13" si="37">SUM(K10:K12)</f>
+        <v>-346</v>
+      </c>
+      <c r="L13" s="6">
+        <f t="shared" ref="L13:M13" si="38">SUM(L10:L12)</f>
+        <v>-322</v>
+      </c>
+      <c r="M13" s="6">
+        <f t="shared" si="38"/>
+        <v>-245</v>
+      </c>
+      <c r="N13" s="6">
+        <f t="shared" ref="N13" si="39">SUM(N10:N12)</f>
+        <v>-348</v>
+      </c>
+      <c r="O13" s="6">
+        <f t="shared" ref="O13" si="40">SUM(O10:O12)</f>
+        <v>-321</v>
+      </c>
+      <c r="P13" s="6">
+        <f t="shared" ref="P13" si="41">SUM(P10:P12)</f>
+        <v>-128</v>
+      </c>
+      <c r="Q13" s="6">
+        <f t="shared" ref="Q13:R13" si="42">SUM(Q10:Q12)</f>
+        <v>-272</v>
+      </c>
+      <c r="R13" s="6">
+        <f t="shared" si="42"/>
+        <v>-318</v>
+      </c>
+      <c r="S13" s="6">
+        <f t="shared" ref="S13:T13" si="43">SUM(S10:S12)</f>
+        <v>-333</v>
+      </c>
+      <c r="T13" s="6">
+        <f t="shared" si="43"/>
+        <v>-192</v>
+      </c>
       <c r="X13" s="6">
-        <f t="shared" ref="X13:AC13" si="12">SUM(X10:X12)</f>
+        <f t="shared" ref="X13:AC13" si="44">SUM(X10:X12)</f>
         <v>-2053</v>
       </c>
       <c r="Y13" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="44"/>
         <v>-1613</v>
       </c>
       <c r="Z13" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="44"/>
         <v>-1815</v>
       </c>
       <c r="AA13" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="44"/>
         <v>-973</v>
       </c>
       <c r="AB13" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="44"/>
         <v>-1169</v>
       </c>
       <c r="AC13" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="44"/>
         <v>-1039</v>
       </c>
       <c r="AD13" s="6">
-        <f t="shared" ref="AD13:AN13" si="13">SUM(AD10:AD12)</f>
+        <f t="shared" ref="AD13:AN13" si="45">SUM(AD10:AD12)</f>
         <v>-1047.6500000000001</v>
       </c>
       <c r="AE13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="45"/>
         <v>-1056.3343</v>
       </c>
       <c r="AF13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="45"/>
         <v>-1065.0516770000002</v>
       </c>
       <c r="AG13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="45"/>
         <v>-1073.8008487900001</v>
       </c>
       <c r="AH13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="45"/>
         <v>-1082.5804719485002</v>
       </c>
       <c r="AI13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="45"/>
         <v>-1091.3891397787033</v>
       </c>
       <c r="AJ13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="45"/>
         <v>-1100.22538018053</v>
       </c>
       <c r="AK13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="45"/>
         <v>-1109.0876534564959</v>
       </c>
       <c r="AL13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="45"/>
         <v>-1117.9743500494465</v>
       </c>
       <c r="AM13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="45"/>
         <v>-1126.8837882100781</v>
       </c>
       <c r="AN13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="45"/>
         <v>-1135.81421159212</v>
       </c>
     </row>
@@ -1718,79 +2137,151 @@
       <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
+      <c r="K14" s="9">
+        <f t="shared" ref="K14" si="46">K9-K13</f>
+        <v>2037</v>
+      </c>
+      <c r="L14" s="9">
+        <f t="shared" ref="L14:M14" si="47">L9-L13</f>
+        <v>2135</v>
+      </c>
+      <c r="M14" s="9">
+        <f t="shared" si="47"/>
+        <v>2042</v>
+      </c>
+      <c r="N14" s="9">
+        <f t="shared" ref="N14" si="48">N9-N13</f>
+        <v>2385</v>
+      </c>
+      <c r="O14" s="9">
+        <f t="shared" ref="O14" si="49">O9-O13</f>
+        <v>2029</v>
+      </c>
+      <c r="P14" s="9">
+        <f t="shared" ref="P14:Q14" si="50">P9-P13</f>
+        <v>2148</v>
+      </c>
+      <c r="Q14" s="9">
+        <f t="shared" si="50"/>
+        <v>2140</v>
+      </c>
+      <c r="R14" s="9">
+        <f t="shared" ref="R14" si="51">R9-R13</f>
+        <v>696</v>
+      </c>
+      <c r="S14" s="9">
+        <f t="shared" ref="S14:T14" si="52">S9-S13</f>
+        <v>2372</v>
+      </c>
+      <c r="T14" s="9">
+        <f t="shared" si="52"/>
+        <v>748</v>
+      </c>
       <c r="X14" s="9">
-        <f t="shared" ref="X14:AC14" si="14">X9-X13</f>
+        <f t="shared" ref="X14:AC14" si="53">X9-X13</f>
         <v>8545</v>
       </c>
       <c r="Y14" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="53"/>
         <v>8644</v>
       </c>
       <c r="Z14" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="53"/>
         <v>9123</v>
       </c>
       <c r="AA14" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="53"/>
         <v>8348</v>
       </c>
       <c r="AB14" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="53"/>
         <v>8507</v>
       </c>
       <c r="AC14" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="53"/>
         <v>7013</v>
       </c>
       <c r="AD14" s="9">
-        <f t="shared" ref="AD14:AN14" si="15">AD9-AD13</f>
+        <f t="shared" ref="AD14:AN14" si="54">AD9-AD13</f>
         <v>9152.8069999999989</v>
       </c>
       <c r="AE14" s="9">
-        <f t="shared" si="15"/>
-        <v>9271.628422000007</v>
+        <f t="shared" si="54"/>
+        <v>9338.137216000001</v>
       </c>
       <c r="AF14" s="9">
-        <f t="shared" si="15"/>
-        <v>9392.4568587799913</v>
+        <f t="shared" si="54"/>
+        <v>9459.6307407199965</v>
       </c>
       <c r="AG14" s="9">
-        <f t="shared" si="15"/>
-        <v>9515.3369445045901</v>
+        <f t="shared" si="54"/>
+        <v>9583.1825652640036</v>
       </c>
       <c r="AH14" s="9">
-        <f t="shared" si="15"/>
-        <v>9640.3144966005475</v>
+        <f t="shared" si="54"/>
+        <v>9708.8385735675383</v>
       </c>
       <c r="AI14" s="9">
-        <f t="shared" si="15"/>
-        <v>9767.4365496969931</v>
+        <f t="shared" si="54"/>
+        <v>9836.6458674336409</v>
       </c>
       <c r="AJ14" s="9">
-        <f t="shared" si="15"/>
-        <v>9896.7513905682972</v>
+        <f t="shared" si="54"/>
+        <v>9966.652801482338</v>
       </c>
       <c r="AK14" s="9">
-        <f t="shared" si="15"/>
-        <v>10028.308594109556</v>
+        <f t="shared" si="54"/>
+        <v>10098.909019132734</v>
       </c>
       <c r="AL14" s="9">
-        <f t="shared" si="15"/>
-        <v>10162.159060375294</v>
+        <f t="shared" si="54"/>
+        <v>10233.465489648699</v>
       </c>
       <c r="AM14" s="9">
-        <f t="shared" si="15"/>
-        <v>10298.355052713436</v>
+        <f t="shared" si="54"/>
+        <v>10370.374546279578</v>
       </c>
       <c r="AN14" s="9">
-        <f t="shared" si="15"/>
-        <v>10436.950237026975</v>
+        <f t="shared" si="54"/>
+        <v>10509.68992552877</v>
       </c>
     </row>
     <row r="15" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="K15" s="6">
+        <v>202</v>
+      </c>
+      <c r="L15" s="6">
+        <v>223</v>
+      </c>
+      <c r="M15" s="6">
+        <v>237</v>
+      </c>
+      <c r="N15" s="6">
+        <f t="shared" ref="N15:N17" si="55">AB15-M15-L15-K15</f>
+        <v>254</v>
+      </c>
+      <c r="O15" s="6">
+        <v>255</v>
+      </c>
+      <c r="P15" s="6">
+        <v>261</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>256</v>
+      </c>
+      <c r="R15" s="6">
+        <f t="shared" ref="R15:R17" si="56">AC15-Q15-P15-O15</f>
+        <v>264</v>
+      </c>
+      <c r="S15" s="6">
+        <v>268</v>
+      </c>
+      <c r="T15" s="6">
+        <v>274</v>
+      </c>
       <c r="X15" s="6">
         <v>653</v>
       </c>
@@ -1814,43 +2305,43 @@
         <v>1046.3599999999999</v>
       </c>
       <c r="AE15" s="6">
-        <f t="shared" ref="AE15:AN15" si="16">AD15*1.01</f>
+        <f t="shared" ref="AE15:AN15" si="57">AD15*1.01</f>
         <v>1056.8235999999999</v>
       </c>
       <c r="AF15" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="57"/>
         <v>1067.391836</v>
       </c>
       <c r="AG15" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="57"/>
         <v>1078.06575436</v>
       </c>
       <c r="AH15" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="57"/>
         <v>1088.8464119036</v>
       </c>
       <c r="AI15" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="57"/>
         <v>1099.7348760226359</v>
       </c>
       <c r="AJ15" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="57"/>
         <v>1110.7322247828622</v>
       </c>
       <c r="AK15" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="57"/>
         <v>1121.8395470306909</v>
       </c>
       <c r="AL15" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="57"/>
         <v>1133.0579425009978</v>
       </c>
       <c r="AM15" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="57"/>
         <v>1144.3885219260078</v>
       </c>
       <c r="AN15" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="57"/>
         <v>1155.8324071452678</v>
       </c>
     </row>
@@ -1858,6 +2349,38 @@
       <c r="B16" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="K16" s="6">
+        <v>-110</v>
+      </c>
+      <c r="L16" s="6">
+        <v>-111</v>
+      </c>
+      <c r="M16" s="6">
+        <v>-111</v>
+      </c>
+      <c r="N16" s="6">
+        <f t="shared" si="55"/>
+        <v>-111</v>
+      </c>
+      <c r="O16" s="6">
+        <v>-16</v>
+      </c>
+      <c r="P16" s="6">
+        <v>-15</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>-16</v>
+      </c>
+      <c r="R16" s="6">
+        <f t="shared" si="56"/>
+        <v>-15</v>
+      </c>
+      <c r="S16" s="6">
+        <v>98</v>
+      </c>
+      <c r="T16" s="6">
+        <v>99</v>
+      </c>
       <c r="X16" s="6">
         <v>577</v>
       </c>
@@ -1914,6 +2437,38 @@
       <c r="B17" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="K17" s="6">
+        <v>-49</v>
+      </c>
+      <c r="L17" s="6">
+        <v>17</v>
+      </c>
+      <c r="M17" s="6">
+        <v>-37</v>
+      </c>
+      <c r="N17" s="6">
+        <f t="shared" si="55"/>
+        <v>5</v>
+      </c>
+      <c r="O17" s="6">
+        <v>-45</v>
+      </c>
+      <c r="P17" s="6">
+        <v>-46</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>-18</v>
+      </c>
+      <c r="R17" s="6">
+        <f t="shared" si="56"/>
+        <v>-72</v>
+      </c>
+      <c r="S17" s="6">
+        <v>-30</v>
+      </c>
+      <c r="T17" s="6">
+        <v>-42</v>
+      </c>
       <c r="X17" s="6">
         <v>74</v>
       </c>
@@ -1970,72 +2525,112 @@
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="K18" s="6">
+        <f t="shared" ref="K18" si="58">SUM(K15:K17)</f>
+        <v>43</v>
+      </c>
+      <c r="L18" s="6">
+        <f t="shared" ref="L18:M18" si="59">SUM(L15:L17)</f>
+        <v>129</v>
+      </c>
+      <c r="M18" s="6">
+        <f t="shared" si="59"/>
+        <v>89</v>
+      </c>
+      <c r="N18" s="6">
+        <f t="shared" ref="N18" si="60">SUM(N15:N17)</f>
+        <v>148</v>
+      </c>
+      <c r="O18" s="6">
+        <f t="shared" ref="O18" si="61">SUM(O15:O17)</f>
+        <v>194</v>
+      </c>
+      <c r="P18" s="6">
+        <f t="shared" ref="P18" si="62">SUM(P15:P17)</f>
+        <v>200</v>
+      </c>
+      <c r="Q18" s="6">
+        <f t="shared" ref="Q18:R18" si="63">SUM(Q15:Q17)</f>
+        <v>222</v>
+      </c>
+      <c r="R18" s="6">
+        <f t="shared" si="63"/>
+        <v>177</v>
+      </c>
+      <c r="S18" s="6">
+        <f t="shared" ref="S18:T18" si="64">SUM(S15:S17)</f>
+        <v>336</v>
+      </c>
+      <c r="T18" s="6">
+        <f t="shared" si="64"/>
+        <v>331</v>
+      </c>
       <c r="X18" s="6">
-        <f t="shared" ref="X18:AC18" si="17">SUM(X15:X17)</f>
+        <f t="shared" ref="X18:AC18" si="65">SUM(X15:X17)</f>
         <v>1304</v>
       </c>
       <c r="Y18" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="65"/>
         <v>409</v>
       </c>
       <c r="Z18" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="65"/>
         <v>1573</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="65"/>
         <v>1668</v>
       </c>
       <c r="AB18" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="65"/>
         <v>409</v>
       </c>
       <c r="AC18" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="65"/>
         <v>793</v>
       </c>
       <c r="AD18" s="6">
-        <f t="shared" ref="AD18:AN18" si="18">SUM(AD15:AD17)</f>
+        <f t="shared" ref="AD18:AN18" si="66">SUM(AD15:AD17)</f>
         <v>1046.3599999999999</v>
       </c>
       <c r="AE18" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="66"/>
         <v>1056.8235999999999</v>
       </c>
       <c r="AF18" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="66"/>
         <v>1067.391836</v>
       </c>
       <c r="AG18" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="66"/>
         <v>1078.06575436</v>
       </c>
       <c r="AH18" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="66"/>
         <v>1088.8464119036</v>
       </c>
       <c r="AI18" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="66"/>
         <v>1099.7348760226359</v>
       </c>
       <c r="AJ18" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="66"/>
         <v>1110.7322247828622</v>
       </c>
       <c r="AK18" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="66"/>
         <v>1121.8395470306909</v>
       </c>
       <c r="AL18" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="66"/>
         <v>1133.0579425009978</v>
       </c>
       <c r="AM18" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="66"/>
         <v>1144.3885219260078</v>
       </c>
       <c r="AN18" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="66"/>
         <v>1155.8324071452678</v>
       </c>
     </row>
@@ -2043,79 +2638,151 @@
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="K19" s="9">
+        <f t="shared" ref="K19" si="67">K14-K18</f>
+        <v>1994</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" ref="L19:M19" si="68">L14-L18</f>
+        <v>2006</v>
+      </c>
+      <c r="M19" s="9">
+        <f t="shared" si="68"/>
+        <v>1953</v>
+      </c>
+      <c r="N19" s="9">
+        <f t="shared" ref="N19" si="69">N14-N18</f>
+        <v>2237</v>
+      </c>
+      <c r="O19" s="9">
+        <f t="shared" ref="O19" si="70">O14-O18</f>
+        <v>1835</v>
+      </c>
+      <c r="P19" s="9">
+        <f t="shared" ref="P19:Q19" si="71">P14-P18</f>
+        <v>1948</v>
+      </c>
+      <c r="Q19" s="9">
+        <f t="shared" si="71"/>
+        <v>1918</v>
+      </c>
+      <c r="R19" s="9">
+        <f t="shared" ref="R19" si="72">R14-R18</f>
+        <v>519</v>
+      </c>
+      <c r="S19" s="9">
+        <f t="shared" ref="S19:T19" si="73">S14-S18</f>
+        <v>2036</v>
+      </c>
+      <c r="T19" s="9">
+        <f t="shared" si="73"/>
+        <v>417</v>
+      </c>
       <c r="X19" s="9">
-        <f t="shared" ref="X19:AC19" si="19">X14-X18</f>
+        <f t="shared" ref="X19:AC19" si="74">X14-X18</f>
         <v>7241</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="74"/>
         <v>8235</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="74"/>
         <v>7550</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="74"/>
         <v>6680</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="74"/>
         <v>8098</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="74"/>
         <v>6220</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" ref="AD19:AN19" si="20">AD14-AD18</f>
+        <f t="shared" ref="AD19:AN19" si="75">AD14-AD18</f>
         <v>8106.4469999999992</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="20"/>
-        <v>8214.8048220000073</v>
+        <f t="shared" si="75"/>
+        <v>8281.3136160000013</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" si="20"/>
-        <v>8325.0650227799906</v>
+        <f t="shared" si="75"/>
+        <v>8392.2389047199958</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="20"/>
-        <v>8437.2711901445909</v>
+        <f t="shared" si="75"/>
+        <v>8505.1168109040045</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" si="20"/>
-        <v>8551.4680846969477</v>
+        <f t="shared" si="75"/>
+        <v>8619.9921616639385</v>
       </c>
       <c r="AI19" s="9">
-        <f t="shared" si="20"/>
-        <v>8667.7016736743572</v>
+        <f t="shared" si="75"/>
+        <v>8736.9109914110049</v>
       </c>
       <c r="AJ19" s="9">
-        <f t="shared" si="20"/>
-        <v>8786.0191657854357</v>
+        <f t="shared" si="75"/>
+        <v>8855.9205766994764</v>
       </c>
       <c r="AK19" s="9">
-        <f t="shared" si="20"/>
-        <v>8906.4690470788646</v>
+        <f t="shared" si="75"/>
+        <v>8977.0694721020427</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="20"/>
-        <v>9029.1011178742956</v>
+        <f t="shared" si="75"/>
+        <v>9100.4075471477008</v>
       </c>
       <c r="AM19" s="9">
-        <f t="shared" si="20"/>
-        <v>9153.9665307874275</v>
+        <f t="shared" si="75"/>
+        <v>9225.9860243535695</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" si="20"/>
-        <v>9281.1178298817067</v>
+        <f t="shared" si="75"/>
+        <v>9353.8575183835019</v>
       </c>
     </row>
     <row r="20" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="K20" s="6">
+        <v>305</v>
+      </c>
+      <c r="L20" s="6">
+        <v>325</v>
+      </c>
+      <c r="M20" s="6">
+        <v>269</v>
+      </c>
+      <c r="N20" s="6">
+        <f>AB20-M20-L20-K20</f>
+        <v>279</v>
+      </c>
+      <c r="O20" s="6">
+        <v>290</v>
+      </c>
+      <c r="P20" s="6">
+        <v>307</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>295</v>
+      </c>
+      <c r="R20" s="6">
+        <f>AC20-Q20-P20-O20</f>
+        <v>-8</v>
+      </c>
+      <c r="S20" s="6">
+        <v>324</v>
+      </c>
+      <c r="T20" s="6">
+        <v>75</v>
+      </c>
       <c r="X20" s="6">
         <v>1011</v>
       </c>
@@ -2139,676 +2806,822 @@
         <v>1215.9670499999997</v>
       </c>
       <c r="AE20" s="6">
-        <f t="shared" ref="AE20:AN20" si="21">AE19*0.15</f>
-        <v>1232.2207233000011</v>
+        <f t="shared" ref="AE20:AN20" si="76">AE19*0.15</f>
+        <v>1242.1970424000001</v>
       </c>
       <c r="AF20" s="6">
-        <f t="shared" si="21"/>
-        <v>1248.7597534169986</v>
+        <f t="shared" si="76"/>
+        <v>1258.8358357079994</v>
       </c>
       <c r="AG20" s="6">
-        <f t="shared" si="21"/>
-        <v>1265.5906785216887</v>
+        <f t="shared" si="76"/>
+        <v>1275.7675216356006</v>
       </c>
       <c r="AH20" s="6">
-        <f t="shared" si="21"/>
-        <v>1282.7202127045421</v>
+        <f t="shared" si="76"/>
+        <v>1292.9988242495908</v>
       </c>
       <c r="AI20" s="6">
-        <f t="shared" si="21"/>
-        <v>1300.1552510511535</v>
+        <f t="shared" si="76"/>
+        <v>1310.5366487116507</v>
       </c>
       <c r="AJ20" s="6">
-        <f t="shared" si="21"/>
-        <v>1317.9028748678154</v>
+        <f t="shared" si="76"/>
+        <v>1328.3880865049214</v>
       </c>
       <c r="AK20" s="6">
-        <f t="shared" si="21"/>
-        <v>1335.9703570618296</v>
+        <f t="shared" si="76"/>
+        <v>1346.5604208153063</v>
       </c>
       <c r="AL20" s="6">
-        <f t="shared" si="21"/>
-        <v>1354.3651676811444</v>
+        <f t="shared" si="76"/>
+        <v>1365.061132072155</v>
       </c>
       <c r="AM20" s="6">
-        <f t="shared" si="21"/>
-        <v>1373.0949796181142</v>
+        <f t="shared" si="76"/>
+        <v>1383.8979036530354</v>
       </c>
       <c r="AN20" s="6">
-        <f t="shared" si="21"/>
-        <v>1392.167674482256</v>
+        <f t="shared" si="76"/>
+        <v>1403.0786277575253</v>
       </c>
     </row>
     <row r="21" spans="2:138" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="K21" s="9">
+        <f t="shared" ref="K21" si="77">K19-K20</f>
+        <v>1689</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" ref="L21:M21" si="78">L19-L20</f>
+        <v>1681</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="78"/>
+        <v>1684</v>
+      </c>
+      <c r="N21" s="9">
+        <f t="shared" ref="N21" si="79">N19-N20</f>
+        <v>1958</v>
+      </c>
+      <c r="O21" s="9">
+        <f t="shared" ref="O21" si="80">O19-O20</f>
+        <v>1545</v>
+      </c>
+      <c r="P21" s="9">
+        <f t="shared" ref="P21:Q21" si="81">P19-P20</f>
+        <v>1641</v>
+      </c>
+      <c r="Q21" s="9">
+        <f t="shared" si="81"/>
+        <v>1623</v>
+      </c>
+      <c r="R21" s="9">
+        <f t="shared" ref="R21" si="82">R19-R20</f>
+        <v>527</v>
+      </c>
+      <c r="S21" s="9">
+        <f t="shared" ref="S21:T21" si="83">S19-S20</f>
+        <v>1712</v>
+      </c>
+      <c r="T21" s="9">
+        <f t="shared" si="83"/>
+        <v>342</v>
+      </c>
       <c r="X21" s="9">
-        <f t="shared" ref="X21:AC21" si="22">X19-X20</f>
+        <f t="shared" ref="X21:AC21" si="84">X19-X20</f>
         <v>6230</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="84"/>
         <v>6888</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="84"/>
         <v>6315</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="84"/>
         <v>5732</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="84"/>
         <v>6920</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="84"/>
         <v>5336</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" ref="AD21:AN21" si="23">AD19-AD20</f>
+        <f t="shared" ref="AD21:AN21" si="85">AD19-AD20</f>
         <v>6890.479949999999</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="23"/>
-        <v>6982.5840987000065</v>
+        <f t="shared" si="85"/>
+        <v>7039.1165736000012</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="23"/>
-        <v>7076.3052693629925</v>
+        <f t="shared" si="85"/>
+        <v>7133.4030690119962</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="23"/>
-        <v>7171.6805116229025</v>
+        <f t="shared" si="85"/>
+        <v>7229.3492892684044</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="23"/>
-        <v>7268.7478719924056</v>
+        <f t="shared" si="85"/>
+        <v>7326.9933374143475</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="23"/>
-        <v>7367.5464226232034</v>
+        <f t="shared" si="85"/>
+        <v>7426.3743426993542</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="23"/>
-        <v>7468.1162909176201</v>
+        <f t="shared" si="85"/>
+        <v>7527.5324901945551</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="23"/>
-        <v>7570.4986900170352</v>
+        <f t="shared" si="85"/>
+        <v>7630.5090512867364</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="23"/>
-        <v>7674.7359501931514</v>
+        <f t="shared" si="85"/>
+        <v>7735.3464150755462</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="23"/>
-        <v>7780.8715511693135</v>
+        <f t="shared" si="85"/>
+        <v>7842.0881207005341</v>
       </c>
       <c r="AN21" s="9">
-        <f t="shared" si="23"/>
-        <v>7888.9501553994505</v>
+        <f t="shared" si="85"/>
+        <v>7950.7788906259766</v>
       </c>
       <c r="AO21" s="3">
         <f>AN21*(1+$AQ$26)</f>
-        <v>7810.0606538454558</v>
+        <v>7871.2711017197171</v>
       </c>
       <c r="AP21" s="3">
-        <f t="shared" ref="AP21:DA21" si="24">AO21*(1+$AQ$26)</f>
-        <v>7731.9600473070013</v>
+        <f t="shared" ref="AP21:DA21" si="86">AO21*(1+$AQ$26)</f>
+        <v>7792.5583907025202</v>
       </c>
       <c r="AQ21" s="3">
-        <f t="shared" si="24"/>
-        <v>7654.6404468339315</v>
+        <f t="shared" si="86"/>
+        <v>7714.6328067954946</v>
       </c>
       <c r="AR21" s="3">
-        <f t="shared" si="24"/>
-        <v>7578.094042365592</v>
+        <f t="shared" si="86"/>
+        <v>7637.4864787275392</v>
       </c>
       <c r="AS21" s="3">
-        <f t="shared" si="24"/>
-        <v>7502.3131019419361</v>
+        <f t="shared" si="86"/>
+        <v>7561.1116139402639</v>
       </c>
       <c r="AT21" s="3">
-        <f t="shared" si="24"/>
-        <v>7427.2899709225167</v>
+        <f t="shared" si="86"/>
+        <v>7485.500497800861</v>
       </c>
       <c r="AU21" s="3">
-        <f t="shared" si="24"/>
-        <v>7353.0170712132913</v>
+        <f t="shared" si="86"/>
+        <v>7410.6454928228522</v>
       </c>
       <c r="AV21" s="3">
-        <f t="shared" si="24"/>
-        <v>7279.4869005011587</v>
+        <f t="shared" si="86"/>
+        <v>7336.539037894624</v>
       </c>
       <c r="AW21" s="3">
-        <f t="shared" si="24"/>
-        <v>7206.6920314961471</v>
+        <f t="shared" si="86"/>
+        <v>7263.1736475156777</v>
       </c>
       <c r="AX21" s="3">
-        <f t="shared" si="24"/>
-        <v>7134.6251111811853</v>
+        <f t="shared" si="86"/>
+        <v>7190.541911040521</v>
       </c>
       <c r="AY21" s="3">
-        <f t="shared" si="24"/>
-        <v>7063.278860069373</v>
+        <f t="shared" si="86"/>
+        <v>7118.6364919301159</v>
       </c>
       <c r="AZ21" s="3">
-        <f t="shared" si="24"/>
-        <v>6992.6460714686791</v>
+        <f t="shared" si="86"/>
+        <v>7047.4501270108149</v>
       </c>
       <c r="BA21" s="3">
-        <f t="shared" si="24"/>
-        <v>6922.7196107539921</v>
+        <f t="shared" si="86"/>
+        <v>6976.9756257407071</v>
       </c>
       <c r="BB21" s="3">
-        <f t="shared" si="24"/>
-        <v>6853.4924146464518</v>
+        <f t="shared" si="86"/>
+        <v>6907.2058694833004</v>
       </c>
       <c r="BC21" s="3">
-        <f t="shared" si="24"/>
-        <v>6784.9574904999872</v>
+        <f t="shared" si="86"/>
+        <v>6838.1338107884676</v>
       </c>
       <c r="BD21" s="3">
-        <f t="shared" si="24"/>
-        <v>6717.1079155949874</v>
+        <f t="shared" si="86"/>
+        <v>6769.7524726805832</v>
       </c>
       <c r="BE21" s="3">
-        <f t="shared" si="24"/>
-        <v>6649.9368364390375</v>
+        <f t="shared" si="86"/>
+        <v>6702.0549479537776</v>
       </c>
       <c r="BF21" s="3">
-        <f t="shared" si="24"/>
-        <v>6583.4374680746469</v>
+        <f t="shared" si="86"/>
+        <v>6635.0343984742394</v>
       </c>
       <c r="BG21" s="3">
-        <f t="shared" si="24"/>
-        <v>6517.6030933939001</v>
+        <f t="shared" si="86"/>
+        <v>6568.6840544894967</v>
       </c>
       <c r="BH21" s="3">
-        <f t="shared" si="24"/>
-        <v>6452.4270624599612</v>
+        <f t="shared" si="86"/>
+        <v>6502.9972139446018</v>
       </c>
       <c r="BI21" s="3">
-        <f t="shared" si="24"/>
-        <v>6387.9027918353613</v>
+        <f t="shared" si="86"/>
+        <v>6437.9672418051559</v>
       </c>
       <c r="BJ21" s="3">
-        <f t="shared" si="24"/>
-        <v>6324.0237639170073</v>
+        <f t="shared" si="86"/>
+        <v>6373.5875693871039</v>
       </c>
       <c r="BK21" s="3">
-        <f t="shared" si="24"/>
-        <v>6260.7835262778372</v>
+        <f t="shared" si="86"/>
+        <v>6309.8516936932328</v>
       </c>
       <c r="BL21" s="3">
-        <f t="shared" si="24"/>
-        <v>6198.1756910150589</v>
+        <f t="shared" si="86"/>
+        <v>6246.7531767563005</v>
       </c>
       <c r="BM21" s="3">
-        <f t="shared" si="24"/>
-        <v>6136.1939341049083</v>
+        <f t="shared" si="86"/>
+        <v>6184.2856449887377</v>
       </c>
       <c r="BN21" s="3">
-        <f t="shared" si="24"/>
-        <v>6074.8319947638593</v>
+        <f t="shared" si="86"/>
+        <v>6122.4427885388504</v>
       </c>
       <c r="BO21" s="3">
-        <f t="shared" si="24"/>
-        <v>6014.083674816221</v>
+        <f t="shared" si="86"/>
+        <v>6061.2183606534618</v>
       </c>
       <c r="BP21" s="3">
-        <f t="shared" si="24"/>
-        <v>5953.9428380680583</v>
+        <f t="shared" si="86"/>
+        <v>6000.6061770469269</v>
       </c>
       <c r="BQ21" s="3">
-        <f t="shared" si="24"/>
-        <v>5894.4034096873775</v>
+        <f t="shared" si="86"/>
+        <v>5940.6001152764575</v>
       </c>
       <c r="BR21" s="3">
-        <f t="shared" si="24"/>
-        <v>5835.4593755905034</v>
+        <f t="shared" si="86"/>
+        <v>5881.194114123693</v>
       </c>
       <c r="BS21" s="3">
-        <f t="shared" si="24"/>
-        <v>5777.1047818345987</v>
+        <f t="shared" si="86"/>
+        <v>5822.3821729824558</v>
       </c>
       <c r="BT21" s="3">
-        <f t="shared" si="24"/>
-        <v>5719.3337340162525</v>
+        <f t="shared" si="86"/>
+        <v>5764.1583512526313</v>
       </c>
       <c r="BU21" s="3">
-        <f t="shared" si="24"/>
-        <v>5662.1403966760899</v>
+        <f t="shared" si="86"/>
+        <v>5706.516767740105</v>
       </c>
       <c r="BV21" s="3">
-        <f t="shared" si="24"/>
-        <v>5605.5189927093288</v>
+        <f t="shared" si="86"/>
+        <v>5649.4516000627036</v>
       </c>
       <c r="BW21" s="3">
-        <f t="shared" si="24"/>
-        <v>5549.4638027822357</v>
+        <f t="shared" si="86"/>
+        <v>5592.9570840620763</v>
       </c>
       <c r="BX21" s="3">
-        <f t="shared" si="24"/>
-        <v>5493.9691647544132</v>
+        <f t="shared" si="86"/>
+        <v>5537.0275132214556</v>
       </c>
       <c r="BY21" s="3">
-        <f t="shared" si="24"/>
-        <v>5439.0294731068689</v>
+        <f t="shared" si="86"/>
+        <v>5481.6572380892412</v>
       </c>
       <c r="BZ21" s="3">
-        <f t="shared" si="24"/>
-        <v>5384.6391783757999</v>
+        <f t="shared" si="86"/>
+        <v>5426.8406657083488</v>
       </c>
       <c r="CA21" s="3">
-        <f t="shared" si="24"/>
-        <v>5330.7927865920419</v>
+        <f t="shared" si="86"/>
+        <v>5372.5722590512651</v>
       </c>
       <c r="CB21" s="3">
-        <f t="shared" si="24"/>
-        <v>5277.4848587261213</v>
+        <f t="shared" si="86"/>
+        <v>5318.8465364607528</v>
       </c>
       <c r="CC21" s="3">
-        <f t="shared" si="24"/>
-        <v>5224.7100101388596</v>
+        <f t="shared" si="86"/>
+        <v>5265.6580710961452</v>
       </c>
       <c r="CD21" s="3">
-        <f t="shared" si="24"/>
-        <v>5172.4629100374714</v>
+        <f t="shared" si="86"/>
+        <v>5213.0014903851834</v>
       </c>
       <c r="CE21" s="3">
-        <f t="shared" si="24"/>
-        <v>5120.7382809370965</v>
+        <f t="shared" si="86"/>
+        <v>5160.8714754813318</v>
       </c>
       <c r="CF21" s="3">
-        <f t="shared" si="24"/>
-        <v>5069.5308981277258</v>
+        <f t="shared" si="86"/>
+        <v>5109.2627607265185</v>
       </c>
       <c r="CG21" s="3">
-        <f t="shared" si="24"/>
-        <v>5018.8355891464489</v>
+        <f t="shared" si="86"/>
+        <v>5058.1701331192535</v>
       </c>
       <c r="CH21" s="3">
-        <f t="shared" si="24"/>
-        <v>4968.6472332549847</v>
+        <f t="shared" si="86"/>
+        <v>5007.5884317880609</v>
       </c>
       <c r="CI21" s="3">
-        <f t="shared" si="24"/>
-        <v>4918.9607609224349</v>
+        <f t="shared" si="86"/>
+        <v>4957.5125474701799</v>
       </c>
       <c r="CJ21" s="3">
-        <f t="shared" si="24"/>
-        <v>4869.7711533132106</v>
+        <f t="shared" si="86"/>
+        <v>4907.937421995478</v>
       </c>
       <c r="CK21" s="3">
-        <f t="shared" si="24"/>
-        <v>4821.0734417800786</v>
+        <f t="shared" si="86"/>
+        <v>4858.8580477755231</v>
       </c>
       <c r="CL21" s="3">
-        <f t="shared" si="24"/>
-        <v>4772.8627073622774</v>
+        <f t="shared" si="86"/>
+        <v>4810.2694672977677</v>
       </c>
       <c r="CM21" s="3">
-        <f t="shared" si="24"/>
-        <v>4725.1340802886543</v>
+        <f t="shared" si="86"/>
+        <v>4762.1667726247897</v>
       </c>
       <c r="CN21" s="3">
-        <f t="shared" si="24"/>
-        <v>4677.8827394857681</v>
+        <f t="shared" si="86"/>
+        <v>4714.5451048985415</v>
       </c>
       <c r="CO21" s="3">
-        <f t="shared" si="24"/>
-        <v>4631.1039120909099</v>
+        <f t="shared" si="86"/>
+        <v>4667.3996538495558</v>
       </c>
       <c r="CP21" s="3">
-        <f t="shared" si="24"/>
-        <v>4584.7928729700006</v>
+        <f t="shared" si="86"/>
+        <v>4620.7256573110599</v>
       </c>
       <c r="CQ21" s="3">
-        <f t="shared" si="24"/>
-        <v>4538.9449442403002</v>
+        <f t="shared" si="86"/>
+        <v>4574.5184007379494</v>
       </c>
       <c r="CR21" s="3">
-        <f t="shared" si="24"/>
-        <v>4493.5554947978972</v>
+        <f t="shared" si="86"/>
+        <v>4528.7732167305694</v>
       </c>
       <c r="CS21" s="3">
-        <f t="shared" si="24"/>
-        <v>4448.6199398499184</v>
+        <f t="shared" si="86"/>
+        <v>4483.4854845632635</v>
       </c>
       <c r="CT21" s="3">
-        <f t="shared" si="24"/>
-        <v>4404.1337404514188</v>
+        <f t="shared" si="86"/>
+        <v>4438.6506297176311</v>
       </c>
       <c r="CU21" s="3">
-        <f t="shared" si="24"/>
-        <v>4360.092403046905</v>
+        <f t="shared" si="86"/>
+        <v>4394.2641234204548</v>
       </c>
       <c r="CV21" s="3">
-        <f t="shared" si="24"/>
-        <v>4316.4914790164357</v>
+        <f t="shared" si="86"/>
+        <v>4350.3214821862503</v>
       </c>
       <c r="CW21" s="3">
-        <f t="shared" si="24"/>
-        <v>4273.3265642262713</v>
+        <f t="shared" si="86"/>
+        <v>4306.8182673643878</v>
       </c>
       <c r="CX21" s="3">
-        <f t="shared" si="24"/>
-        <v>4230.5932985840082</v>
+        <f t="shared" si="86"/>
+        <v>4263.7500846907442</v>
       </c>
       <c r="CY21" s="3">
-        <f t="shared" si="24"/>
-        <v>4188.2873655981684</v>
+        <f t="shared" si="86"/>
+        <v>4221.1125838438365</v>
       </c>
       <c r="CZ21" s="3">
-        <f t="shared" si="24"/>
-        <v>4146.4044919421867</v>
+        <f t="shared" si="86"/>
+        <v>4178.9014580053981</v>
       </c>
       <c r="DA21" s="3">
-        <f t="shared" si="24"/>
-        <v>4104.9404470227646</v>
+        <f t="shared" si="86"/>
+        <v>4137.1124434253443</v>
       </c>
       <c r="DB21" s="3">
-        <f t="shared" ref="DB21:EH21" si="25">DA21*(1+$AQ$26)</f>
-        <v>4063.8910425525369</v>
+        <f t="shared" ref="DB21:EH21" si="87">DA21*(1+$AQ$26)</f>
+        <v>4095.7413189910908</v>
       </c>
       <c r="DC21" s="3">
-        <f t="shared" si="25"/>
-        <v>4023.2521321270115</v>
+        <f t="shared" si="87"/>
+        <v>4054.78390580118</v>
       </c>
       <c r="DD21" s="3">
-        <f t="shared" si="25"/>
-        <v>3983.0196108057412</v>
+        <f t="shared" si="87"/>
+        <v>4014.2360667431681</v>
       </c>
       <c r="DE21" s="3">
-        <f t="shared" si="25"/>
-        <v>3943.1894146976838</v>
+        <f t="shared" si="87"/>
+        <v>3974.0937060757365</v>
       </c>
       <c r="DF21" s="3">
-        <f t="shared" si="25"/>
-        <v>3903.7575205507069</v>
+        <f t="shared" si="87"/>
+        <v>3934.352769014979</v>
       </c>
       <c r="DG21" s="3">
-        <f t="shared" si="25"/>
-        <v>3864.7199453451999</v>
+        <f t="shared" si="87"/>
+        <v>3895.009241324829</v>
       </c>
       <c r="DH21" s="3">
-        <f t="shared" si="25"/>
-        <v>3826.0727458917477</v>
+        <f t="shared" si="87"/>
+        <v>3856.0591489115805</v>
       </c>
       <c r="DI21" s="3">
-        <f t="shared" si="25"/>
-        <v>3787.81201843283</v>
+        <f t="shared" si="87"/>
+        <v>3817.4985574224647</v>
       </c>
       <c r="DJ21" s="3">
-        <f t="shared" si="25"/>
-        <v>3749.9338982485015</v>
+        <f t="shared" si="87"/>
+        <v>3779.3235718482401</v>
       </c>
       <c r="DK21" s="3">
-        <f t="shared" si="25"/>
-        <v>3712.4345592660165</v>
+        <f t="shared" si="87"/>
+        <v>3741.5303361297579</v>
       </c>
       <c r="DL21" s="3">
-        <f t="shared" si="25"/>
-        <v>3675.3102136733564</v>
+        <f t="shared" si="87"/>
+        <v>3704.1150327684604</v>
       </c>
       <c r="DM21" s="3">
-        <f t="shared" si="25"/>
-        <v>3638.5571115366229</v>
+        <f t="shared" si="87"/>
+        <v>3667.0738824407758</v>
       </c>
       <c r="DN21" s="3">
-        <f t="shared" si="25"/>
-        <v>3602.1715404212564</v>
+        <f t="shared" si="87"/>
+        <v>3630.4031436163682</v>
       </c>
       <c r="DO21" s="3">
-        <f t="shared" si="25"/>
-        <v>3566.1498250170439</v>
+        <f t="shared" si="87"/>
+        <v>3594.0991121802044</v>
       </c>
       <c r="DP21" s="3">
-        <f t="shared" si="25"/>
-        <v>3530.4883267668733</v>
+        <f t="shared" si="87"/>
+        <v>3558.1581210584022</v>
       </c>
       <c r="DQ21" s="3">
-        <f t="shared" si="25"/>
-        <v>3495.1834434992047</v>
+        <f t="shared" si="87"/>
+        <v>3522.5765398478184</v>
       </c>
       <c r="DR21" s="3">
-        <f t="shared" si="25"/>
-        <v>3460.2316090642125</v>
+        <f t="shared" si="87"/>
+        <v>3487.35077444934</v>
       </c>
       <c r="DS21" s="3">
-        <f t="shared" si="25"/>
-        <v>3425.6292929735705</v>
+        <f t="shared" si="87"/>
+        <v>3452.4772667048464</v>
       </c>
       <c r="DT21" s="3">
-        <f t="shared" si="25"/>
-        <v>3391.373000043835</v>
+        <f t="shared" si="87"/>
+        <v>3417.9524940377978</v>
       </c>
       <c r="DU21" s="3">
-        <f t="shared" si="25"/>
-        <v>3357.4592700433964</v>
+        <f t="shared" si="87"/>
+        <v>3383.7729690974197</v>
       </c>
       <c r="DV21" s="3">
-        <f t="shared" si="25"/>
-        <v>3323.8846773429623</v>
+        <f t="shared" si="87"/>
+        <v>3349.9352394064454</v>
       </c>
       <c r="DW21" s="3">
-        <f t="shared" si="25"/>
-        <v>3290.6458305695328</v>
+        <f t="shared" si="87"/>
+        <v>3316.435887012381</v>
       </c>
       <c r="DX21" s="3">
-        <f t="shared" si="25"/>
-        <v>3257.7393722638376</v>
+        <f t="shared" si="87"/>
+        <v>3283.271528142257</v>
       </c>
       <c r="DY21" s="3">
-        <f t="shared" si="25"/>
-        <v>3225.161978541199</v>
+        <f t="shared" si="87"/>
+        <v>3250.4388128608343</v>
       </c>
       <c r="DZ21" s="3">
-        <f t="shared" si="25"/>
-        <v>3192.910358755787</v>
+        <f t="shared" si="87"/>
+        <v>3217.934424732226</v>
       </c>
       <c r="EA21" s="3">
-        <f t="shared" si="25"/>
-        <v>3160.9812551682289</v>
+        <f t="shared" si="87"/>
+        <v>3185.7550804849038</v>
       </c>
       <c r="EB21" s="3">
-        <f t="shared" si="25"/>
-        <v>3129.3714426165466</v>
+        <f t="shared" si="87"/>
+        <v>3153.897529680055</v>
       </c>
       <c r="EC21" s="3">
-        <f t="shared" si="25"/>
-        <v>3098.0777281903811</v>
+        <f t="shared" si="87"/>
+        <v>3122.3585543832542</v>
       </c>
       <c r="ED21" s="3">
-        <f t="shared" si="25"/>
-        <v>3067.0969509084771</v>
+        <f t="shared" si="87"/>
+        <v>3091.1349688394216</v>
       </c>
       <c r="EE21" s="3">
-        <f t="shared" si="25"/>
-        <v>3036.4259813993922</v>
+        <f t="shared" si="87"/>
+        <v>3060.2236191510274</v>
       </c>
       <c r="EF21" s="3">
-        <f t="shared" si="25"/>
-        <v>3006.0617215853981</v>
+        <f t="shared" si="87"/>
+        <v>3029.6213829595172</v>
       </c>
       <c r="EG21" s="3">
-        <f t="shared" si="25"/>
-        <v>2976.001104369544</v>
+        <f t="shared" si="87"/>
+        <v>2999.325169129922</v>
       </c>
       <c r="EH21" s="3">
-        <f t="shared" si="25"/>
-        <v>2946.2410933258484</v>
+        <f t="shared" si="87"/>
+        <v>2969.3319174386229</v>
       </c>
     </row>
     <row r="22" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="K22" s="6">
+        <f>233.5</f>
+        <v>233.5</v>
+      </c>
+      <c r="L22" s="6">
+        <f>233.5</f>
+        <v>233.5</v>
+      </c>
+      <c r="M22" s="6">
+        <f>233.5</f>
+        <v>233.5</v>
+      </c>
+      <c r="N22" s="6">
+        <f>233.5</f>
+        <v>233.5</v>
+      </c>
+      <c r="O22" s="6">
+        <f>233.5</f>
+        <v>233.5</v>
+      </c>
+      <c r="P22" s="6">
+        <f t="shared" ref="P22" si="88">235.4</f>
+        <v>235.4</v>
+      </c>
+      <c r="Q22" s="6">
+        <f>233.5</f>
+        <v>233.5</v>
+      </c>
+      <c r="R22" s="6">
+        <f>233.5</f>
+        <v>233.5</v>
+      </c>
+      <c r="S22" s="6">
+        <f>233.5</f>
+        <v>233.5</v>
+      </c>
+      <c r="T22" s="6">
+        <f>233.5</f>
+        <v>233.5</v>
+      </c>
       <c r="X22" s="6">
-        <f t="shared" ref="X22:AN22" si="26">235.4</f>
+        <f t="shared" ref="X22:AC22" si="89">235.4</f>
         <v>235.4</v>
       </c>
       <c r="Y22" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="89"/>
         <v>235.4</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="89"/>
         <v>235.4</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="89"/>
         <v>235.4</v>
       </c>
       <c r="AB22" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="89"/>
         <v>235.4</v>
       </c>
       <c r="AC22" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="89"/>
         <v>235.4</v>
       </c>
       <c r="AD22" s="6">
-        <f t="shared" si="26"/>
-        <v>235.4</v>
+        <f t="shared" ref="AD22:AN22" si="90">233.5</f>
+        <v>233.5</v>
       </c>
       <c r="AE22" s="6">
-        <f t="shared" si="26"/>
-        <v>235.4</v>
+        <f t="shared" si="90"/>
+        <v>233.5</v>
       </c>
       <c r="AF22" s="6">
-        <f t="shared" si="26"/>
-        <v>235.4</v>
+        <f t="shared" si="90"/>
+        <v>233.5</v>
       </c>
       <c r="AG22" s="6">
-        <f t="shared" si="26"/>
-        <v>235.4</v>
+        <f t="shared" si="90"/>
+        <v>233.5</v>
       </c>
       <c r="AH22" s="6">
-        <f t="shared" si="26"/>
-        <v>235.4</v>
+        <f t="shared" si="90"/>
+        <v>233.5</v>
       </c>
       <c r="AI22" s="6">
-        <f t="shared" si="26"/>
-        <v>235.4</v>
+        <f t="shared" si="90"/>
+        <v>233.5</v>
       </c>
       <c r="AJ22" s="6">
-        <f t="shared" si="26"/>
-        <v>235.4</v>
+        <f t="shared" si="90"/>
+        <v>233.5</v>
       </c>
       <c r="AK22" s="6">
-        <f t="shared" si="26"/>
-        <v>235.4</v>
+        <f t="shared" si="90"/>
+        <v>233.5</v>
       </c>
       <c r="AL22" s="6">
-        <f t="shared" si="26"/>
-        <v>235.4</v>
+        <f t="shared" si="90"/>
+        <v>233.5</v>
       </c>
       <c r="AM22" s="6">
-        <f t="shared" si="26"/>
-        <v>235.4</v>
+        <f t="shared" si="90"/>
+        <v>233.5</v>
       </c>
       <c r="AN22" s="6">
-        <f t="shared" si="26"/>
-        <v>235.4</v>
+        <f t="shared" si="90"/>
+        <v>233.5</v>
       </c>
     </row>
     <row r="23" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="K23" s="10">
+        <f t="shared" ref="K23" si="91">K21/K22</f>
+        <v>7.2334047109207713</v>
+      </c>
+      <c r="L23" s="10">
+        <f t="shared" ref="L23:M23" si="92">L21/L22</f>
+        <v>7.1991434689507496</v>
+      </c>
+      <c r="M23" s="10">
+        <f t="shared" si="92"/>
+        <v>7.2119914346895078</v>
+      </c>
+      <c r="N23" s="10">
+        <f t="shared" ref="N23" si="93">N21/N22</f>
+        <v>8.3854389721627403</v>
+      </c>
+      <c r="O23" s="10">
+        <f t="shared" ref="O23" si="94">O21/O22</f>
+        <v>6.6167023554603857</v>
+      </c>
+      <c r="P23" s="10">
+        <f t="shared" ref="P23:Q23" si="95">P21/P22</f>
+        <v>6.9711129991503817</v>
+      </c>
+      <c r="Q23" s="10">
+        <f t="shared" si="95"/>
+        <v>6.9507494646680943</v>
+      </c>
+      <c r="R23" s="10">
+        <f t="shared" ref="R23" si="96">R21/R22</f>
+        <v>2.2569593147751608</v>
+      </c>
+      <c r="S23" s="10">
+        <f t="shared" ref="S23:T23" si="97">S21/S22</f>
+        <v>7.3319057815845827</v>
+      </c>
+      <c r="T23" s="10">
+        <f t="shared" si="97"/>
+        <v>1.4646680942184154</v>
+      </c>
       <c r="X23" s="10">
-        <f t="shared" ref="X23:AC23" si="27">X21/X22</f>
+        <f t="shared" ref="X23:AC23" si="98">X21/X22</f>
         <v>26.465590484282071</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="98"/>
         <v>29.260832625318606</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="98"/>
         <v>26.826677994902294</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="98"/>
         <v>24.350042480883602</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="98"/>
         <v>29.396771452846217</v>
       </c>
       <c r="AC23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="98"/>
         <v>22.667799490229395</v>
       </c>
       <c r="AD23" s="10">
-        <f t="shared" ref="AD23:AN23" si="28">AD21/AD22</f>
-        <v>29.271367672047575</v>
+        <f t="shared" ref="AD23:AN23" si="99">AD21/AD22</f>
+        <v>29.509550107066378</v>
       </c>
       <c r="AE23" s="10">
-        <f t="shared" si="28"/>
-        <v>29.662634234069696</v>
+        <f t="shared" si="99"/>
+        <v>30.146109522912212</v>
       </c>
       <c r="AF23" s="10">
-        <f t="shared" si="28"/>
-        <v>30.060770048270996</v>
+        <f t="shared" si="99"/>
+        <v>30.54990607713917</v>
       </c>
       <c r="AG23" s="10">
-        <f t="shared" si="28"/>
-        <v>30.465932504770187</v>
+        <f t="shared" si="99"/>
+        <v>30.960810660678391</v>
       </c>
       <c r="AH23" s="10">
-        <f t="shared" si="28"/>
-        <v>30.878283228514892</v>
+        <f t="shared" si="99"/>
+        <v>31.378986455735962</v>
       </c>
       <c r="AI23" s="10">
-        <f t="shared" si="28"/>
-        <v>31.297988201457958</v>
+        <f t="shared" si="99"/>
+        <v>31.804601039397664</v>
       </c>
       <c r="AJ23" s="10">
-        <f t="shared" si="28"/>
-        <v>31.725217888350127</v>
+        <f t="shared" si="99"/>
+        <v>32.237826510469183</v>
       </c>
       <c r="AK23" s="10">
-        <f t="shared" si="28"/>
-        <v>32.160147366257583</v>
+        <f t="shared" si="99"/>
+        <v>32.678839620071678</v>
       </c>
       <c r="AL23" s="10">
-        <f t="shared" si="28"/>
-        <v>32.602956457914829</v>
+        <f t="shared" si="99"/>
+        <v>33.127821906105126</v>
       </c>
       <c r="AM23" s="10">
-        <f t="shared" si="28"/>
-        <v>33.053829869028519</v>
+        <f t="shared" si="99"/>
+        <v>33.584959831693936</v>
       </c>
       <c r="AN23" s="10">
-        <f t="shared" si="28"/>
-        <v>33.512957329649325</v>
+        <f t="shared" si="99"/>
+        <v>34.050444927734375</v>
       </c>
     </row>
     <row r="25" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="O25" s="11">
+        <f t="shared" ref="O25:P27" si="100">O3/K3-1</f>
+        <v>0.13332268880728093</v>
+      </c>
+      <c r="P25" s="11">
+        <f t="shared" si="100"/>
+        <v>9.8197412414595231E-2</v>
+      </c>
+      <c r="Q25" s="11">
+        <f>Q3/M3-1</f>
+        <v>3.2681604110175622E-2</v>
+      </c>
+      <c r="R25" s="11">
+        <f>R3/N3-1</f>
+        <v>-2.9247823636249781E-2</v>
+      </c>
+      <c r="S25" s="11">
+        <f>S3/O3-1</f>
+        <v>5.2127359819667429E-2</v>
+      </c>
+      <c r="T25" s="11">
+        <f>T3/P3-1</f>
+        <v>2.6474286848898743E-3</v>
+      </c>
       <c r="X25" s="11"/>
       <c r="Y25" s="11">
-        <f t="shared" ref="Y25:AB27" si="29">Y3/X3-1</f>
+        <f t="shared" ref="Y25:AB27" si="101">Y3/X3-1</f>
         <v>9.7396759434998925E-2</v>
       </c>
       <c r="Z25" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="101"/>
         <v>2.7435916108359937E-2</v>
       </c>
       <c r="AA25" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="101"/>
         <v>-1.7170195800478405E-2</v>
       </c>
       <c r="AB25" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="101"/>
         <v>1.4405221216601261E-2</v>
       </c>
       <c r="AC25" s="11">
@@ -2816,47 +3629,47 @@
         <v>5.3532391362303366E-2</v>
       </c>
       <c r="AD25" s="11">
-        <f t="shared" ref="AD25:AN27" si="30">AD3/AC3-1</f>
+        <f t="shared" ref="AD25:AN27" si="102">AD3/AC3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE25" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF25" s="11">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF25" s="11">
-        <f t="shared" si="30"/>
+      <c r="AG25" s="11">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG25" s="11">
-        <f t="shared" si="30"/>
+      <c r="AH25" s="11">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH25" s="11">
-        <f t="shared" si="30"/>
+      <c r="AI25" s="11">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI25" s="11">
-        <f t="shared" si="30"/>
+      <c r="AJ25" s="11">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ25" s="11">
-        <f t="shared" si="30"/>
+      <c r="AK25" s="11">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AK25" s="11">
-        <f t="shared" si="30"/>
+      <c r="AL25" s="11">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AL25" s="11">
-        <f t="shared" si="30"/>
+      <c r="AM25" s="11">
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AM25" s="11">
-        <f t="shared" si="30"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AN25" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -2864,69 +3677,95 @@
       <c r="B26" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="O26" s="11">
+        <f t="shared" si="100"/>
+        <v>0.15346153846153854</v>
+      </c>
+      <c r="P26" s="11">
+        <f t="shared" si="100"/>
+        <v>2.6575809199318678E-2</v>
+      </c>
+      <c r="Q26" s="11">
+        <f t="shared" ref="Q26:T27" si="103">Q4/M4-1</f>
+        <v>-8.1005586592178824E-2</v>
+      </c>
+      <c r="R26" s="11">
+        <f t="shared" si="103"/>
+        <v>7.3959408324733467E-2</v>
+      </c>
+      <c r="S26" s="11">
+        <f t="shared" si="103"/>
+        <v>9.3364454818272158E-3</v>
+      </c>
+      <c r="T26" s="11">
+        <f t="shared" si="103"/>
+        <v>-2.3232658479920287E-3</v>
+      </c>
       <c r="X26" s="11"/>
       <c r="Y26" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="101"/>
         <v>7.2855825391945794E-2</v>
       </c>
       <c r="Z26" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="101"/>
         <v>1.3276026743075375E-2</v>
       </c>
       <c r="AA26" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="101"/>
         <v>-8.5776227731171328E-3</v>
       </c>
       <c r="AB26" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="101"/>
         <v>7.4919186157064166E-2</v>
       </c>
       <c r="AC26" s="11">
-        <f t="shared" ref="AC26:AC27" si="31">AC4/AB4-1</f>
+        <f t="shared" ref="AC26:AC27" si="104">AC4/AB4-1</f>
         <v>4.0686361224128831E-2</v>
       </c>
       <c r="AD26" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE26" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF26" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG26" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH26" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI26" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ26" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK26" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL26" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM26" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN26" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AP26" s="1" t="s">
@@ -2940,70 +3779,96 @@
       <c r="B27" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="O27" s="12">
+        <f t="shared" si="100"/>
+        <v>0.13678434483670499</v>
+      </c>
+      <c r="P27" s="12">
+        <f t="shared" si="100"/>
+        <v>8.5604744503684271E-2</v>
+      </c>
+      <c r="Q27" s="12">
+        <f t="shared" si="103"/>
+        <v>1.339021211043967E-2</v>
+      </c>
+      <c r="R27" s="12">
+        <f t="shared" si="103"/>
+        <v>-1.3351700752357698E-2</v>
+      </c>
+      <c r="S27" s="12">
+        <f t="shared" si="103"/>
+        <v>4.4664146554230788E-2</v>
+      </c>
+      <c r="T27" s="12">
+        <f t="shared" si="103"/>
+        <v>1.8209910605893054E-3</v>
+      </c>
       <c r="X27" s="12"/>
       <c r="Y27" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="101"/>
         <v>9.3392630241423191E-2</v>
       </c>
       <c r="Z27" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="101"/>
         <v>2.516896541178637E-2</v>
       </c>
       <c r="AA27" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="101"/>
         <v>-1.5810512499254248E-2</v>
       </c>
       <c r="AB27" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="101"/>
         <v>2.4051285160038738E-2</v>
       </c>
       <c r="AC27" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="104"/>
         <v>5.1382989744120922E-2</v>
       </c>
       <c r="AD27" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="102"/>
         <v>2.1656180059963726E-2</v>
       </c>
       <c r="AE27" s="12">
-        <f t="shared" si="30"/>
-        <v>1.33394120156205E-2</v>
+        <f t="shared" si="102"/>
+        <v>2.1669706007810374E-2</v>
       </c>
       <c r="AF27" s="12">
-        <f t="shared" si="30"/>
-        <v>1.3394316193867661E-2</v>
+        <f t="shared" si="102"/>
+        <v>1.3366640271178509E-2</v>
       </c>
       <c r="AG27" s="12">
-        <f t="shared" si="30"/>
-        <v>1.3449936144120933E-2</v>
+        <f t="shared" si="102"/>
+        <v>1.3421900170688561E-2</v>
       </c>
       <c r="AH27" s="12">
-        <f t="shared" si="30"/>
-        <v>1.3506275052879602E-2</v>
+        <f t="shared" si="102"/>
+        <v>1.34778774518447E-2</v>
       </c>
       <c r="AI27" s="12">
-        <f t="shared" si="30"/>
-        <v>1.356333590956571E-2</v>
+        <f t="shared" si="102"/>
+        <v>1.3534575203956845E-2</v>
       </c>
       <c r="AJ27" s="12">
-        <f t="shared" si="30"/>
-        <v>1.3621121499584277E-2</v>
+        <f t="shared" si="102"/>
+        <v>1.3591996315806876E-2</v>
       </c>
       <c r="AK27" s="12">
-        <f t="shared" si="30"/>
-        <v>1.3679634397371299E-2</v>
+        <f t="shared" si="102"/>
+        <v>1.3650143468702192E-2</v>
       </c>
       <c r="AL27" s="12">
-        <f t="shared" si="30"/>
-        <v>1.3738876959430435E-2</v>
+        <f t="shared" si="102"/>
+        <v>1.3709019129517053E-2</v>
       </c>
       <c r="AM27" s="12">
-        <f t="shared" si="30"/>
-        <v>1.3798851317376792E-2</v>
+        <f t="shared" si="102"/>
+        <v>1.3768625543731705E-2</v>
       </c>
       <c r="AN27" s="12">
-        <f t="shared" si="30"/>
-        <v>1.3859559370987151E-2</v>
+        <f t="shared" si="102"/>
+        <v>1.3828964728477056E-2</v>
       </c>
       <c r="AP27" s="1" t="s">
         <v>60</v>
@@ -3016,24 +3881,64 @@
       <c r="B28" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="K28" s="11">
+        <f>(K3-K6)/K3</f>
+        <v>0.10977167491617436</v>
+      </c>
+      <c r="L28" s="11">
+        <f>(L3-L6)/L3</f>
+        <v>0.11048117458932985</v>
+      </c>
+      <c r="M28" s="11">
+        <f>(M3-M6)/M3</f>
+        <v>0.10296846011131726</v>
+      </c>
+      <c r="N28" s="11">
+        <f t="shared" ref="N28" si="105">(N3-N6)/N3</f>
+        <v>0.10778480616271059</v>
+      </c>
+      <c r="O28" s="11">
+        <f t="shared" ref="O28:T29" si="106">(O3-O6)/O3</f>
+        <v>9.2420400112707801E-2</v>
+      </c>
+      <c r="P28" s="11">
+        <f t="shared" si="106"/>
+        <v>0.10516910450724734</v>
+      </c>
+      <c r="Q28" s="11">
+        <f t="shared" si="106"/>
+        <v>0.10420121614151465</v>
+      </c>
+      <c r="R28" s="11">
+        <f t="shared" si="106"/>
+        <v>1.0322580645161291E-3</v>
+      </c>
+      <c r="S28" s="11">
+        <f t="shared" si="106"/>
+        <v>0.11060524906266737</v>
+      </c>
+      <c r="T28" s="11">
+        <f t="shared" si="106"/>
+        <v>4.4887451316918611E-2</v>
+      </c>
       <c r="X28" s="11">
-        <f t="shared" ref="X28:AB28" si="32">(X3-X6)/X3</f>
+        <f t="shared" ref="X28:AB28" si="107">(X3-X6)/X3</f>
         <v>0.10916428585699159</v>
       </c>
       <c r="Y28" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="107"/>
         <v>0.10799592193416836</v>
       </c>
       <c r="Z28" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="107"/>
         <v>0.10918756091078231</v>
       </c>
       <c r="AA28" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="107"/>
         <v>0.11013954494645369</v>
       </c>
       <c r="AB28" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="107"/>
         <v>0.10768683906513818</v>
       </c>
       <c r="AC28" s="11">
@@ -3041,79 +3946,119 @@
         <v>7.4649526797914881E-2</v>
       </c>
       <c r="AD28" s="11">
-        <f t="shared" ref="AD28:AN28" si="33">(AD3-AD6)/AD3</f>
+        <f t="shared" ref="AD28:AN28" si="108">(AD3-AD6)/AD3</f>
         <v>0.10999999999999996</v>
       </c>
       <c r="AE28" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="108"/>
+        <v>0.11</v>
+      </c>
+      <c r="AF28" s="11">
+        <f t="shared" si="108"/>
+        <v>0.11000000000000004</v>
+      </c>
+      <c r="AG28" s="11">
+        <f t="shared" si="108"/>
+        <v>0.11000000000000003</v>
+      </c>
+      <c r="AH28" s="11">
+        <f t="shared" si="108"/>
+        <v>0.10999999999999995</v>
+      </c>
+      <c r="AI28" s="11">
+        <f t="shared" si="108"/>
+        <v>0.10999999999999995</v>
+      </c>
+      <c r="AJ28" s="11">
+        <f t="shared" si="108"/>
+        <v>0.10999999999999995</v>
+      </c>
+      <c r="AK28" s="11">
+        <f t="shared" si="108"/>
+        <v>0.11</v>
+      </c>
+      <c r="AL28" s="11">
+        <f t="shared" si="108"/>
+        <v>0.10999999999999997</v>
+      </c>
+      <c r="AM28" s="11">
+        <f t="shared" si="108"/>
         <v>0.10999999999999999</v>
       </c>
-      <c r="AF28" s="11">
-        <f t="shared" si="33"/>
-        <v>0.10999999999999996</v>
-      </c>
-      <c r="AG28" s="11">
-        <f t="shared" si="33"/>
-        <v>0.10999999999999995</v>
-      </c>
-      <c r="AH28" s="11">
-        <f t="shared" si="33"/>
-        <v>0.11000000000000001</v>
-      </c>
-      <c r="AI28" s="11">
-        <f t="shared" si="33"/>
-        <v>0.10999999999999999</v>
-      </c>
-      <c r="AJ28" s="11">
-        <f t="shared" si="33"/>
-        <v>0.11000000000000003</v>
-      </c>
-      <c r="AK28" s="11">
-        <f t="shared" si="33"/>
-        <v>0.11000000000000001</v>
-      </c>
-      <c r="AL28" s="11">
-        <f t="shared" si="33"/>
-        <v>0.10999999999999995</v>
-      </c>
-      <c r="AM28" s="11">
-        <f t="shared" si="33"/>
+      <c r="AN28" s="11">
+        <f t="shared" si="108"/>
         <v>0.11000000000000004</v>
-      </c>
-      <c r="AN28" s="11">
-        <f t="shared" si="33"/>
-        <v>0.11</v>
       </c>
       <c r="AP28" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AQ28" s="6">
         <f>NPV(AQ27,AD21:EH21)</f>
-        <v>101171.23586137164</v>
+        <v>101920.66407516327</v>
       </c>
     </row>
     <row r="29" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="K29" s="11">
+        <f>(K4-K7)/K4</f>
+        <v>0.12153846153846154</v>
+      </c>
+      <c r="L29" s="11">
+        <f>(L4-L7)/L4</f>
+        <v>9.9829642248722317E-2</v>
+      </c>
+      <c r="M29" s="11">
+        <f>(M4-M7)/M4</f>
+        <v>0.12360335195530726</v>
+      </c>
+      <c r="N29" s="11">
+        <f t="shared" ref="N29" si="109">(N4-N7)/N4</f>
+        <v>0.108703130374957</v>
+      </c>
+      <c r="O29" s="11">
+        <f t="shared" si="106"/>
+        <v>0.13204401467155719</v>
+      </c>
+      <c r="P29" s="11">
+        <f t="shared" si="106"/>
+        <v>0.14304679721208099</v>
+      </c>
+      <c r="Q29" s="11">
+        <f t="shared" si="106"/>
+        <v>0.13677811550151975</v>
+      </c>
+      <c r="R29" s="11">
+        <f t="shared" si="106"/>
+        <v>0.1159513132607303</v>
+      </c>
+      <c r="S29" s="11">
+        <f t="shared" si="106"/>
+        <v>0.12784935579781961</v>
+      </c>
+      <c r="T29" s="11">
+        <f t="shared" si="106"/>
+        <v>-4.1250831669993347E-2</v>
+      </c>
       <c r="X29" s="11">
-        <f t="shared" ref="X29:AB29" si="34">(X4-X7)/X4</f>
+        <f t="shared" ref="X29:AB29" si="110">(X4-X7)/X4</f>
         <v>0.10533866174812993</v>
       </c>
       <c r="Y29" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="110"/>
         <v>0.10496657115568291</v>
       </c>
       <c r="Z29" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="110"/>
         <v>0.10802149118672826</v>
       </c>
       <c r="AA29" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="110"/>
         <v>0.12036508841985168</v>
       </c>
       <c r="AB29" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="110"/>
         <v>0.11312577392534937</v>
       </c>
       <c r="AC29" s="11">
@@ -3121,47 +4066,47 @@
         <v>0.13165051844297126</v>
       </c>
       <c r="AD29" s="11">
-        <f t="shared" ref="AD29:AN29" si="35">(AD4-AD7)/AD4</f>
+        <f t="shared" ref="AD29:AN29" si="111">(AD4-AD7)/AD4</f>
         <v>0.11999999999999995</v>
       </c>
       <c r="AE29" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="111"/>
         <v>0.12000000000000001</v>
       </c>
       <c r="AF29" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="111"/>
         <v>0.12000000000000001</v>
       </c>
       <c r="AG29" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="111"/>
         <v>0.12000000000000004</v>
       </c>
       <c r="AH29" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="111"/>
         <v>0.12000000000000002</v>
       </c>
       <c r="AI29" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="111"/>
         <v>0.12000000000000004</v>
       </c>
       <c r="AJ29" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="111"/>
         <v>0.12000000000000005</v>
       </c>
       <c r="AK29" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="111"/>
         <v>0.11999999999999998</v>
       </c>
       <c r="AL29" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="111"/>
         <v>0.11999999999999998</v>
       </c>
       <c r="AM29" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="111"/>
         <v>0.12000000000000001</v>
       </c>
       <c r="AN29" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="111"/>
         <v>0.12000000000000004</v>
       </c>
       <c r="AP29" s="1" t="s">
@@ -3176,24 +4121,64 @@
       <c r="B30" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="K30" s="11">
+        <f>K9/K5</f>
+        <v>0.11179426153642734</v>
+      </c>
+      <c r="L30" s="11">
+        <f>L9/L5</f>
+        <v>0.10860839873000659</v>
+      </c>
+      <c r="M30" s="11">
+        <f>M9/M5</f>
+        <v>0.10646996089584074</v>
+      </c>
+      <c r="N30" s="11">
+        <f t="shared" ref="N30" si="112">N9/N5</f>
+        <v>0.10792624774822507</v>
+      </c>
+      <c r="O30" s="11">
+        <f t="shared" ref="O30:T30" si="113">O9/O5</f>
+        <v>9.9331200930503058E-2</v>
+      </c>
+      <c r="P30" s="11">
+        <f t="shared" si="113"/>
+        <v>0.11146672552698378</v>
+      </c>
+      <c r="Q30" s="11">
+        <f t="shared" si="113"/>
+        <v>0.10921421889616464</v>
+      </c>
+      <c r="R30" s="11">
+        <f t="shared" si="113"/>
+        <v>2.0298571581999787E-2</v>
+      </c>
+      <c r="S30" s="11">
+        <f t="shared" si="113"/>
+        <v>0.1135111061626677</v>
+      </c>
+      <c r="T30" s="11">
+        <f t="shared" si="113"/>
+        <v>3.0625172128890113E-2</v>
+      </c>
       <c r="X30" s="11">
-        <f t="shared" ref="X30:AB30" si="36">X9/X5</f>
+        <f t="shared" ref="X30:AB30" si="114">X9/X5</f>
         <v>0.10854009228917275</v>
       </c>
       <c r="Y30" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="114"/>
         <v>0.10751093305605676</v>
       </c>
       <c r="Z30" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="114"/>
         <v>0.10900304277787722</v>
       </c>
       <c r="AA30" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="114"/>
         <v>0.11176951988360814</v>
       </c>
       <c r="AB30" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="114"/>
         <v>0.10859688327832946</v>
       </c>
       <c r="AC30" s="11">
@@ -3201,79 +4186,119 @@
         <v>8.4089917373984774E-2</v>
       </c>
       <c r="AD30" s="11">
-        <f t="shared" ref="AD30:AN30" si="37">AD9/AD5</f>
+        <f t="shared" ref="AD30:AN30" si="115">AD9/AD5</f>
         <v>0.11166970600781023</v>
       </c>
       <c r="AE30" s="11">
-        <f t="shared" si="37"/>
-        <v>0.11169715809693399</v>
+        <f t="shared" si="115"/>
+        <v>0.11168332013558931</v>
       </c>
       <c r="AF30" s="11">
-        <f t="shared" si="37"/>
-        <v>0.11172496807206032</v>
+        <f t="shared" si="115"/>
+        <v>0.11171095008534422</v>
       </c>
       <c r="AG30" s="11">
-        <f t="shared" si="37"/>
-        <v>0.11175313752643963</v>
+        <f t="shared" si="115"/>
+        <v>0.11173893872592235</v>
       </c>
       <c r="AH30" s="11">
-        <f t="shared" si="37"/>
-        <v>0.11178166795478273</v>
+        <f t="shared" si="115"/>
+        <v>0.11176728760197827</v>
       </c>
       <c r="AI30" s="11">
-        <f t="shared" si="37"/>
-        <v>0.11181056074979222</v>
+        <f t="shared" si="115"/>
+        <v>0.11179599815790325</v>
       </c>
       <c r="AJ30" s="11">
-        <f t="shared" si="37"/>
-        <v>0.11183981719868552</v>
+        <f t="shared" si="115"/>
+        <v>0.11182507173435116</v>
       </c>
       <c r="AK30" s="11">
-        <f t="shared" si="37"/>
-        <v>0.11186943847971523</v>
+        <f t="shared" si="115"/>
+        <v>0.11185450956475865</v>
       </c>
       <c r="AL30" s="11">
-        <f t="shared" si="37"/>
-        <v>0.11189942565868839</v>
+        <f t="shared" si="115"/>
+        <v>0.11188431277186586</v>
       </c>
       <c r="AM30" s="11">
-        <f t="shared" si="37"/>
-        <v>0.11192977968549371</v>
+        <f t="shared" si="115"/>
+        <v>0.11191448236423868</v>
       </c>
       <c r="AN30" s="11">
-        <f t="shared" si="37"/>
-        <v>0.111960501390638</v>
+        <f t="shared" si="115"/>
+        <v>0.11194501923279906</v>
       </c>
       <c r="AP30" s="1" t="s">
         <v>63</v>
       </c>
       <c r="AQ30" s="6">
         <f>AQ28+AQ29</f>
-        <v>83384.235861371635</v>
+        <v>84133.664075163266</v>
       </c>
     </row>
     <row r="31" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="K31" s="11">
+        <f>K14/K5</f>
+        <v>0.13466878222927409</v>
+      </c>
+      <c r="L31" s="11">
+        <f>L14/L5</f>
+        <v>0.12789792128437069</v>
+      </c>
+      <c r="M31" s="11">
+        <f>M14/M5</f>
+        <v>0.12098589880317573</v>
+      </c>
+      <c r="N31" s="11">
+        <f t="shared" ref="N31" si="116">N14/N5</f>
+        <v>0.12636431069195719</v>
+      </c>
+      <c r="O31" s="11">
+        <f t="shared" ref="O31:T31" si="117">O14/O5</f>
+        <v>0.11799941843559174</v>
+      </c>
+      <c r="P31" s="11">
+        <f t="shared" si="117"/>
+        <v>0.11852996358017878</v>
+      </c>
+      <c r="Q31" s="11">
+        <f t="shared" si="117"/>
+        <v>0.12511693171188026</v>
+      </c>
+      <c r="R31" s="11">
+        <f t="shared" si="117"/>
+        <v>3.7375147674793253E-2</v>
+      </c>
+      <c r="S31" s="11">
+        <f t="shared" si="117"/>
+        <v>0.13204921226966543</v>
+      </c>
+      <c r="T31" s="11">
+        <f t="shared" si="117"/>
+        <v>4.1200771137427705E-2</v>
+      </c>
       <c r="X31" s="11">
-        <f t="shared" ref="X31:AB31" si="38">X14/X5</f>
+        <f t="shared" ref="X31:AB31" si="118">X14/X5</f>
         <v>0.14286430816558551</v>
       </c>
       <c r="Y31" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="118"/>
         <v>0.13217529588060797</v>
       </c>
       <c r="Z31" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="118"/>
         <v>0.13607481653839271</v>
       </c>
       <c r="AA31" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="118"/>
         <v>0.12651551891367604</v>
       </c>
       <c r="AB31" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="118"/>
         <v>0.12589720442201535</v>
       </c>
       <c r="AC31" s="11">
@@ -3281,79 +4306,119 @@
         <v>9.8714862829553926E-2</v>
       </c>
       <c r="AD31" s="11">
-        <f t="shared" ref="AD31:AN31" si="39">AD14/AD5</f>
+        <f t="shared" ref="AD31:AN31" si="119">AD14/AD5</f>
         <v>0.12610382091750075</v>
       </c>
       <c r="AE31" s="11">
-        <f t="shared" si="39"/>
-        <v>0.12605933887319448</v>
+        <f t="shared" si="119"/>
+        <v>0.1259283973239371</v>
       </c>
       <c r="AF31" s="11">
-        <f t="shared" si="39"/>
-        <v>0.12601427692762923</v>
+        <f t="shared" si="119"/>
+        <v>0.12588413659351141</v>
       </c>
       <c r="AG31" s="11">
-        <f t="shared" si="39"/>
-        <v>0.12596863249917994</v>
+        <f t="shared" si="119"/>
+        <v>0.12583930127218113</v>
       </c>
       <c r="AH31" s="11">
-        <f t="shared" si="39"/>
-        <v>0.12592240316588899</v>
+        <f t="shared" si="119"/>
+        <v>0.12579388888554568</v>
       </c>
       <c r="AI31" s="11">
-        <f t="shared" si="39"/>
-        <v>0.12587558667108781</v>
+        <f t="shared" si="119"/>
+        <v>0.12574789711981899</v>
       </c>
       <c r="AJ31" s="11">
-        <f t="shared" si="39"/>
-        <v>0.12582818092903056</v>
+        <f t="shared" si="119"/>
+        <v>0.12570132382739288</v>
       </c>
       <c r="AK31" s="11">
-        <f t="shared" si="39"/>
-        <v>0.12578018403053445</v>
+        <f t="shared" si="119"/>
+        <v>0.12565416703240995</v>
       </c>
       <c r="AL31" s="11">
-        <f t="shared" si="39"/>
-        <v>0.12573159424861663</v>
+        <f t="shared" si="119"/>
+        <v>0.1256064249363405</v>
       </c>
       <c r="AM31" s="11">
-        <f t="shared" si="39"/>
-        <v>0.12568241004412339</v>
+        <f t="shared" si="119"/>
+        <v>0.12555809592355188</v>
       </c>
       <c r="AN31" s="11">
-        <f t="shared" si="39"/>
-        <v>0.12563263007134079</v>
+        <f t="shared" si="119"/>
+        <v>0.12550917856686486</v>
       </c>
       <c r="AP31" s="1" t="s">
         <v>64</v>
       </c>
       <c r="AQ31" s="4">
         <f>AQ30/AN22</f>
-        <v>354.22360179002391</v>
+        <v>360.31547783795833</v>
       </c>
     </row>
     <row r="32" spans="2:138" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="K32" s="11">
+        <f>K20/K19</f>
+        <v>0.15295887662988966</v>
+      </c>
+      <c r="L32" s="11">
+        <f>L20/L19</f>
+        <v>0.16201395812562314</v>
+      </c>
+      <c r="M32" s="11">
+        <f>M20/M19</f>
+        <v>0.13773681515617001</v>
+      </c>
+      <c r="N32" s="11">
+        <f t="shared" ref="N32" si="120">N20/N19</f>
+        <v>0.12472060795708538</v>
+      </c>
+      <c r="O32" s="11">
+        <f t="shared" ref="O32:T32" si="121">O20/O19</f>
+        <v>0.15803814713896458</v>
+      </c>
+      <c r="P32" s="11">
+        <f t="shared" si="121"/>
+        <v>0.15759753593429157</v>
+      </c>
+      <c r="Q32" s="11">
+        <f t="shared" si="121"/>
+        <v>0.15380604796663191</v>
+      </c>
+      <c r="R32" s="11">
+        <f t="shared" si="121"/>
+        <v>-1.5414258188824663E-2</v>
+      </c>
+      <c r="S32" s="11">
+        <f t="shared" si="121"/>
+        <v>0.15913555992141454</v>
+      </c>
+      <c r="T32" s="11">
+        <f t="shared" si="121"/>
+        <v>0.17985611510791366</v>
+      </c>
       <c r="X32" s="11">
-        <f t="shared" ref="X32:AB32" si="40">X20/X19</f>
+        <f t="shared" ref="X32:AB32" si="122">X20/X19</f>
         <v>0.13962159922662615</v>
       </c>
       <c r="Y32" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="122"/>
         <v>0.16357012750455374</v>
       </c>
       <c r="Z32" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="122"/>
         <v>0.16357615894039734</v>
       </c>
       <c r="AA32" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="122"/>
         <v>0.14191616766467066</v>
       </c>
       <c r="AB32" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="122"/>
         <v>0.14546801679427018</v>
       </c>
       <c r="AC32" s="11">
@@ -3361,47 +4426,47 @@
         <v>0.14212218649517686</v>
       </c>
       <c r="AD32" s="11">
-        <f t="shared" ref="AD32:AN32" si="41">AD20/AD19</f>
+        <f t="shared" ref="AD32:AN32" si="123">AD20/AD19</f>
         <v>0.15</v>
       </c>
       <c r="AE32" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="123"/>
         <v>0.15</v>
       </c>
       <c r="AF32" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="123"/>
         <v>0.15</v>
       </c>
       <c r="AG32" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="123"/>
         <v>0.15</v>
       </c>
       <c r="AH32" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="123"/>
         <v>0.15</v>
       </c>
       <c r="AI32" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="123"/>
         <v>0.15</v>
       </c>
       <c r="AJ32" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="123"/>
         <v>0.15</v>
       </c>
       <c r="AK32" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="123"/>
         <v>0.15</v>
       </c>
       <c r="AL32" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="123"/>
         <v>0.15</v>
       </c>
       <c r="AM32" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="123"/>
         <v>0.15</v>
       </c>
       <c r="AN32" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="123"/>
         <v>0.15</v>
       </c>
       <c r="AP32" s="1" t="s">
@@ -3409,31 +4474,71 @@
       </c>
       <c r="AQ32" s="4">
         <f>Main!D3</f>
-        <v>462.5</v>
+        <v>421.42</v>
       </c>
     </row>
     <row r="33" spans="2:43" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="K33" s="11">
+        <f>K21/K5</f>
+        <v>0.11166203887346292</v>
+      </c>
+      <c r="L33" s="11">
+        <f>L21/L5</f>
+        <v>0.10070089258970825</v>
+      </c>
+      <c r="M33" s="11">
+        <f>M21/M5</f>
+        <v>9.977485484062093E-2</v>
+      </c>
+      <c r="N33" s="11">
+        <f t="shared" ref="N33" si="124">N21/N5</f>
+        <v>0.1037405955282399</v>
+      </c>
+      <c r="O33" s="11">
+        <f t="shared" ref="O33:T33" si="125">O21/O5</f>
+        <v>8.9851701075894158E-2</v>
+      </c>
+      <c r="P33" s="11">
+        <f t="shared" si="125"/>
+        <v>9.0552919103851673E-2</v>
+      </c>
+      <c r="Q33" s="11">
+        <f t="shared" si="125"/>
+        <v>9.4890084190832558E-2</v>
+      </c>
+      <c r="R33" s="11">
+        <f t="shared" si="125"/>
+        <v>2.8299860380195468E-2</v>
+      </c>
+      <c r="S33" s="11">
+        <f t="shared" si="125"/>
+        <v>9.5307019985525807E-2</v>
+      </c>
+      <c r="T33" s="11">
+        <f t="shared" si="125"/>
+        <v>1.8837785733957588E-2</v>
+      </c>
       <c r="X33" s="11">
-        <f t="shared" ref="X33:AB33" si="42">X21/X5</f>
+        <f t="shared" ref="X33:AB33" si="126">X21/X5</f>
         <v>0.10415970039456965</v>
       </c>
       <c r="Y33" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="126"/>
         <v>0.10532432184470474</v>
       </c>
       <c r="Z33" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="126"/>
         <v>9.4191873993198491E-2</v>
       </c>
       <c r="AA33" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="126"/>
         <v>8.6869544131910767E-2</v>
       </c>
       <c r="AB33" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="126"/>
         <v>0.1024107975314854</v>
       </c>
       <c r="AC33" s="11">
@@ -3441,55 +4546,55 @@
         <v>7.5109440761229121E-2</v>
       </c>
       <c r="AD33" s="11">
-        <f t="shared" ref="AD33:AN33" si="43">AD21/AD5</f>
+        <f t="shared" ref="AD33:AN33" si="127">AD21/AD5</f>
         <v>9.4934357257880506E-2</v>
       </c>
       <c r="AE33" s="11">
-        <f t="shared" si="43"/>
-        <v>9.4936929635789785E-2</v>
+        <f t="shared" si="127"/>
+        <v>9.4925213475232306E-2</v>
       </c>
       <c r="AF33" s="11">
-        <f t="shared" si="43"/>
-        <v>9.493953554914461E-2</v>
+        <f t="shared" si="127"/>
+        <v>9.492783713539879E-2</v>
       </c>
       <c r="AG33" s="11">
-        <f t="shared" si="43"/>
-        <v>9.494217514723978E-2</v>
+        <f t="shared" si="127"/>
+        <v>9.4930494855809233E-2</v>
       </c>
       <c r="AH33" s="11">
-        <f t="shared" si="43"/>
-        <v>9.4944848570135951E-2</v>
+        <f t="shared" si="127"/>
+        <v>9.4933186783139209E-2</v>
       </c>
       <c r="AI33" s="11">
-        <f t="shared" si="43"/>
-        <v>9.4947555948335247E-2</v>
+        <f t="shared" si="127"/>
+        <v>9.4935913054544213E-2</v>
       </c>
       <c r="AJ33" s="11">
-        <f t="shared" si="43"/>
-        <v>9.4950297402455294E-2</v>
+        <f t="shared" si="127"/>
+        <v>9.4938673797328982E-2</v>
       </c>
       <c r="AK33" s="11">
-        <f t="shared" si="43"/>
-        <v>9.495307304290361E-2</v>
+        <f t="shared" si="127"/>
+        <v>9.4941469128616729E-2</v>
       </c>
       <c r="AL33" s="11">
-        <f t="shared" si="43"/>
-        <v>9.4955882969550792E-2</v>
+        <f t="shared" si="127"/>
+        <v>9.4944299155019785E-2</v>
       </c>
       <c r="AM33" s="11">
-        <f t="shared" si="43"/>
-        <v>9.4958727271405516E-2</v>
+        <f t="shared" si="127"/>
+        <v>9.4947163972308776E-2</v>
       </c>
       <c r="AN33" s="11">
-        <f t="shared" si="43"/>
-        <v>9.4961606026289627E-2</v>
+        <f t="shared" si="127"/>
+        <v>9.4950063665082726E-2</v>
       </c>
       <c r="AP33" s="3" t="s">
         <v>66</v>
       </c>
       <c r="AQ33" s="12">
         <f>AQ31/AQ32-1</f>
-        <v>-0.2341111312648132</v>
+        <v>-0.14499673048749862</v>
       </c>
     </row>
     <row r="34" spans="2:43" x14ac:dyDescent="0.3">

--- a/Financial Analysis/LMT.xlsx
+++ b/Financial Analysis/LMT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA73989-42A1-4F2F-96D1-DFF6648958AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF798E6-C675-4E89-ADD4-18D315786A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4D34CE10-A2B1-43BA-A8EF-FB8FB8D75171}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
   <si>
     <t>LMT</t>
   </si>
@@ -233,16 +233,26 @@
   </si>
   <si>
     <t>Slightly overvalued</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,6 +294,15 @@
       <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -327,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -347,6 +366,8 @@
     <xf numFmtId="4" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -793,14 +814,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>421.42</v>
+        <v>504.49</v>
       </c>
       <c r="E3" s="5">
-        <v>45862</v>
+        <v>45934</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45869</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="5">
         <v>45958</v>
@@ -824,7 +845,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>98401.57</v>
+        <v>117798.41500000001</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -869,7 +890,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>116188.57</v>
+        <v>135585.41500000001</v>
       </c>
     </row>
   </sheetData>
@@ -879,7 +900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A3F992-CF1A-49DF-A7A3-B2026107AC3A}">
-  <dimension ref="B2:EH34"/>
+  <dimension ref="B2:EH40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -3882,63 +3903,63 @@
         <v>53</v>
       </c>
       <c r="K28" s="11">
-        <f>(K3-K6)/K3</f>
+        <f t="shared" ref="K28:M29" si="105">(K3-K6)/K3</f>
         <v>0.10977167491617436</v>
       </c>
       <c r="L28" s="11">
-        <f>(L3-L6)/L3</f>
+        <f t="shared" si="105"/>
         <v>0.11048117458932985</v>
       </c>
       <c r="M28" s="11">
-        <f>(M3-M6)/M3</f>
+        <f t="shared" si="105"/>
         <v>0.10296846011131726</v>
       </c>
       <c r="N28" s="11">
-        <f t="shared" ref="N28" si="105">(N3-N6)/N3</f>
+        <f t="shared" ref="N28" si="106">(N3-N6)/N3</f>
         <v>0.10778480616271059</v>
       </c>
       <c r="O28" s="11">
-        <f t="shared" ref="O28:T29" si="106">(O3-O6)/O3</f>
+        <f t="shared" ref="O28:T29" si="107">(O3-O6)/O3</f>
         <v>9.2420400112707801E-2</v>
       </c>
       <c r="P28" s="11">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.10516910450724734</v>
       </c>
       <c r="Q28" s="11">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.10420121614151465</v>
       </c>
       <c r="R28" s="11">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>1.0322580645161291E-3</v>
       </c>
       <c r="S28" s="11">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.11060524906266737</v>
       </c>
       <c r="T28" s="11">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>4.4887451316918611E-2</v>
       </c>
       <c r="X28" s="11">
-        <f t="shared" ref="X28:AB28" si="107">(X3-X6)/X3</f>
+        <f t="shared" ref="X28:AB28" si="108">(X3-X6)/X3</f>
         <v>0.10916428585699159</v>
       </c>
       <c r="Y28" s="11">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.10799592193416836</v>
       </c>
       <c r="Z28" s="11">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.10918756091078231</v>
       </c>
       <c r="AA28" s="11">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.11013954494645369</v>
       </c>
       <c r="AB28" s="11">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.10768683906513818</v>
       </c>
       <c r="AC28" s="11">
@@ -3946,47 +3967,47 @@
         <v>7.4649526797914881E-2</v>
       </c>
       <c r="AD28" s="11">
-        <f t="shared" ref="AD28:AN28" si="108">(AD3-AD6)/AD3</f>
+        <f t="shared" ref="AD28:AN28" si="109">(AD3-AD6)/AD3</f>
         <v>0.10999999999999996</v>
       </c>
       <c r="AE28" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.11</v>
       </c>
       <c r="AF28" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.11000000000000004</v>
       </c>
       <c r="AG28" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.11000000000000003</v>
       </c>
       <c r="AH28" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.10999999999999995</v>
       </c>
       <c r="AI28" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.10999999999999995</v>
       </c>
       <c r="AJ28" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.10999999999999995</v>
       </c>
       <c r="AK28" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.11</v>
       </c>
       <c r="AL28" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.10999999999999997</v>
       </c>
       <c r="AM28" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="AN28" s="11">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.11000000000000004</v>
       </c>
       <c r="AP28" s="1" t="s">
@@ -4002,63 +4023,63 @@
         <v>54</v>
       </c>
       <c r="K29" s="11">
-        <f>(K4-K7)/K4</f>
+        <f t="shared" si="105"/>
         <v>0.12153846153846154</v>
       </c>
       <c r="L29" s="11">
-        <f>(L4-L7)/L4</f>
+        <f t="shared" si="105"/>
         <v>9.9829642248722317E-2</v>
       </c>
       <c r="M29" s="11">
-        <f>(M4-M7)/M4</f>
+        <f t="shared" si="105"/>
         <v>0.12360335195530726</v>
       </c>
       <c r="N29" s="11">
-        <f t="shared" ref="N29" si="109">(N4-N7)/N4</f>
+        <f t="shared" ref="N29" si="110">(N4-N7)/N4</f>
         <v>0.108703130374957</v>
       </c>
       <c r="O29" s="11">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.13204401467155719</v>
       </c>
       <c r="P29" s="11">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.14304679721208099</v>
       </c>
       <c r="Q29" s="11">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.13677811550151975</v>
       </c>
       <c r="R29" s="11">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.1159513132607303</v>
       </c>
       <c r="S29" s="11">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.12784935579781961</v>
       </c>
       <c r="T29" s="11">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>-4.1250831669993347E-2</v>
       </c>
       <c r="X29" s="11">
-        <f t="shared" ref="X29:AB29" si="110">(X4-X7)/X4</f>
+        <f t="shared" ref="X29:AB29" si="111">(X4-X7)/X4</f>
         <v>0.10533866174812993</v>
       </c>
       <c r="Y29" s="11">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.10496657115568291</v>
       </c>
       <c r="Z29" s="11">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.10802149118672826</v>
       </c>
       <c r="AA29" s="11">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.12036508841985168</v>
       </c>
       <c r="AB29" s="11">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.11312577392534937</v>
       </c>
       <c r="AC29" s="11">
@@ -4066,47 +4087,47 @@
         <v>0.13165051844297126</v>
       </c>
       <c r="AD29" s="11">
-        <f t="shared" ref="AD29:AN29" si="111">(AD4-AD7)/AD4</f>
+        <f t="shared" ref="AD29:AN29" si="112">(AD4-AD7)/AD4</f>
         <v>0.11999999999999995</v>
       </c>
       <c r="AE29" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.12000000000000001</v>
       </c>
       <c r="AF29" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.12000000000000001</v>
       </c>
       <c r="AG29" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.12000000000000004</v>
       </c>
       <c r="AH29" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.12000000000000002</v>
       </c>
       <c r="AI29" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.12000000000000004</v>
       </c>
       <c r="AJ29" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.12000000000000005</v>
       </c>
       <c r="AK29" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.11999999999999998</v>
       </c>
       <c r="AL29" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.11999999999999998</v>
       </c>
       <c r="AM29" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.12000000000000001</v>
       </c>
       <c r="AN29" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.12000000000000004</v>
       </c>
       <c r="AP29" s="1" t="s">
@@ -4134,51 +4155,51 @@
         <v>0.10646996089584074</v>
       </c>
       <c r="N30" s="11">
-        <f t="shared" ref="N30" si="112">N9/N5</f>
+        <f t="shared" ref="N30" si="113">N9/N5</f>
         <v>0.10792624774822507</v>
       </c>
       <c r="O30" s="11">
-        <f t="shared" ref="O30:T30" si="113">O9/O5</f>
+        <f t="shared" ref="O30:T30" si="114">O9/O5</f>
         <v>9.9331200930503058E-2</v>
       </c>
       <c r="P30" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.11146672552698378</v>
       </c>
       <c r="Q30" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.10921421889616464</v>
       </c>
       <c r="R30" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>2.0298571581999787E-2</v>
       </c>
       <c r="S30" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.1135111061626677</v>
       </c>
       <c r="T30" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>3.0625172128890113E-2</v>
       </c>
       <c r="X30" s="11">
-        <f t="shared" ref="X30:AB30" si="114">X9/X5</f>
+        <f t="shared" ref="X30:AB30" si="115">X9/X5</f>
         <v>0.10854009228917275</v>
       </c>
       <c r="Y30" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0.10751093305605676</v>
       </c>
       <c r="Z30" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0.10900304277787722</v>
       </c>
       <c r="AA30" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0.11176951988360814</v>
       </c>
       <c r="AB30" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0.10859688327832946</v>
       </c>
       <c r="AC30" s="11">
@@ -4186,47 +4207,47 @@
         <v>8.4089917373984774E-2</v>
       </c>
       <c r="AD30" s="11">
-        <f t="shared" ref="AD30:AN30" si="115">AD9/AD5</f>
+        <f t="shared" ref="AD30:AN30" si="116">AD9/AD5</f>
         <v>0.11166970600781023</v>
       </c>
       <c r="AE30" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.11168332013558931</v>
       </c>
       <c r="AF30" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.11171095008534422</v>
       </c>
       <c r="AG30" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.11173893872592235</v>
       </c>
       <c r="AH30" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.11176728760197827</v>
       </c>
       <c r="AI30" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.11179599815790325</v>
       </c>
       <c r="AJ30" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.11182507173435116</v>
       </c>
       <c r="AK30" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.11185450956475865</v>
       </c>
       <c r="AL30" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.11188431277186586</v>
       </c>
       <c r="AM30" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.11191448236423868</v>
       </c>
       <c r="AN30" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.11194501923279906</v>
       </c>
       <c r="AP30" s="1" t="s">
@@ -4254,51 +4275,51 @@
         <v>0.12098589880317573</v>
       </c>
       <c r="N31" s="11">
-        <f t="shared" ref="N31" si="116">N14/N5</f>
+        <f t="shared" ref="N31" si="117">N14/N5</f>
         <v>0.12636431069195719</v>
       </c>
       <c r="O31" s="11">
-        <f t="shared" ref="O31:T31" si="117">O14/O5</f>
+        <f t="shared" ref="O31:T31" si="118">O14/O5</f>
         <v>0.11799941843559174</v>
       </c>
       <c r="P31" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.11852996358017878</v>
       </c>
       <c r="Q31" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.12511693171188026</v>
       </c>
       <c r="R31" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>3.7375147674793253E-2</v>
       </c>
       <c r="S31" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.13204921226966543</v>
       </c>
       <c r="T31" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>4.1200771137427705E-2</v>
       </c>
       <c r="X31" s="11">
-        <f t="shared" ref="X31:AB31" si="118">X14/X5</f>
+        <f t="shared" ref="X31:AB31" si="119">X14/X5</f>
         <v>0.14286430816558551</v>
       </c>
       <c r="Y31" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.13217529588060797</v>
       </c>
       <c r="Z31" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.13607481653839271</v>
       </c>
       <c r="AA31" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.12651551891367604</v>
       </c>
       <c r="AB31" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.12589720442201535</v>
       </c>
       <c r="AC31" s="11">
@@ -4306,47 +4327,47 @@
         <v>9.8714862829553926E-2</v>
       </c>
       <c r="AD31" s="11">
-        <f t="shared" ref="AD31:AN31" si="119">AD14/AD5</f>
+        <f t="shared" ref="AD31:AN31" si="120">AD14/AD5</f>
         <v>0.12610382091750075</v>
       </c>
       <c r="AE31" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.1259283973239371</v>
       </c>
       <c r="AF31" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.12588413659351141</v>
       </c>
       <c r="AG31" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.12583930127218113</v>
       </c>
       <c r="AH31" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.12579388888554568</v>
       </c>
       <c r="AI31" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.12574789711981899</v>
       </c>
       <c r="AJ31" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.12570132382739288</v>
       </c>
       <c r="AK31" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.12565416703240995</v>
       </c>
       <c r="AL31" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.1256064249363405</v>
       </c>
       <c r="AM31" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.12555809592355188</v>
       </c>
       <c r="AN31" s="11">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.12550917856686486</v>
       </c>
       <c r="AP31" s="1" t="s">
@@ -4374,51 +4395,51 @@
         <v>0.13773681515617001</v>
       </c>
       <c r="N32" s="11">
-        <f t="shared" ref="N32" si="120">N20/N19</f>
+        <f t="shared" ref="N32" si="121">N20/N19</f>
         <v>0.12472060795708538</v>
       </c>
       <c r="O32" s="11">
-        <f t="shared" ref="O32:T32" si="121">O20/O19</f>
+        <f t="shared" ref="O32:T32" si="122">O20/O19</f>
         <v>0.15803814713896458</v>
       </c>
       <c r="P32" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.15759753593429157</v>
       </c>
       <c r="Q32" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.15380604796663191</v>
       </c>
       <c r="R32" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>-1.5414258188824663E-2</v>
       </c>
       <c r="S32" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.15913555992141454</v>
       </c>
       <c r="T32" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.17985611510791366</v>
       </c>
       <c r="X32" s="11">
-        <f t="shared" ref="X32:AB32" si="122">X20/X19</f>
+        <f t="shared" ref="X32:AB32" si="123">X20/X19</f>
         <v>0.13962159922662615</v>
       </c>
       <c r="Y32" s="11">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.16357012750455374</v>
       </c>
       <c r="Z32" s="11">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.16357615894039734</v>
       </c>
       <c r="AA32" s="11">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.14191616766467066</v>
       </c>
       <c r="AB32" s="11">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.14546801679427018</v>
       </c>
       <c r="AC32" s="11">
@@ -4426,47 +4447,47 @@
         <v>0.14212218649517686</v>
       </c>
       <c r="AD32" s="11">
-        <f t="shared" ref="AD32:AN32" si="123">AD20/AD19</f>
+        <f t="shared" ref="AD32:AN32" si="124">AD20/AD19</f>
         <v>0.15</v>
       </c>
       <c r="AE32" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.15</v>
       </c>
       <c r="AF32" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.15</v>
       </c>
       <c r="AG32" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.15</v>
       </c>
       <c r="AH32" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.15</v>
       </c>
       <c r="AI32" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.15</v>
       </c>
       <c r="AJ32" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.15</v>
       </c>
       <c r="AK32" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.15</v>
       </c>
       <c r="AL32" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.15</v>
       </c>
       <c r="AM32" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.15</v>
       </c>
       <c r="AN32" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.15</v>
       </c>
       <c r="AP32" s="1" t="s">
@@ -4474,7 +4495,7 @@
       </c>
       <c r="AQ32" s="4">
         <f>Main!D3</f>
-        <v>421.42</v>
+        <v>504.49</v>
       </c>
     </row>
     <row r="33" spans="2:43" x14ac:dyDescent="0.3">
@@ -4494,51 +4515,51 @@
         <v>9.977485484062093E-2</v>
       </c>
       <c r="N33" s="11">
-        <f t="shared" ref="N33" si="124">N21/N5</f>
+        <f t="shared" ref="N33" si="125">N21/N5</f>
         <v>0.1037405955282399</v>
       </c>
       <c r="O33" s="11">
-        <f t="shared" ref="O33:T33" si="125">O21/O5</f>
+        <f t="shared" ref="O33:T33" si="126">O21/O5</f>
         <v>8.9851701075894158E-2</v>
       </c>
       <c r="P33" s="11">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>9.0552919103851673E-2</v>
       </c>
       <c r="Q33" s="11">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>9.4890084190832558E-2</v>
       </c>
       <c r="R33" s="11">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>2.8299860380195468E-2</v>
       </c>
       <c r="S33" s="11">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>9.5307019985525807E-2</v>
       </c>
       <c r="T33" s="11">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>1.8837785733957588E-2</v>
       </c>
       <c r="X33" s="11">
-        <f t="shared" ref="X33:AB33" si="126">X21/X5</f>
+        <f t="shared" ref="X33:AB33" si="127">X21/X5</f>
         <v>0.10415970039456965</v>
       </c>
       <c r="Y33" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.10532432184470474</v>
       </c>
       <c r="Z33" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>9.4191873993198491E-2</v>
       </c>
       <c r="AA33" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>8.6869544131910767E-2</v>
       </c>
       <c r="AB33" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.1024107975314854</v>
       </c>
       <c r="AC33" s="11">
@@ -4546,47 +4567,47 @@
         <v>7.5109440761229121E-2</v>
       </c>
       <c r="AD33" s="11">
-        <f t="shared" ref="AD33:AN33" si="127">AD21/AD5</f>
+        <f t="shared" ref="AD33:AN33" si="128">AD21/AD5</f>
         <v>9.4934357257880506E-2</v>
       </c>
       <c r="AE33" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.4925213475232306E-2</v>
       </c>
       <c r="AF33" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.492783713539879E-2</v>
       </c>
       <c r="AG33" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.4930494855809233E-2</v>
       </c>
       <c r="AH33" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.4933186783139209E-2</v>
       </c>
       <c r="AI33" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.4935913054544213E-2</v>
       </c>
       <c r="AJ33" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.4938673797328982E-2</v>
       </c>
       <c r="AK33" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.4941469128616729E-2</v>
       </c>
       <c r="AL33" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.4944299155019785E-2</v>
       </c>
       <c r="AM33" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.4947163972308776E-2</v>
       </c>
       <c r="AN33" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.4950063665082726E-2</v>
       </c>
       <c r="AP33" s="3" t="s">
@@ -4594,7 +4615,7 @@
       </c>
       <c r="AQ33" s="12">
         <f>AQ31/AQ32-1</f>
-        <v>-0.14499673048749862</v>
+        <v>-0.28578271553854717</v>
       </c>
     </row>
     <row r="34" spans="2:43" x14ac:dyDescent="0.3">
@@ -4603,6 +4624,32 @@
       </c>
       <c r="AQ34" s="8" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="2:43" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="T37" s="13">
+        <v>58870</v>
+      </c>
+    </row>
+    <row r="39" spans="2:43" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T39" s="14">
+        <f>Main!D9/Model!T37</f>
+        <v>2.3031325802615936</v>
+      </c>
+    </row>
+    <row r="40" spans="2:43" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="T40" s="11">
+        <f>T37/Main!D9-1</f>
+        <v>-0.56580875605241165</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/LMT.xlsx
+++ b/Financial Analysis/LMT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865908FF-D039-4B95-876F-AEAE03996B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5626C6AA-E6EE-426C-8AE4-B221CB825914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4D34CE10-A2B1-43BA-A8EF-FB8FB8D75171}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="89">
   <si>
     <t>LMT</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>International helicopters</t>
+  </si>
+  <si>
+    <t>Q425 8K</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -297,7 +303,7 @@
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,6 +355,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -391,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -422,6 +437,10 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,13 +462,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -493,14 +512,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>59</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
@@ -517,8 +536,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13853160" y="15240"/>
-          <a:ext cx="0" cy="7612380"/>
+          <a:off x="14683740" y="15240"/>
+          <a:ext cx="0" cy="10904220"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -868,17 +887,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>485.41</v>
+        <v>610.42999999999995</v>
       </c>
       <c r="E3" s="5">
-        <v>45955</v>
+        <v>46059</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45955</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="5">
-        <v>46049</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
@@ -886,10 +905,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <v>231.4</v>
+        <f>230.9</f>
+        <v>230.9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
@@ -898,7 +918,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>112323.87400000001</v>
+        <v>140948.28699999998</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -906,11 +926,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>3470</f>
-        <v>3470</v>
+        <f>4121</f>
+        <v>4121</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>58</v>
@@ -921,11 +941,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>1669+20520</f>
-        <v>22189</v>
+        <f>1168+20531</f>
+        <v>21699</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
@@ -934,7 +954,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>-18719</v>
+        <v>-17578</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
@@ -943,7 +963,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>131042.87400000001</v>
+        <v>158526.28699999998</v>
       </c>
     </row>
   </sheetData>
@@ -953,18 +973,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A3F992-CF1A-49DF-A7A3-B2026107AC3A}">
-  <dimension ref="B2:EH64"/>
+  <dimension ref="B2:EL64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="41" width="8.88671875" style="1"/>
-    <col min="42" max="42" width="14.109375" style="1" customWidth="1"/>
-    <col min="43" max="43" width="17.109375" style="1" customWidth="1"/>
-    <col min="44" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="45" width="8.88671875" style="1"/>
+    <col min="46" max="46" width="14.109375" style="1" customWidth="1"/>
+    <col min="47" max="47" width="17.109375" style="1" customWidth="1"/>
+    <col min="48" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:44" x14ac:dyDescent="0.3">
       <c r="C2" s="8" t="s">
         <v>14</v>
       </c>
@@ -1025,59 +1045,63 @@
       <c r="V2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="X2" s="1">
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="8"/>
+      <c r="AB2" s="1">
         <v>2019</v>
       </c>
-      <c r="Y2" s="1">
+      <c r="AC2" s="1">
         <v>2020</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="AD2" s="1">
         <v>2021</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="AE2" s="1">
         <v>2022</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AF2" s="1">
         <v>2023</v>
       </c>
-      <c r="AC2" s="1">
+      <c r="AG2" s="1">
         <v>2024</v>
       </c>
-      <c r="AD2" s="1">
+      <c r="AH2" s="1">
         <v>2025</v>
       </c>
-      <c r="AE2" s="1">
+      <c r="AI2" s="1">
         <v>2026</v>
       </c>
-      <c r="AF2" s="1">
+      <c r="AJ2" s="1">
         <v>2027</v>
       </c>
-      <c r="AG2" s="1">
+      <c r="AK2" s="1">
         <v>2028</v>
       </c>
-      <c r="AH2" s="1">
+      <c r="AL2" s="1">
         <v>2029</v>
       </c>
-      <c r="AI2" s="1">
+      <c r="AM2" s="1">
         <v>2030</v>
       </c>
-      <c r="AJ2" s="1">
+      <c r="AN2" s="1">
         <v>2031</v>
       </c>
-      <c r="AK2" s="1">
+      <c r="AO2" s="1">
         <v>2032</v>
       </c>
-      <c r="AL2" s="1">
+      <c r="AP2" s="1">
         <v>2033</v>
       </c>
-      <c r="AM2" s="1">
+      <c r="AQ2" s="1">
         <v>2034</v>
       </c>
-      <c r="AN2" s="1">
+      <c r="AR2" s="1">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>81</v>
       </c>
@@ -1098,15 +1122,23 @@
       <c r="Q3" s="8">
         <v>48</v>
       </c>
-      <c r="R3" s="8"/>
+      <c r="R3" s="8">
+        <v>62</v>
+      </c>
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
       <c r="U3" s="8">
         <v>46</v>
       </c>
-      <c r="V3" s="8"/>
-    </row>
-    <row r="4" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="V3" s="8">
+        <v>48</v>
+      </c>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+    </row>
+    <row r="4" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>82</v>
       </c>
@@ -1127,15 +1159,23 @@
       <c r="Q4" s="8">
         <v>2</v>
       </c>
-      <c r="R4" s="8"/>
+      <c r="R4" s="8">
+        <v>7</v>
+      </c>
       <c r="S4" s="8"/>
       <c r="T4" s="8"/>
       <c r="U4" s="8">
         <v>5</v>
       </c>
-      <c r="V4" s="8"/>
-    </row>
-    <row r="5" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="V4" s="8">
+        <v>4</v>
+      </c>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="8"/>
+    </row>
+    <row r="5" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>83</v>
       </c>
@@ -1156,15 +1196,23 @@
       <c r="Q5" s="8">
         <v>4</v>
       </c>
-      <c r="R5" s="8"/>
+      <c r="R5" s="8">
+        <v>8</v>
+      </c>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
       <c r="U5" s="8">
         <v>0</v>
       </c>
-      <c r="V5" s="8"/>
-    </row>
-    <row r="6" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="V5" s="8">
+        <v>0</v>
+      </c>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+    </row>
+    <row r="6" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>84</v>
       </c>
@@ -1185,15 +1233,23 @@
       <c r="Q6" s="8">
         <v>24</v>
       </c>
-      <c r="R6" s="8"/>
+      <c r="R6" s="8">
+        <v>25</v>
+      </c>
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
       <c r="U6" s="8">
         <v>22</v>
       </c>
-      <c r="V6" s="8"/>
-    </row>
-    <row r="7" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="V6" s="8">
+        <v>35</v>
+      </c>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8"/>
+    </row>
+    <row r="7" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>85</v>
       </c>
@@ -1214,15 +1270,23 @@
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="8"/>
+      <c r="R7" s="8">
+        <v>1</v>
+      </c>
       <c r="S7" s="8"/>
       <c r="T7" s="8"/>
       <c r="U7" s="8">
         <v>1</v>
       </c>
-      <c r="V7" s="8"/>
-    </row>
-    <row r="8" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="V7" s="8">
+        <v>0</v>
+      </c>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+    </row>
+    <row r="8" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>86</v>
       </c>
@@ -1243,15 +1307,23 @@
       <c r="Q8" s="8">
         <v>4</v>
       </c>
-      <c r="R8" s="8"/>
+      <c r="R8" s="8">
+        <v>8</v>
+      </c>
       <c r="S8" s="8"/>
       <c r="T8" s="8"/>
       <c r="U8" s="8">
         <v>6</v>
       </c>
-      <c r="V8" s="8"/>
-    </row>
-    <row r="9" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="V8" s="8">
+        <v>11</v>
+      </c>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+    </row>
+    <row r="9" spans="2:44" x14ac:dyDescent="0.3">
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -1272,8 +1344,12 @@
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
       <c r="V9" s="8"/>
-    </row>
-    <row r="10" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+    </row>
+    <row r="10" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>72</v>
       </c>
@@ -1300,15 +1376,21 @@
       <c r="U10" s="16">
         <v>47506</v>
       </c>
-      <c r="V10" s="8"/>
-      <c r="AC10" s="16">
+      <c r="V10" s="16">
+        <v>59435</v>
+      </c>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AG10" s="16">
         <v>62763</v>
       </c>
-      <c r="AD10" s="16">
-        <v>47506</v>
-      </c>
-    </row>
-    <row r="11" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AH10" s="16">
+        <v>59435</v>
+      </c>
+    </row>
+    <row r="11" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>73</v>
       </c>
@@ -1335,15 +1417,21 @@
       <c r="U11" s="16">
         <v>45906</v>
       </c>
-      <c r="V11" s="8"/>
-      <c r="AC11" s="16">
+      <c r="V11" s="16">
+        <v>46650</v>
+      </c>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8"/>
+      <c r="AG11" s="16">
         <v>38783</v>
       </c>
-      <c r="AD11" s="16">
-        <v>45906</v>
-      </c>
-    </row>
-    <row r="12" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AH11" s="16">
+        <v>46650</v>
+      </c>
+    </row>
+    <row r="12" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>74</v>
       </c>
@@ -1370,15 +1458,21 @@
       <c r="U12" s="16">
         <v>47269</v>
       </c>
-      <c r="V12" s="8"/>
-      <c r="AC12" s="16">
+      <c r="V12" s="16">
+        <v>47715</v>
+      </c>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+      <c r="AG12" s="16">
         <v>38117</v>
       </c>
-      <c r="AD12" s="16">
-        <v>47269</v>
-      </c>
-    </row>
-    <row r="13" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AH12" s="16">
+        <v>47715</v>
+      </c>
+    </row>
+    <row r="13" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>75</v>
       </c>
@@ -1405,15 +1499,21 @@
       <c r="U13" s="16">
         <v>38390</v>
       </c>
-      <c r="V13" s="8"/>
-      <c r="AC13" s="16">
+      <c r="V13" s="16">
+        <v>39822</v>
+      </c>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8"/>
+      <c r="AG13" s="16">
         <v>36377</v>
       </c>
-      <c r="AD13" s="16">
-        <v>38390</v>
-      </c>
-    </row>
-    <row r="14" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AH13" s="16">
+        <v>39822</v>
+      </c>
+    </row>
+    <row r="14" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>80</v>
       </c>
@@ -1442,17 +1542,24 @@
         <f>SUM(U10:U13)</f>
         <v>179071</v>
       </c>
-      <c r="V14" s="15"/>
-      <c r="AC14" s="17">
-        <f>SUM(AC10:AC13)</f>
+      <c r="V14" s="17">
+        <f>SUM(V10:V13)</f>
+        <v>193622</v>
+      </c>
+      <c r="W14" s="15"/>
+      <c r="X14" s="15"/>
+      <c r="Y14" s="15"/>
+      <c r="Z14" s="15"/>
+      <c r="AG14" s="17">
+        <f>SUM(AG10:AG13)</f>
         <v>176040</v>
       </c>
-      <c r="AD14" s="17">
-        <f>SUM(AD10:AD13)</f>
-        <v>179071</v>
-      </c>
-    </row>
-    <row r="15" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AH14" s="17">
+        <f>SUM(AH10:AH13)</f>
+        <v>193622</v>
+      </c>
+    </row>
+    <row r="15" spans="2:44" x14ac:dyDescent="0.3">
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -1473,8 +1580,12 @@
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
       <c r="V15" s="8"/>
-    </row>
-    <row r="16" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="8"/>
+    </row>
+    <row r="16" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>72</v>
       </c>
@@ -1495,15 +1606,23 @@
       <c r="Q16" s="16">
         <v>6487</v>
       </c>
-      <c r="R16" s="8"/>
+      <c r="R16" s="16">
+        <v>8009</v>
+      </c>
       <c r="S16" s="8"/>
       <c r="T16" s="8"/>
       <c r="U16" s="16">
         <v>7256</v>
       </c>
-      <c r="V16" s="8"/>
-    </row>
-    <row r="17" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="V16" s="16">
+        <v>8524</v>
+      </c>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+    </row>
+    <row r="17" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>73</v>
       </c>
@@ -1524,15 +1643,23 @@
       <c r="Q17" s="16">
         <v>3175</v>
       </c>
-      <c r="R17" s="8"/>
+      <c r="R17" s="16">
+        <v>3412</v>
+      </c>
       <c r="S17" s="8"/>
       <c r="T17" s="8"/>
       <c r="U17" s="16">
         <v>3624</v>
       </c>
-      <c r="V17" s="8"/>
-    </row>
-    <row r="18" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="V17" s="16">
+        <v>4020</v>
+      </c>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+    </row>
+    <row r="18" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>74</v>
       </c>
@@ -1553,15 +1680,23 @@
       <c r="Q18" s="16">
         <v>4367</v>
       </c>
-      <c r="R18" s="8"/>
+      <c r="R18" s="16">
+        <v>4261</v>
+      </c>
       <c r="S18" s="8"/>
       <c r="T18" s="8"/>
       <c r="U18" s="16">
         <v>4373</v>
       </c>
-      <c r="V18" s="8"/>
-    </row>
-    <row r="19" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="V18" s="16">
+        <v>4616</v>
+      </c>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="8"/>
+    </row>
+    <row r="19" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>75</v>
       </c>
@@ -1582,15 +1717,23 @@
       <c r="Q19" s="16">
         <v>3075</v>
       </c>
-      <c r="R19" s="8"/>
+      <c r="R19" s="16">
+        <v>2940</v>
+      </c>
       <c r="S19" s="8"/>
       <c r="T19" s="8"/>
       <c r="U19" s="16">
         <v>3356</v>
       </c>
-      <c r="V19" s="8"/>
-    </row>
-    <row r="20" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="V19" s="16">
+        <v>3161</v>
+      </c>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="8"/>
+    </row>
+    <row r="20" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>33</v>
       </c>
@@ -1612,16 +1755,26 @@
         <f>SUM(Q16:Q19)</f>
         <v>17104</v>
       </c>
-      <c r="R20" s="15"/>
+      <c r="R20" s="17">
+        <f>SUM(R16:R19)</f>
+        <v>18622</v>
+      </c>
       <c r="S20" s="15"/>
       <c r="T20" s="15"/>
       <c r="U20" s="17">
         <f>SUM(U16:U19)</f>
         <v>18609</v>
       </c>
-      <c r="V20" s="15"/>
-    </row>
-    <row r="21" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="V20" s="17">
+        <f>SUM(V16:V19)</f>
+        <v>20321</v>
+      </c>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15"/>
+      <c r="Z20" s="15"/>
+    </row>
+    <row r="21" spans="2:44" x14ac:dyDescent="0.3">
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -1642,8 +1795,12 @@
       <c r="T21" s="8"/>
       <c r="U21" s="8"/>
       <c r="V21" s="8"/>
-    </row>
-    <row r="22" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="W21" s="8"/>
+      <c r="X21" s="8"/>
+      <c r="Y21" s="8"/>
+      <c r="Z21" s="8"/>
+    </row>
+    <row r="22" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>32</v>
       </c>
@@ -1657,7 +1814,7 @@
         <v>14014</v>
       </c>
       <c r="N22" s="6">
-        <f>AB22-M22-L22-K22</f>
+        <f>AF22-M22-L22-K22</f>
         <v>15967</v>
       </c>
       <c r="O22" s="6">
@@ -1670,7 +1827,7 @@
         <v>14472</v>
       </c>
       <c r="R22" s="6">
-        <f>AC22-Q22-P22-O22</f>
+        <f>AG22-Q22-P22-O22</f>
         <v>15500</v>
       </c>
       <c r="S22" s="6">
@@ -1682,74 +1839,78 @@
       <c r="U22" s="6">
         <v>15311</v>
       </c>
-      <c r="V22" s="6">
-        <f>R22*1.04</f>
-        <v>16120</v>
-      </c>
-      <c r="X22" s="6">
+      <c r="V22" s="18">
+        <f>R22*1.07</f>
+        <v>16585</v>
+      </c>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="6"/>
+      <c r="AB22" s="6">
         <v>50053</v>
       </c>
-      <c r="Y22" s="6">
+      <c r="AC22" s="6">
         <v>54928</v>
       </c>
-      <c r="Z22" s="6">
+      <c r="AD22" s="6">
         <v>56435</v>
       </c>
-      <c r="AA22" s="6">
+      <c r="AE22" s="6">
         <v>55466</v>
       </c>
-      <c r="AB22" s="6">
+      <c r="AF22" s="6">
         <v>56265</v>
       </c>
-      <c r="AC22" s="6">
+      <c r="AG22" s="6">
         <v>59277</v>
       </c>
-      <c r="AD22" s="6">
+      <c r="AH22" s="6">
         <f>SUM(S22:V22)</f>
-        <v>61516</v>
-      </c>
-      <c r="AE22" s="6">
-        <f>AD22*1.03</f>
-        <v>63361.48</v>
-      </c>
-      <c r="AF22" s="6">
-        <f>AE22*1.02</f>
-        <v>64628.709600000002</v>
-      </c>
-      <c r="AG22" s="6">
-        <f t="shared" ref="AG22:AN22" si="0">AF22*1.01</f>
-        <v>65274.996696000002</v>
-      </c>
-      <c r="AH22" s="6">
-        <f t="shared" si="0"/>
-        <v>65927.746662960009</v>
+        <v>61981</v>
       </c>
       <c r="AI22" s="6">
-        <f t="shared" si="0"/>
-        <v>66587.024129589612</v>
+        <f>AH22*1.03</f>
+        <v>63840.43</v>
       </c>
       <c r="AJ22" s="6">
-        <f t="shared" si="0"/>
-        <v>67252.894370885508</v>
+        <f>AI22*1.02</f>
+        <v>65117.238600000004</v>
       </c>
       <c r="AK22" s="6">
-        <f t="shared" si="0"/>
-        <v>67925.423314594358</v>
+        <f t="shared" ref="AK22:AR22" si="0">AJ22*1.01</f>
+        <v>65768.410986000003</v>
       </c>
       <c r="AL22" s="6">
         <f t="shared" si="0"/>
-        <v>68604.677547740299</v>
+        <v>66426.095095860001</v>
       </c>
       <c r="AM22" s="6">
         <f t="shared" si="0"/>
-        <v>69290.724323217699</v>
+        <v>67090.356046818604</v>
       </c>
       <c r="AN22" s="6">
         <f t="shared" si="0"/>
-        <v>69983.631566449883</v>
-      </c>
-    </row>
-    <row r="23" spans="2:40" x14ac:dyDescent="0.3">
+        <v>67761.259607286789</v>
+      </c>
+      <c r="AO22" s="6">
+        <f t="shared" si="0"/>
+        <v>68438.872203359657</v>
+      </c>
+      <c r="AP22" s="6">
+        <f t="shared" si="0"/>
+        <v>69123.260925393261</v>
+      </c>
+      <c r="AQ22" s="6">
+        <f t="shared" si="0"/>
+        <v>69814.49353464719</v>
+      </c>
+      <c r="AR22" s="6">
+        <f t="shared" si="0"/>
+        <v>70512.638469993661</v>
+      </c>
+    </row>
+    <row r="23" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
@@ -1763,7 +1924,7 @@
         <v>2864</v>
       </c>
       <c r="N23" s="6">
-        <f>AB23-M23-L23-K23</f>
+        <f>AF23-M23-L23-K23</f>
         <v>2907</v>
       </c>
       <c r="O23" s="6">
@@ -1776,7 +1937,7 @@
         <v>2632</v>
       </c>
       <c r="R23" s="6">
-        <f>AC23-Q23-P23-O23</f>
+        <f>AG23-Q23-P23-O23</f>
         <v>3122</v>
       </c>
       <c r="S23" s="6">
@@ -1788,74 +1949,78 @@
       <c r="U23" s="6">
         <v>3298</v>
       </c>
-      <c r="V23" s="6">
-        <f>R23*1.1</f>
-        <v>3434.2000000000003</v>
-      </c>
-      <c r="X23" s="6">
+      <c r="V23" s="18">
+        <f>R23*1.11</f>
+        <v>3465.4200000000005</v>
+      </c>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="6"/>
+      <c r="AB23" s="6">
         <v>9759</v>
       </c>
-      <c r="Y23" s="6">
+      <c r="AC23" s="6">
         <v>10470</v>
       </c>
-      <c r="Z23" s="6">
+      <c r="AD23" s="6">
         <v>10609</v>
       </c>
-      <c r="AA23" s="6">
+      <c r="AE23" s="6">
         <v>10518</v>
       </c>
-      <c r="AB23" s="6">
+      <c r="AF23" s="6">
         <v>11306</v>
       </c>
-      <c r="AC23" s="6">
+      <c r="AG23" s="6">
         <v>11766</v>
       </c>
-      <c r="AD23" s="6">
+      <c r="AH23" s="6">
         <f>SUM(S23:V23)</f>
-        <v>12765.2</v>
-      </c>
-      <c r="AE23" s="6">
-        <f>AD23*1.05</f>
-        <v>13403.460000000001</v>
-      </c>
-      <c r="AF23" s="6">
-        <f t="shared" ref="AF23:AN23" si="1">AE23*1.03</f>
-        <v>13805.563800000002</v>
-      </c>
-      <c r="AG23" s="6">
-        <f t="shared" si="1"/>
-        <v>14219.730714000003</v>
-      </c>
-      <c r="AH23" s="6">
-        <f t="shared" si="1"/>
-        <v>14646.322635420003</v>
+        <v>12796.42</v>
       </c>
       <c r="AI23" s="6">
-        <f t="shared" si="1"/>
-        <v>15085.712314482604</v>
+        <f>AH23*1.05</f>
+        <v>13436.241</v>
       </c>
       <c r="AJ23" s="6">
-        <f t="shared" si="1"/>
-        <v>15538.283683917081</v>
+        <f t="shared" ref="AJ23:AR23" si="1">AI23*1.03</f>
+        <v>13839.328230000001</v>
       </c>
       <c r="AK23" s="6">
         <f t="shared" si="1"/>
-        <v>16004.432194434594</v>
+        <v>14254.508076900001</v>
       </c>
       <c r="AL23" s="6">
         <f t="shared" si="1"/>
-        <v>16484.565160267633</v>
+        <v>14682.143319207002</v>
       </c>
       <c r="AM23" s="6">
         <f t="shared" si="1"/>
-        <v>16979.102115075664</v>
+        <v>15122.607618783211</v>
       </c>
       <c r="AN23" s="6">
         <f t="shared" si="1"/>
-        <v>17488.475178527933</v>
-      </c>
-    </row>
-    <row r="24" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
+        <v>15576.285847346708</v>
+      </c>
+      <c r="AO23" s="6">
+        <f t="shared" si="1"/>
+        <v>16043.574422767109</v>
+      </c>
+      <c r="AP23" s="6">
+        <f t="shared" si="1"/>
+        <v>16524.881655450125</v>
+      </c>
+      <c r="AQ23" s="6">
+        <f t="shared" si="1"/>
+        <v>17020.628105113628</v>
+      </c>
+      <c r="AR23" s="6">
+        <f t="shared" si="1"/>
+        <v>17531.246948267039</v>
+      </c>
+    </row>
+    <row r="24" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>33</v>
       </c>
@@ -1904,79 +2069,83 @@
         <v>18609</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="9"/>
-        <v>19554.2</v>
-      </c>
-      <c r="X24" s="9">
-        <f t="shared" ref="X24:AN24" si="10">X22+X23</f>
+        <f>V20</f>
+        <v>20321</v>
+      </c>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="9"/>
+      <c r="AB24" s="9">
+        <f t="shared" ref="AB24:AR24" si="10">AB22+AB23</f>
         <v>59812</v>
       </c>
-      <c r="Y24" s="9">
+      <c r="AC24" s="9">
         <f t="shared" si="10"/>
         <v>65398</v>
       </c>
-      <c r="Z24" s="9">
+      <c r="AD24" s="9">
         <f t="shared" si="10"/>
         <v>67044</v>
       </c>
-      <c r="AA24" s="9">
+      <c r="AE24" s="9">
         <f t="shared" si="10"/>
         <v>65984</v>
       </c>
-      <c r="AB24" s="9">
+      <c r="AF24" s="9">
         <f t="shared" si="10"/>
         <v>67571</v>
       </c>
-      <c r="AC24" s="9">
+      <c r="AG24" s="9">
         <f t="shared" si="10"/>
         <v>71043</v>
       </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="10"/>
-        <v>74281.2</v>
-      </c>
-      <c r="AE24" s="9">
-        <f t="shared" si="10"/>
-        <v>76764.94</v>
-      </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="10"/>
-        <v>78434.273400000005</v>
-      </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="10"/>
-        <v>79494.727410000007</v>
-      </c>
       <c r="AH24" s="9">
         <f t="shared" si="10"/>
-        <v>80574.069298380011</v>
+        <v>74777.42</v>
       </c>
       <c r="AI24" s="9">
         <f t="shared" si="10"/>
-        <v>81672.736444072216</v>
+        <v>77276.671000000002</v>
       </c>
       <c r="AJ24" s="9">
         <f t="shared" si="10"/>
-        <v>82791.178054802585</v>
+        <v>78956.566830000011</v>
       </c>
       <c r="AK24" s="9">
         <f t="shared" si="10"/>
-        <v>83929.855509028945</v>
+        <v>80022.919062900008</v>
       </c>
       <c r="AL24" s="9">
         <f t="shared" si="10"/>
-        <v>85089.242708007936</v>
+        <v>81108.238415066997</v>
       </c>
       <c r="AM24" s="9">
         <f t="shared" si="10"/>
-        <v>86269.826438293356</v>
+        <v>82212.963665601812</v>
       </c>
       <c r="AN24" s="9">
         <f t="shared" si="10"/>
-        <v>87472.10674497782</v>
-      </c>
-    </row>
-    <row r="25" spans="2:40" x14ac:dyDescent="0.3">
+        <v>83337.545454633495</v>
+      </c>
+      <c r="AO24" s="9">
+        <f t="shared" si="10"/>
+        <v>84482.446626126766</v>
+      </c>
+      <c r="AP24" s="9">
+        <f t="shared" si="10"/>
+        <v>85648.142580843385</v>
+      </c>
+      <c r="AQ24" s="9">
+        <f t="shared" si="10"/>
+        <v>86835.121639760822</v>
+      </c>
+      <c r="AR24" s="9">
+        <f t="shared" si="10"/>
+        <v>88043.885418260703</v>
+      </c>
+    </row>
+    <row r="25" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>34</v>
       </c>
@@ -1990,7 +2159,7 @@
         <v>12571</v>
       </c>
       <c r="N25" s="6">
-        <f t="shared" ref="N25:N26" si="11">AB25-M25-L25-K25</f>
+        <f t="shared" ref="N25:N26" si="11">AF25-M25-L25-K25</f>
         <v>14246</v>
       </c>
       <c r="O25" s="6">
@@ -2003,7 +2172,7 @@
         <v>12964</v>
       </c>
       <c r="R25" s="6">
-        <f t="shared" ref="R25:R26" si="12">AC25-Q25-P25-O25</f>
+        <f t="shared" ref="R25:R26" si="12">AG25-Q25-P25-O25</f>
         <v>15484</v>
       </c>
       <c r="S25" s="6">
@@ -2015,74 +2184,78 @@
       <c r="U25" s="6">
         <v>13708</v>
       </c>
-      <c r="V25" s="6">
+      <c r="V25" s="18">
         <f>V22*0.89</f>
-        <v>14346.800000000001</v>
-      </c>
-      <c r="X25" s="6">
+        <v>14760.65</v>
+      </c>
+      <c r="W25" s="6"/>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="6"/>
+      <c r="AB25" s="6">
         <v>44589</v>
       </c>
-      <c r="Y25" s="6">
+      <c r="AC25" s="6">
         <v>48996</v>
       </c>
-      <c r="Z25" s="6">
+      <c r="AD25" s="6">
         <v>50273</v>
       </c>
-      <c r="AA25" s="6">
+      <c r="AE25" s="6">
         <v>49357</v>
       </c>
-      <c r="AB25" s="6">
+      <c r="AF25" s="6">
         <v>50206</v>
       </c>
-      <c r="AC25" s="6">
+      <c r="AG25" s="6">
         <v>54852</v>
       </c>
-      <c r="AD25" s="6">
-        <f t="shared" ref="AD25:AD26" si="13">SUM(S25:V25)</f>
-        <v>55807.8</v>
-      </c>
-      <c r="AE25" s="6">
-        <f t="shared" ref="AE25:AN25" si="14">AE22*0.89</f>
-        <v>56391.717200000006</v>
-      </c>
-      <c r="AF25" s="6">
-        <f t="shared" si="14"/>
-        <v>57519.551544000002</v>
-      </c>
-      <c r="AG25" s="6">
-        <f t="shared" si="14"/>
-        <v>58094.74705944</v>
-      </c>
       <c r="AH25" s="6">
-        <f t="shared" si="14"/>
-        <v>58675.694530034409</v>
+        <f t="shared" ref="AH25:AH26" si="13">SUM(S25:V25)</f>
+        <v>56221.65</v>
       </c>
       <c r="AI25" s="6">
-        <f t="shared" si="14"/>
-        <v>59262.451475334754</v>
+        <f t="shared" ref="AI25:AR25" si="14">AI22*0.89</f>
+        <v>56817.9827</v>
       </c>
       <c r="AJ25" s="6">
         <f t="shared" si="14"/>
-        <v>59855.075990088102</v>
+        <v>57954.342354000008</v>
       </c>
       <c r="AK25" s="6">
         <f t="shared" si="14"/>
-        <v>60453.62674998898</v>
+        <v>58533.885777540003</v>
       </c>
       <c r="AL25" s="6">
         <f t="shared" si="14"/>
-        <v>61058.163017488871</v>
+        <v>59119.224635315404</v>
       </c>
       <c r="AM25" s="6">
         <f t="shared" si="14"/>
-        <v>61668.744647663756</v>
+        <v>59710.416881668556</v>
       </c>
       <c r="AN25" s="6">
         <f t="shared" si="14"/>
-        <v>62285.4320941404</v>
-      </c>
-    </row>
-    <row r="26" spans="2:40" x14ac:dyDescent="0.3">
+        <v>60307.521050485244</v>
+      </c>
+      <c r="AO25" s="6">
+        <f t="shared" si="14"/>
+        <v>60910.596260990096</v>
+      </c>
+      <c r="AP25" s="6">
+        <f t="shared" si="14"/>
+        <v>61519.702223600005</v>
+      </c>
+      <c r="AQ25" s="6">
+        <f t="shared" si="14"/>
+        <v>62134.899245836001</v>
+      </c>
+      <c r="AR25" s="6">
+        <f t="shared" si="14"/>
+        <v>62756.248238294356</v>
+      </c>
+    </row>
+    <row r="26" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>35</v>
       </c>
@@ -2121,74 +2294,78 @@
       <c r="U26" s="6">
         <v>2871</v>
       </c>
-      <c r="V26" s="6">
+      <c r="V26" s="18">
         <f>V23*0.87</f>
-        <v>2987.7540000000004</v>
-      </c>
-      <c r="X26" s="6">
+        <v>3014.9154000000003</v>
+      </c>
+      <c r="W26" s="6"/>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="6"/>
+      <c r="AB26" s="6">
         <v>8731</v>
       </c>
-      <c r="Y26" s="6">
+      <c r="AC26" s="6">
         <v>9371</v>
       </c>
-      <c r="Z26" s="6">
+      <c r="AD26" s="6">
         <v>9463</v>
       </c>
-      <c r="AA26" s="6">
+      <c r="AE26" s="6">
         <v>9252</v>
       </c>
-      <c r="AB26" s="6">
+      <c r="AF26" s="6">
         <v>10027</v>
       </c>
-      <c r="AC26" s="6">
+      <c r="AG26" s="6">
         <v>10217</v>
       </c>
-      <c r="AD26" s="6">
+      <c r="AH26" s="6">
         <f t="shared" si="13"/>
-        <v>11628.754000000001</v>
-      </c>
-      <c r="AE26" s="6">
-        <f t="shared" ref="AE26:AN26" si="15">AE23*0.88</f>
-        <v>11795.044800000001</v>
-      </c>
-      <c r="AF26" s="6">
-        <f t="shared" si="15"/>
-        <v>12148.896144000002</v>
-      </c>
-      <c r="AG26" s="6">
-        <f t="shared" si="15"/>
-        <v>12513.363028320002</v>
-      </c>
-      <c r="AH26" s="6">
-        <f t="shared" si="15"/>
-        <v>12888.763919169603</v>
+        <v>11655.9154</v>
       </c>
       <c r="AI26" s="6">
-        <f t="shared" si="15"/>
-        <v>13275.426836744691</v>
+        <f t="shared" ref="AI26:AR26" si="15">AI23*0.88</f>
+        <v>11823.89208</v>
       </c>
       <c r="AJ26" s="6">
         <f t="shared" si="15"/>
-        <v>13673.689641847031</v>
+        <v>12178.608842400001</v>
       </c>
       <c r="AK26" s="6">
         <f t="shared" si="15"/>
-        <v>14083.900331102443</v>
+        <v>12543.967107672001</v>
       </c>
       <c r="AL26" s="6">
         <f t="shared" si="15"/>
-        <v>14506.417341035518</v>
+        <v>12920.286120902161</v>
       </c>
       <c r="AM26" s="6">
         <f t="shared" si="15"/>
-        <v>14941.609861266585</v>
+        <v>13307.894704529226</v>
       </c>
       <c r="AN26" s="6">
         <f t="shared" si="15"/>
-        <v>15389.858157104582</v>
-      </c>
-    </row>
-    <row r="27" spans="2:40" x14ac:dyDescent="0.3">
+        <v>13707.131545665103</v>
+      </c>
+      <c r="AO26" s="6">
+        <f t="shared" si="15"/>
+        <v>14118.345492035056</v>
+      </c>
+      <c r="AP26" s="6">
+        <f t="shared" si="15"/>
+        <v>14541.895856796109</v>
+      </c>
+      <c r="AQ26" s="6">
+        <f t="shared" si="15"/>
+        <v>14978.152732499993</v>
+      </c>
+      <c r="AR26" s="6">
+        <f t="shared" si="15"/>
+        <v>15427.497314474995</v>
+      </c>
+    </row>
+    <row r="27" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>37</v>
       </c>
@@ -2237,79 +2414,82 @@
         <v>16579</v>
       </c>
       <c r="V27" s="6">
-        <f t="shared" si="23"/>
-        <v>17334.554</v>
-      </c>
-      <c r="X27" s="6">
-        <f t="shared" ref="X27:AC27" si="24">X25+X26</f>
+        <v>17999</v>
+      </c>
+      <c r="W27" s="6"/>
+      <c r="X27" s="6"/>
+      <c r="Y27" s="6"/>
+      <c r="Z27" s="6"/>
+      <c r="AB27" s="6">
+        <f t="shared" ref="AB27:AG27" si="24">AB25+AB26</f>
         <v>53320</v>
       </c>
-      <c r="Y27" s="6">
+      <c r="AC27" s="6">
         <f t="shared" si="24"/>
         <v>58367</v>
       </c>
-      <c r="Z27" s="6">
+      <c r="AD27" s="6">
         <f t="shared" si="24"/>
         <v>59736</v>
       </c>
-      <c r="AA27" s="6">
+      <c r="AE27" s="6">
         <f t="shared" si="24"/>
         <v>58609</v>
       </c>
-      <c r="AB27" s="6">
+      <c r="AF27" s="6">
         <f t="shared" si="24"/>
         <v>60233</v>
       </c>
-      <c r="AC27" s="6">
+      <c r="AG27" s="6">
         <f t="shared" si="24"/>
         <v>65069</v>
       </c>
-      <c r="AD27" s="6">
-        <f t="shared" ref="AD27:AN27" si="25">AD25+AD26</f>
-        <v>67436.554000000004</v>
-      </c>
-      <c r="AE27" s="6">
-        <f t="shared" si="25"/>
-        <v>68186.762000000002</v>
-      </c>
-      <c r="AF27" s="6">
-        <f t="shared" si="25"/>
-        <v>69668.447688</v>
-      </c>
-      <c r="AG27" s="6">
-        <f t="shared" si="25"/>
-        <v>70608.110087759997</v>
-      </c>
       <c r="AH27" s="6">
-        <f t="shared" si="25"/>
-        <v>71564.458449204016</v>
+        <f t="shared" ref="AH27:AR27" si="25">AH25+AH26</f>
+        <v>67877.565400000007</v>
       </c>
       <c r="AI27" s="6">
         <f t="shared" si="25"/>
-        <v>72537.87831207944</v>
+        <v>68641.874779999998</v>
       </c>
       <c r="AJ27" s="6">
         <f t="shared" si="25"/>
-        <v>73528.765631935137</v>
+        <v>70132.951196400012</v>
       </c>
       <c r="AK27" s="6">
         <f t="shared" si="25"/>
-        <v>74537.527081091423</v>
+        <v>71077.852885212007</v>
       </c>
       <c r="AL27" s="6">
         <f t="shared" si="25"/>
-        <v>75564.580358524385</v>
+        <v>72039.510756217569</v>
       </c>
       <c r="AM27" s="6">
         <f t="shared" si="25"/>
-        <v>76610.354508930337</v>
+        <v>73018.311586197786</v>
       </c>
       <c r="AN27" s="6">
         <f t="shared" si="25"/>
-        <v>77675.29025124498</v>
-      </c>
-    </row>
-    <row r="28" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
+        <v>74014.65259615035</v>
+      </c>
+      <c r="AO27" s="6">
+        <f t="shared" si="25"/>
+        <v>75028.941753025152</v>
+      </c>
+      <c r="AP27" s="6">
+        <f t="shared" si="25"/>
+        <v>76061.598080396114</v>
+      </c>
+      <c r="AQ27" s="6">
+        <f t="shared" si="25"/>
+        <v>77113.051978335992</v>
+      </c>
+      <c r="AR27" s="6">
+        <f t="shared" si="25"/>
+        <v>78183.745552769353</v>
+      </c>
+    </row>
+    <row r="28" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>12</v>
       </c>
@@ -2359,78 +2539,82 @@
       </c>
       <c r="V28" s="9">
         <f t="shared" si="33"/>
-        <v>2219.6460000000006</v>
-      </c>
-      <c r="X28" s="9">
-        <f t="shared" ref="X28:AC28" si="34">X24-X27</f>
+        <v>2322</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AB28" s="9">
+        <f t="shared" ref="AB28:AG28" si="34">AB24-AB27</f>
         <v>6492</v>
       </c>
-      <c r="Y28" s="9">
+      <c r="AC28" s="9">
         <f t="shared" si="34"/>
         <v>7031</v>
       </c>
-      <c r="Z28" s="9">
+      <c r="AD28" s="9">
         <f t="shared" si="34"/>
         <v>7308</v>
       </c>
-      <c r="AA28" s="9">
+      <c r="AE28" s="9">
         <f t="shared" si="34"/>
         <v>7375</v>
       </c>
-      <c r="AB28" s="9">
+      <c r="AF28" s="9">
         <f t="shared" si="34"/>
         <v>7338</v>
       </c>
-      <c r="AC28" s="9">
+      <c r="AG28" s="9">
         <f t="shared" si="34"/>
         <v>5974</v>
       </c>
-      <c r="AD28" s="9">
-        <f t="shared" ref="AD28:AN28" si="35">AD24-AD27</f>
-        <v>6844.6459999999934</v>
-      </c>
-      <c r="AE28" s="9">
-        <f t="shared" si="35"/>
-        <v>8578.1779999999999</v>
-      </c>
-      <c r="AF28" s="9">
-        <f t="shared" si="35"/>
-        <v>8765.8257120000053</v>
-      </c>
-      <c r="AG28" s="9">
-        <f t="shared" si="35"/>
-        <v>8886.6173222400103</v>
-      </c>
       <c r="AH28" s="9">
-        <f t="shared" si="35"/>
-        <v>9009.6108491759951</v>
+        <f t="shared" ref="AH28:AR28" si="35">AH24-AH27</f>
+        <v>6899.8545999999915</v>
       </c>
       <c r="AI28" s="9">
         <f t="shared" si="35"/>
-        <v>9134.8581319927762</v>
+        <v>8634.7962200000038</v>
       </c>
       <c r="AJ28" s="9">
         <f t="shared" si="35"/>
-        <v>9262.4124228674482</v>
+        <v>8823.6156335999985</v>
       </c>
       <c r="AK28" s="9">
         <f t="shared" si="35"/>
-        <v>9392.3284279375221</v>
+        <v>8945.0661776880006</v>
       </c>
       <c r="AL28" s="9">
         <f t="shared" si="35"/>
-        <v>9524.6623494835512</v>
+        <v>9068.7276588494278</v>
       </c>
       <c r="AM28" s="9">
         <f t="shared" si="35"/>
-        <v>9659.4719293630187</v>
+        <v>9194.6520794040262</v>
       </c>
       <c r="AN28" s="9">
         <f t="shared" si="35"/>
-        <v>9796.8164937328402</v>
-      </c>
-    </row>
-    <row r="29" spans="2:40" x14ac:dyDescent="0.3">
+        <v>9322.8928584831447</v>
+      </c>
+      <c r="AO28" s="9">
+        <f t="shared" si="35"/>
+        <v>9453.5048731016141</v>
+      </c>
+      <c r="AP28" s="9">
+        <f t="shared" si="35"/>
+        <v>9586.5445004472713</v>
+      </c>
+      <c r="AQ28" s="9">
+        <f t="shared" si="35"/>
+        <v>9722.06966142483</v>
+      </c>
+      <c r="AR28" s="9">
+        <f t="shared" si="35"/>
+        <v>9860.1398654913501</v>
+      </c>
+    </row>
+    <row r="29" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>39</v>
       </c>
@@ -2444,7 +2628,7 @@
       </c>
       <c r="Q29" s="6"/>
       <c r="R29" s="6">
-        <f t="shared" ref="R29:R31" si="36">AC29-Q29-P29-O29</f>
+        <f t="shared" ref="R29:R31" si="36">AG29-Q29-P29-O29</f>
         <v>0</v>
       </c>
       <c r="S29" s="6"/>
@@ -2454,73 +2638,77 @@
       <c r="U29" s="6">
         <v>0</v>
       </c>
-      <c r="V29" s="6">
+      <c r="V29" s="18">
         <v>0</v>
       </c>
-      <c r="X29" s="6">
+      <c r="W29" s="6"/>
+      <c r="X29" s="6"/>
+      <c r="Y29" s="6"/>
+      <c r="Z29" s="6"/>
+      <c r="AB29" s="6">
         <v>0</v>
       </c>
-      <c r="Y29" s="6">
+      <c r="AC29" s="6">
         <v>27</v>
       </c>
-      <c r="Z29" s="6">
+      <c r="AD29" s="6">
         <v>36</v>
       </c>
-      <c r="AA29" s="6">
+      <c r="AE29" s="6">
         <v>100</v>
       </c>
-      <c r="AB29" s="6">
+      <c r="AF29" s="6">
         <v>92</v>
       </c>
-      <c r="AC29" s="6">
+      <c r="AG29" s="6">
         <v>87</v>
       </c>
-      <c r="AD29" s="6">
+      <c r="AH29" s="6">
         <f>SUM(S29:V29)</f>
         <v>66</v>
       </c>
-      <c r="AE29" s="6">
-        <f t="shared" ref="AE29:AN29" si="37">AD29*1.03</f>
+      <c r="AI29" s="6">
+        <f t="shared" ref="AI29:AR29" si="37">AH29*1.03</f>
         <v>67.98</v>
       </c>
-      <c r="AF29" s="6">
+      <c r="AJ29" s="6">
         <f t="shared" si="37"/>
         <v>70.019400000000005</v>
       </c>
-      <c r="AG29" s="6">
+      <c r="AK29" s="6">
         <f t="shared" si="37"/>
         <v>72.119982000000007</v>
       </c>
-      <c r="AH29" s="6">
+      <c r="AL29" s="6">
         <f t="shared" si="37"/>
         <v>74.283581460000008</v>
       </c>
-      <c r="AI29" s="6">
+      <c r="AM29" s="6">
         <f t="shared" si="37"/>
         <v>76.512088903800006</v>
       </c>
-      <c r="AJ29" s="6">
+      <c r="AN29" s="6">
         <f t="shared" si="37"/>
         <v>78.807451570914012</v>
       </c>
-      <c r="AK29" s="6">
+      <c r="AO29" s="6">
         <f t="shared" si="37"/>
         <v>81.171675118041435</v>
       </c>
-      <c r="AL29" s="6">
+      <c r="AP29" s="6">
         <f t="shared" si="37"/>
         <v>83.606825371582687</v>
       </c>
-      <c r="AM29" s="6">
+      <c r="AQ29" s="6">
         <f t="shared" si="37"/>
         <v>86.115030132730169</v>
       </c>
-      <c r="AN29" s="6">
+      <c r="AR29" s="6">
         <f t="shared" si="37"/>
         <v>88.698481036712082</v>
       </c>
     </row>
-    <row r="30" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>38</v>
       </c>
@@ -2534,7 +2722,7 @@
         <v>-251</v>
       </c>
       <c r="N30" s="6">
-        <f t="shared" ref="N30:N31" si="38">AB30-M30-L30-K30</f>
+        <f t="shared" ref="N30:N31" si="38">AF30-M30-L30-K30</f>
         <v>-350</v>
       </c>
       <c r="O30" s="6">
@@ -2559,73 +2747,77 @@
       <c r="U30" s="6">
         <v>-210</v>
       </c>
-      <c r="V30" s="6">
+      <c r="V30" s="18">
         <v>-210</v>
       </c>
-      <c r="X30" s="6">
+      <c r="W30" s="6"/>
+      <c r="X30" s="6"/>
+      <c r="Y30" s="6"/>
+      <c r="Z30" s="6"/>
+      <c r="AB30" s="6">
         <v>-1875</v>
       </c>
-      <c r="Y30" s="6">
+      <c r="AC30" s="6">
         <v>-1650</v>
       </c>
-      <c r="Z30" s="6">
+      <c r="AD30" s="6">
         <v>-1789</v>
       </c>
-      <c r="AA30" s="6">
+      <c r="AE30" s="6">
         <v>-1012</v>
       </c>
-      <c r="AB30" s="6">
+      <c r="AF30" s="6">
         <v>-1233</v>
       </c>
-      <c r="AC30" s="6">
+      <c r="AG30" s="6">
         <v>-1043</v>
       </c>
-      <c r="AD30" s="6">
+      <c r="AH30" s="6">
         <f>SUM(S30:V30)</f>
         <v>-948</v>
       </c>
-      <c r="AE30" s="6">
-        <f t="shared" ref="AE30:AN30" si="39">AD30*1.01</f>
+      <c r="AI30" s="6">
+        <f t="shared" ref="AI30:AR30" si="39">AH30*1.01</f>
         <v>-957.48</v>
       </c>
-      <c r="AF30" s="6">
+      <c r="AJ30" s="6">
         <f t="shared" si="39"/>
         <v>-967.0548</v>
       </c>
-      <c r="AG30" s="6">
+      <c r="AK30" s="6">
         <f t="shared" si="39"/>
         <v>-976.72534800000005</v>
       </c>
-      <c r="AH30" s="6">
+      <c r="AL30" s="6">
         <f t="shared" si="39"/>
         <v>-986.49260148000008</v>
       </c>
-      <c r="AI30" s="6">
+      <c r="AM30" s="6">
         <f t="shared" si="39"/>
         <v>-996.35752749480014</v>
       </c>
-      <c r="AJ30" s="6">
+      <c r="AN30" s="6">
         <f t="shared" si="39"/>
         <v>-1006.3211027697481</v>
       </c>
-      <c r="AK30" s="6">
+      <c r="AO30" s="6">
         <f t="shared" si="39"/>
         <v>-1016.3843137974455</v>
       </c>
-      <c r="AL30" s="6">
+      <c r="AP30" s="6">
         <f t="shared" si="39"/>
         <v>-1026.5481569354199</v>
       </c>
-      <c r="AM30" s="6">
+      <c r="AQ30" s="6">
         <f t="shared" si="39"/>
         <v>-1036.8136385047742</v>
       </c>
-      <c r="AN30" s="6">
+      <c r="AR30" s="6">
         <f t="shared" si="39"/>
         <v>-1047.181774889822</v>
       </c>
     </row>
-    <row r="31" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>43</v>
       </c>
@@ -2664,73 +2856,77 @@
       <c r="U31" s="6">
         <v>-40</v>
       </c>
-      <c r="V31" s="6">
+      <c r="V31" s="18">
         <v>-40</v>
       </c>
-      <c r="X31" s="6">
+      <c r="W31" s="6"/>
+      <c r="X31" s="6"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="6"/>
+      <c r="AB31" s="6">
         <v>-178</v>
       </c>
-      <c r="Y31" s="6">
+      <c r="AC31" s="6">
         <v>10</v>
       </c>
-      <c r="Z31" s="6">
+      <c r="AD31" s="6">
         <v>-62</v>
       </c>
-      <c r="AA31" s="6">
+      <c r="AE31" s="6">
         <v>-61</v>
       </c>
-      <c r="AB31" s="6">
+      <c r="AF31" s="6">
         <v>-28</v>
       </c>
-      <c r="AC31" s="6">
+      <c r="AG31" s="6">
         <v>-83</v>
       </c>
-      <c r="AD31" s="6">
+      <c r="AH31" s="6">
         <f>SUM(S31:V31)</f>
         <v>-143</v>
       </c>
-      <c r="AE31" s="6">
-        <f t="shared" ref="AE31:AN31" si="40">AD31*1.01</f>
+      <c r="AI31" s="6">
+        <f t="shared" ref="AI31:AR31" si="40">AH31*1.01</f>
         <v>-144.43</v>
       </c>
-      <c r="AF31" s="6">
+      <c r="AJ31" s="6">
         <f t="shared" si="40"/>
         <v>-145.87430000000001</v>
       </c>
-      <c r="AG31" s="6">
+      <c r="AK31" s="6">
         <f t="shared" si="40"/>
         <v>-147.333043</v>
       </c>
-      <c r="AH31" s="6">
+      <c r="AL31" s="6">
         <f t="shared" si="40"/>
         <v>-148.80637343000001</v>
       </c>
-      <c r="AI31" s="6">
+      <c r="AM31" s="6">
         <f t="shared" si="40"/>
         <v>-150.29443716430001</v>
       </c>
-      <c r="AJ31" s="6">
+      <c r="AN31" s="6">
         <f t="shared" si="40"/>
         <v>-151.797381535943</v>
       </c>
-      <c r="AK31" s="6">
+      <c r="AO31" s="6">
         <f t="shared" si="40"/>
         <v>-153.31535535130243</v>
       </c>
-      <c r="AL31" s="6">
+      <c r="AP31" s="6">
         <f t="shared" si="40"/>
         <v>-154.84850890481545</v>
       </c>
-      <c r="AM31" s="6">
+      <c r="AQ31" s="6">
         <f t="shared" si="40"/>
         <v>-156.39699399386359</v>
       </c>
-      <c r="AN31" s="6">
+      <c r="AR31" s="6">
         <f t="shared" si="40"/>
         <v>-157.96096393380222</v>
       </c>
     </row>
-    <row r="32" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>48</v>
       </c>
@@ -2778,80 +2974,84 @@
         <f t="shared" ref="U32:V32" si="48">SUM(U29:U31)</f>
         <v>-250</v>
       </c>
-      <c r="V32" s="6">
+      <c r="V32" s="18">
         <f t="shared" si="48"/>
         <v>-250</v>
       </c>
-      <c r="X32" s="6">
-        <f t="shared" ref="X32:AC32" si="49">SUM(X29:X31)</f>
+      <c r="W32" s="6"/>
+      <c r="X32" s="6"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="6"/>
+      <c r="AB32" s="6">
+        <f t="shared" ref="AB32:AG32" si="49">SUM(AB29:AB31)</f>
         <v>-2053</v>
       </c>
-      <c r="Y32" s="6">
+      <c r="AC32" s="6">
         <f t="shared" si="49"/>
         <v>-1613</v>
       </c>
-      <c r="Z32" s="6">
+      <c r="AD32" s="6">
         <f t="shared" si="49"/>
         <v>-1815</v>
       </c>
-      <c r="AA32" s="6">
+      <c r="AE32" s="6">
         <f t="shared" si="49"/>
         <v>-973</v>
       </c>
-      <c r="AB32" s="6">
+      <c r="AF32" s="6">
         <f t="shared" si="49"/>
         <v>-1169</v>
       </c>
-      <c r="AC32" s="6">
+      <c r="AG32" s="6">
         <f t="shared" si="49"/>
         <v>-1039</v>
       </c>
-      <c r="AD32" s="6">
-        <f t="shared" ref="AD32:AN32" si="50">SUM(AD29:AD31)</f>
+      <c r="AH32" s="6">
+        <f t="shared" ref="AH32:AR32" si="50">SUM(AH29:AH31)</f>
         <v>-1025</v>
       </c>
-      <c r="AE32" s="6">
+      <c r="AI32" s="6">
         <f t="shared" si="50"/>
         <v>-1033.93</v>
       </c>
-      <c r="AF32" s="6">
+      <c r="AJ32" s="6">
         <f t="shared" si="50"/>
         <v>-1042.9096999999999</v>
       </c>
-      <c r="AG32" s="6">
+      <c r="AK32" s="6">
         <f t="shared" si="50"/>
         <v>-1051.9384090000001</v>
       </c>
-      <c r="AH32" s="6">
+      <c r="AL32" s="6">
         <f t="shared" si="50"/>
         <v>-1061.0153934499999</v>
       </c>
-      <c r="AI32" s="6">
+      <c r="AM32" s="6">
         <f t="shared" si="50"/>
         <v>-1070.1398757553002</v>
       </c>
-      <c r="AJ32" s="6">
+      <c r="AN32" s="6">
         <f t="shared" si="50"/>
         <v>-1079.311032734777</v>
       </c>
-      <c r="AK32" s="6">
+      <c r="AO32" s="6">
         <f t="shared" si="50"/>
         <v>-1088.5279940307066</v>
       </c>
-      <c r="AL32" s="6">
+      <c r="AP32" s="6">
         <f t="shared" si="50"/>
         <v>-1097.7898404686528</v>
       </c>
-      <c r="AM32" s="6">
+      <c r="AQ32" s="6">
         <f t="shared" si="50"/>
         <v>-1107.0956023659076</v>
       </c>
-      <c r="AN32" s="6">
+      <c r="AR32" s="6">
         <f t="shared" si="50"/>
         <v>-1116.4442577869122</v>
       </c>
     </row>
-    <row r="33" spans="2:138" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:142" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>40</v>
       </c>
@@ -2899,80 +3099,84 @@
         <f t="shared" ref="U33:V33" si="58">U28-U32</f>
         <v>2280</v>
       </c>
-      <c r="V33" s="9">
+      <c r="V33" s="19">
         <f t="shared" si="58"/>
-        <v>2469.6460000000006</v>
-      </c>
-      <c r="X33" s="9">
-        <f t="shared" ref="X33:AC33" si="59">X28-X32</f>
+        <v>2572</v>
+      </c>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="9"/>
+      <c r="AB33" s="9">
+        <f t="shared" ref="AB33:AG33" si="59">AB28-AB32</f>
         <v>8545</v>
       </c>
-      <c r="Y33" s="9">
+      <c r="AC33" s="9">
         <f t="shared" si="59"/>
         <v>8644</v>
       </c>
-      <c r="Z33" s="9">
+      <c r="AD33" s="9">
         <f t="shared" si="59"/>
         <v>9123</v>
       </c>
-      <c r="AA33" s="9">
+      <c r="AE33" s="9">
         <f t="shared" si="59"/>
         <v>8348</v>
       </c>
-      <c r="AB33" s="9">
+      <c r="AF33" s="9">
         <f t="shared" si="59"/>
         <v>8507</v>
       </c>
-      <c r="AC33" s="9">
+      <c r="AG33" s="9">
         <f t="shared" si="59"/>
         <v>7013</v>
       </c>
-      <c r="AD33" s="9">
-        <f t="shared" ref="AD33:AN33" si="60">AD28-AD32</f>
-        <v>7869.6459999999934</v>
-      </c>
-      <c r="AE33" s="9">
-        <f t="shared" si="60"/>
-        <v>9612.1080000000002</v>
-      </c>
-      <c r="AF33" s="9">
-        <f t="shared" si="60"/>
-        <v>9808.7354120000055</v>
-      </c>
-      <c r="AG33" s="9">
-        <f t="shared" si="60"/>
-        <v>9938.5557312400106</v>
-      </c>
       <c r="AH33" s="9">
-        <f t="shared" si="60"/>
-        <v>10070.626242625995</v>
+        <f t="shared" ref="AH33:AR33" si="60">AH28-AH32</f>
+        <v>7924.8545999999915</v>
       </c>
       <c r="AI33" s="9">
         <f t="shared" si="60"/>
-        <v>10204.998007748076</v>
+        <v>9668.7262200000041</v>
       </c>
       <c r="AJ33" s="9">
         <f t="shared" si="60"/>
-        <v>10341.723455602225</v>
+        <v>9866.5253335999987</v>
       </c>
       <c r="AK33" s="9">
         <f t="shared" si="60"/>
-        <v>10480.856421968228</v>
+        <v>9997.0045866880009</v>
       </c>
       <c r="AL33" s="9">
         <f t="shared" si="60"/>
-        <v>10622.452189952204</v>
+        <v>10129.743052299427</v>
       </c>
       <c r="AM33" s="9">
         <f t="shared" si="60"/>
-        <v>10766.567531728926</v>
+        <v>10264.791955159326</v>
       </c>
       <c r="AN33" s="9">
         <f t="shared" si="60"/>
-        <v>10913.260751519752</v>
-      </c>
-    </row>
-    <row r="34" spans="2:138" x14ac:dyDescent="0.3">
+        <v>10402.203891217921</v>
+      </c>
+      <c r="AO33" s="9">
+        <f t="shared" si="60"/>
+        <v>10542.03286713232</v>
+      </c>
+      <c r="AP33" s="9">
+        <f t="shared" si="60"/>
+        <v>10684.334340915924</v>
+      </c>
+      <c r="AQ33" s="9">
+        <f t="shared" si="60"/>
+        <v>10829.165263790737</v>
+      </c>
+      <c r="AR33" s="9">
+        <f t="shared" si="60"/>
+        <v>10976.584123278262</v>
+      </c>
+    </row>
+    <row r="34" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>41</v>
       </c>
@@ -2986,7 +3190,7 @@
         <v>237</v>
       </c>
       <c r="N34" s="6">
-        <f t="shared" ref="N34:N36" si="61">AB34-M34-L34-K34</f>
+        <f t="shared" ref="N34:N36" si="61">AF34-M34-L34-K34</f>
         <v>254</v>
       </c>
       <c r="O34" s="6">
@@ -2999,7 +3203,7 @@
         <v>256</v>
       </c>
       <c r="R34" s="6">
-        <f t="shared" ref="R34:R36" si="62">AC34-Q34-P34-O34</f>
+        <f t="shared" ref="R34:R36" si="62">AG34-Q34-P34-O34</f>
         <v>264</v>
       </c>
       <c r="S34" s="6">
@@ -3011,73 +3215,77 @@
       <c r="U34" s="6">
         <v>286</v>
       </c>
-      <c r="V34" s="6">
+      <c r="V34" s="18">
         <v>286</v>
       </c>
-      <c r="X34" s="6">
+      <c r="W34" s="6"/>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6"/>
+      <c r="AB34" s="6">
         <v>653</v>
       </c>
-      <c r="Y34" s="6">
+      <c r="AC34" s="6">
         <v>591</v>
       </c>
-      <c r="Z34" s="6">
+      <c r="AD34" s="6">
         <v>569</v>
       </c>
-      <c r="AA34" s="6">
+      <c r="AE34" s="6">
         <v>623</v>
       </c>
-      <c r="AB34" s="6">
+      <c r="AF34" s="6">
         <v>916</v>
       </c>
-      <c r="AC34" s="6">
+      <c r="AG34" s="6">
         <v>1036</v>
       </c>
-      <c r="AD34" s="6">
-        <f t="shared" ref="AD34:AD36" si="63">SUM(S34:V34)</f>
+      <c r="AH34" s="6">
+        <f t="shared" ref="AH34:AH36" si="63">SUM(S34:V34)</f>
         <v>1114</v>
       </c>
-      <c r="AE34" s="6">
-        <f t="shared" ref="AE34:AN34" si="64">AD34*1.01</f>
+      <c r="AI34" s="6">
+        <f t="shared" ref="AI34:AR34" si="64">AH34*1.01</f>
         <v>1125.1400000000001</v>
       </c>
-      <c r="AF34" s="6">
+      <c r="AJ34" s="6">
         <f t="shared" si="64"/>
         <v>1136.3914000000002</v>
       </c>
-      <c r="AG34" s="6">
+      <c r="AK34" s="6">
         <f t="shared" si="64"/>
         <v>1147.7553140000002</v>
       </c>
-      <c r="AH34" s="6">
+      <c r="AL34" s="6">
         <f t="shared" si="64"/>
         <v>1159.2328671400003</v>
       </c>
-      <c r="AI34" s="6">
+      <c r="AM34" s="6">
         <f t="shared" si="64"/>
         <v>1170.8251958114004</v>
       </c>
-      <c r="AJ34" s="6">
+      <c r="AN34" s="6">
         <f t="shared" si="64"/>
         <v>1182.5334477695144</v>
       </c>
-      <c r="AK34" s="6">
+      <c r="AO34" s="6">
         <f t="shared" si="64"/>
         <v>1194.3587822472095</v>
       </c>
-      <c r="AL34" s="6">
+      <c r="AP34" s="6">
         <f t="shared" si="64"/>
         <v>1206.3023700696817</v>
       </c>
-      <c r="AM34" s="6">
+      <c r="AQ34" s="6">
         <f t="shared" si="64"/>
         <v>1218.3653937703787</v>
       </c>
-      <c r="AN34" s="6">
+      <c r="AR34" s="6">
         <f t="shared" si="64"/>
         <v>1230.5490477080825</v>
       </c>
     </row>
-    <row r="35" spans="2:138" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>42</v>
       </c>
@@ -3116,43 +3324,35 @@
       <c r="U35" s="6">
         <v>99</v>
       </c>
-      <c r="V35" s="6">
+      <c r="V35" s="18">
         <v>99</v>
       </c>
-      <c r="X35" s="6">
+      <c r="W35" s="6"/>
+      <c r="X35" s="6"/>
+      <c r="Y35" s="6"/>
+      <c r="Z35" s="6"/>
+      <c r="AB35" s="6">
         <v>577</v>
       </c>
-      <c r="Y35" s="6">
+      <c r="AC35" s="6">
         <v>-219</v>
       </c>
-      <c r="Z35" s="6">
+      <c r="AD35" s="6">
         <v>1292</v>
       </c>
-      <c r="AA35" s="6">
+      <c r="AE35" s="6">
         <v>971</v>
       </c>
-      <c r="AB35" s="6">
+      <c r="AF35" s="6">
         <v>-443</v>
       </c>
-      <c r="AC35" s="6">
+      <c r="AG35" s="6">
         <v>-62</v>
       </c>
-      <c r="AD35" s="6">
+      <c r="AH35" s="6">
         <f t="shared" si="63"/>
         <v>395</v>
       </c>
-      <c r="AE35" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="6">
-        <v>0</v>
-      </c>
       <c r="AI35" s="6">
         <v>0</v>
       </c>
@@ -3171,8 +3371,20 @@
       <c r="AN35" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="2:138" x14ac:dyDescent="0.3">
+      <c r="AO35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR35" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>43</v>
       </c>
@@ -3211,43 +3423,35 @@
       <c r="U36" s="6">
         <v>-43</v>
       </c>
-      <c r="V36" s="6">
+      <c r="V36" s="18">
         <v>-43</v>
       </c>
-      <c r="X36" s="6">
+      <c r="W36" s="6"/>
+      <c r="X36" s="6"/>
+      <c r="Y36" s="6"/>
+      <c r="Z36" s="6"/>
+      <c r="AB36" s="6">
         <v>74</v>
       </c>
-      <c r="Y36" s="6">
+      <c r="AC36" s="6">
         <v>37</v>
       </c>
-      <c r="Z36" s="6">
+      <c r="AD36" s="6">
         <v>-288</v>
       </c>
-      <c r="AA36" s="6">
+      <c r="AE36" s="6">
         <v>74</v>
       </c>
-      <c r="AB36" s="6">
+      <c r="AF36" s="6">
         <v>-64</v>
       </c>
-      <c r="AC36" s="6">
+      <c r="AG36" s="6">
         <v>-181</v>
       </c>
-      <c r="AD36" s="6">
+      <c r="AH36" s="6">
         <f t="shared" si="63"/>
         <v>-158</v>
       </c>
-      <c r="AE36" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG36" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="6">
-        <v>0</v>
-      </c>
       <c r="AI36" s="6">
         <v>0</v>
       </c>
@@ -3266,8 +3470,20 @@
       <c r="AN36" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:138" x14ac:dyDescent="0.3">
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR36" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>49</v>
       </c>
@@ -3315,80 +3531,84 @@
         <f t="shared" ref="U37:V37" si="72">SUM(U34:U36)</f>
         <v>342</v>
       </c>
-      <c r="V37" s="6">
+      <c r="V37" s="18">
         <f t="shared" si="72"/>
         <v>342</v>
       </c>
-      <c r="X37" s="6">
-        <f t="shared" ref="X37:AC37" si="73">SUM(X34:X36)</f>
+      <c r="W37" s="6"/>
+      <c r="X37" s="6"/>
+      <c r="Y37" s="6"/>
+      <c r="Z37" s="6"/>
+      <c r="AB37" s="6">
+        <f t="shared" ref="AB37:AG37" si="73">SUM(AB34:AB36)</f>
         <v>1304</v>
       </c>
-      <c r="Y37" s="6">
+      <c r="AC37" s="6">
         <f t="shared" si="73"/>
         <v>409</v>
       </c>
-      <c r="Z37" s="6">
+      <c r="AD37" s="6">
         <f t="shared" si="73"/>
         <v>1573</v>
       </c>
-      <c r="AA37" s="6">
+      <c r="AE37" s="6">
         <f t="shared" si="73"/>
         <v>1668</v>
       </c>
-      <c r="AB37" s="6">
+      <c r="AF37" s="6">
         <f t="shared" si="73"/>
         <v>409</v>
       </c>
-      <c r="AC37" s="6">
+      <c r="AG37" s="6">
         <f t="shared" si="73"/>
         <v>793</v>
       </c>
-      <c r="AD37" s="6">
-        <f t="shared" ref="AD37:AN37" si="74">SUM(AD34:AD36)</f>
+      <c r="AH37" s="6">
+        <f t="shared" ref="AH37:AR37" si="74">SUM(AH34:AH36)</f>
         <v>1351</v>
       </c>
-      <c r="AE37" s="6">
+      <c r="AI37" s="6">
         <f t="shared" si="74"/>
         <v>1125.1400000000001</v>
       </c>
-      <c r="AF37" s="6">
+      <c r="AJ37" s="6">
         <f t="shared" si="74"/>
         <v>1136.3914000000002</v>
       </c>
-      <c r="AG37" s="6">
+      <c r="AK37" s="6">
         <f t="shared" si="74"/>
         <v>1147.7553140000002</v>
       </c>
-      <c r="AH37" s="6">
+      <c r="AL37" s="6">
         <f t="shared" si="74"/>
         <v>1159.2328671400003</v>
       </c>
-      <c r="AI37" s="6">
+      <c r="AM37" s="6">
         <f t="shared" si="74"/>
         <v>1170.8251958114004</v>
       </c>
-      <c r="AJ37" s="6">
+      <c r="AN37" s="6">
         <f t="shared" si="74"/>
         <v>1182.5334477695144</v>
       </c>
-      <c r="AK37" s="6">
+      <c r="AO37" s="6">
         <f t="shared" si="74"/>
         <v>1194.3587822472095</v>
       </c>
-      <c r="AL37" s="6">
+      <c r="AP37" s="6">
         <f t="shared" si="74"/>
         <v>1206.3023700696817</v>
       </c>
-      <c r="AM37" s="6">
+      <c r="AQ37" s="6">
         <f t="shared" si="74"/>
         <v>1218.3653937703787</v>
       </c>
-      <c r="AN37" s="6">
+      <c r="AR37" s="6">
         <f t="shared" si="74"/>
         <v>1230.5490477080825</v>
       </c>
     </row>
-    <row r="38" spans="2:138" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:142" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>44</v>
       </c>
@@ -3436,80 +3656,84 @@
         <f t="shared" ref="U38:V38" si="82">U33-U37</f>
         <v>1938</v>
       </c>
-      <c r="V38" s="9">
+      <c r="V38" s="19">
         <f t="shared" si="82"/>
-        <v>2127.6460000000006</v>
-      </c>
-      <c r="X38" s="9">
-        <f t="shared" ref="X38:AC38" si="83">X33-X37</f>
+        <v>2230</v>
+      </c>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="9"/>
+      <c r="AB38" s="9">
+        <f t="shared" ref="AB38:AG38" si="83">AB33-AB37</f>
         <v>7241</v>
       </c>
-      <c r="Y38" s="9">
+      <c r="AC38" s="9">
         <f t="shared" si="83"/>
         <v>8235</v>
       </c>
-      <c r="Z38" s="9">
+      <c r="AD38" s="9">
         <f t="shared" si="83"/>
         <v>7550</v>
       </c>
-      <c r="AA38" s="9">
+      <c r="AE38" s="9">
         <f t="shared" si="83"/>
         <v>6680</v>
       </c>
-      <c r="AB38" s="9">
+      <c r="AF38" s="9">
         <f t="shared" si="83"/>
         <v>8098</v>
       </c>
-      <c r="AC38" s="9">
+      <c r="AG38" s="9">
         <f t="shared" si="83"/>
         <v>6220</v>
       </c>
-      <c r="AD38" s="9">
-        <f t="shared" ref="AD38:AN38" si="84">AD33-AD37</f>
-        <v>6518.6459999999934</v>
-      </c>
-      <c r="AE38" s="9">
-        <f t="shared" si="84"/>
-        <v>8486.9680000000008</v>
-      </c>
-      <c r="AF38" s="9">
-        <f t="shared" si="84"/>
-        <v>8672.344012000005</v>
-      </c>
-      <c r="AG38" s="9">
-        <f t="shared" si="84"/>
-        <v>8790.8004172400106</v>
-      </c>
       <c r="AH38" s="9">
-        <f t="shared" si="84"/>
-        <v>8911.3933754859936</v>
+        <f t="shared" ref="AH38:AR38" si="84">AH33-AH37</f>
+        <v>6573.8545999999915</v>
       </c>
       <c r="AI38" s="9">
         <f t="shared" si="84"/>
-        <v>9034.1728119366762</v>
+        <v>8543.5862200000047</v>
       </c>
       <c r="AJ38" s="9">
         <f t="shared" si="84"/>
-        <v>9159.1900078327108</v>
+        <v>8730.1339335999983</v>
       </c>
       <c r="AK38" s="9">
         <f t="shared" si="84"/>
-        <v>9286.4976397210194</v>
+        <v>8849.2492726880009</v>
       </c>
       <c r="AL38" s="9">
         <f t="shared" si="84"/>
-        <v>9416.1498198825229</v>
+        <v>8970.5101851594263</v>
       </c>
       <c r="AM38" s="9">
         <f t="shared" si="84"/>
-        <v>9548.2021379585476</v>
+        <v>9093.9667593479262</v>
       </c>
       <c r="AN38" s="9">
         <f t="shared" si="84"/>
-        <v>9682.7117038116703</v>
-      </c>
-    </row>
-    <row r="39" spans="2:138" x14ac:dyDescent="0.3">
+        <v>9219.6704434484072</v>
+      </c>
+      <c r="AO38" s="9">
+        <f t="shared" si="84"/>
+        <v>9347.6740848851114</v>
+      </c>
+      <c r="AP38" s="9">
+        <f t="shared" si="84"/>
+        <v>9478.031970846243</v>
+      </c>
+      <c r="AQ38" s="9">
+        <f t="shared" si="84"/>
+        <v>9610.7998700203589</v>
+      </c>
+      <c r="AR38" s="9">
+        <f t="shared" si="84"/>
+        <v>9746.0350755701802</v>
+      </c>
+    </row>
+    <row r="39" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
         <v>45</v>
       </c>
@@ -3523,7 +3747,7 @@
         <v>269</v>
       </c>
       <c r="N39" s="6">
-        <f>AB39-M39-L39-K39</f>
+        <f>AF39-M39-L39-K39</f>
         <v>279</v>
       </c>
       <c r="O39" s="6">
@@ -3536,7 +3760,7 @@
         <v>295</v>
       </c>
       <c r="R39" s="6">
-        <f>AC39-Q39-P39-O39</f>
+        <f>AG39-Q39-P39-O39</f>
         <v>-8</v>
       </c>
       <c r="S39" s="6">
@@ -3548,73 +3772,77 @@
       <c r="U39" s="6">
         <v>319</v>
       </c>
-      <c r="V39" s="6">
+      <c r="V39" s="18">
         <v>319</v>
       </c>
-      <c r="X39" s="6">
+      <c r="W39" s="6"/>
+      <c r="X39" s="6"/>
+      <c r="Y39" s="6"/>
+      <c r="Z39" s="6"/>
+      <c r="AB39" s="6">
         <v>1011</v>
       </c>
-      <c r="Y39" s="6">
+      <c r="AC39" s="6">
         <v>1347</v>
       </c>
-      <c r="Z39" s="6">
+      <c r="AD39" s="6">
         <v>1235</v>
       </c>
-      <c r="AA39" s="6">
+      <c r="AE39" s="6">
         <v>948</v>
       </c>
-      <c r="AB39" s="6">
+      <c r="AF39" s="6">
         <v>1178</v>
       </c>
-      <c r="AC39" s="6">
+      <c r="AG39" s="6">
         <v>884</v>
       </c>
-      <c r="AD39" s="6">
+      <c r="AH39" s="6">
         <f>SUM(S39:V39)</f>
         <v>1037</v>
       </c>
-      <c r="AE39" s="6">
-        <f t="shared" ref="AE39:AN39" si="85">AE38*0.15</f>
-        <v>1273.0452</v>
-      </c>
-      <c r="AF39" s="6">
-        <f t="shared" si="85"/>
-        <v>1300.8516018000007</v>
-      </c>
-      <c r="AG39" s="6">
-        <f t="shared" si="85"/>
-        <v>1318.6200625860015</v>
-      </c>
-      <c r="AH39" s="6">
-        <f t="shared" si="85"/>
-        <v>1336.7090063228991</v>
-      </c>
       <c r="AI39" s="6">
-        <f t="shared" si="85"/>
-        <v>1355.1259217905015</v>
+        <f t="shared" ref="AI39:AR39" si="85">AI38*0.15</f>
+        <v>1281.5379330000007</v>
       </c>
       <c r="AJ39" s="6">
         <f t="shared" si="85"/>
-        <v>1373.8785011749067</v>
+        <v>1309.5200900399998</v>
       </c>
       <c r="AK39" s="6">
         <f t="shared" si="85"/>
-        <v>1392.9746459581529</v>
+        <v>1327.3873909032002</v>
       </c>
       <c r="AL39" s="6">
         <f t="shared" si="85"/>
-        <v>1412.4224729823784</v>
+        <v>1345.576527773914</v>
       </c>
       <c r="AM39" s="6">
         <f t="shared" si="85"/>
-        <v>1432.230320693782</v>
+        <v>1364.0950139021888</v>
       </c>
       <c r="AN39" s="6">
         <f t="shared" si="85"/>
-        <v>1452.4067555717504</v>
-      </c>
-    </row>
-    <row r="40" spans="2:138" s="3" customFormat="1" x14ac:dyDescent="0.3">
+        <v>1382.950566517261</v>
+      </c>
+      <c r="AO39" s="6">
+        <f t="shared" si="85"/>
+        <v>1402.1511127327667</v>
+      </c>
+      <c r="AP39" s="6">
+        <f t="shared" si="85"/>
+        <v>1421.7047956269364</v>
+      </c>
+      <c r="AQ39" s="6">
+        <f t="shared" si="85"/>
+        <v>1441.6199805030537</v>
+      </c>
+      <c r="AR39" s="6">
+        <f t="shared" si="85"/>
+        <v>1461.905261335527</v>
+      </c>
+    </row>
+    <row r="40" spans="2:142" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
         <v>46</v>
       </c>
@@ -3662,472 +3890,478 @@
         <f t="shared" ref="U40:V40" si="93">U38-U39</f>
         <v>1619</v>
       </c>
-      <c r="V40" s="9">
+      <c r="V40" s="19">
         <f t="shared" si="93"/>
-        <v>1808.6460000000006</v>
-      </c>
-      <c r="X40" s="9">
-        <f t="shared" ref="X40:AC40" si="94">X38-X39</f>
+        <v>1911</v>
+      </c>
+      <c r="W40" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="X40" s="9"/>
+      <c r="Y40" s="9"/>
+      <c r="Z40" s="9"/>
+      <c r="AB40" s="9">
+        <f t="shared" ref="AB40:AG40" si="94">AB38-AB39</f>
         <v>6230</v>
       </c>
-      <c r="Y40" s="9">
+      <c r="AC40" s="9">
         <f t="shared" si="94"/>
         <v>6888</v>
       </c>
-      <c r="Z40" s="9">
+      <c r="AD40" s="9">
         <f t="shared" si="94"/>
         <v>6315</v>
       </c>
-      <c r="AA40" s="9">
+      <c r="AE40" s="9">
         <f t="shared" si="94"/>
         <v>5732</v>
       </c>
-      <c r="AB40" s="9">
+      <c r="AF40" s="9">
         <f t="shared" si="94"/>
         <v>6920</v>
       </c>
-      <c r="AC40" s="9">
+      <c r="AG40" s="9">
         <f t="shared" si="94"/>
         <v>5336</v>
       </c>
-      <c r="AD40" s="9">
-        <f t="shared" ref="AD40:AN40" si="95">AD38-AD39</f>
-        <v>5481.6459999999934</v>
-      </c>
-      <c r="AE40" s="9">
-        <f t="shared" si="95"/>
-        <v>7213.9228000000003</v>
-      </c>
-      <c r="AF40" s="9">
-        <f t="shared" si="95"/>
-        <v>7371.4924102000041</v>
-      </c>
-      <c r="AG40" s="9">
-        <f t="shared" si="95"/>
-        <v>7472.1803546540086</v>
-      </c>
       <c r="AH40" s="9">
-        <f t="shared" si="95"/>
-        <v>7574.6843691630947</v>
+        <f t="shared" ref="AH40:AR40" si="95">AH38-AH39</f>
+        <v>5536.8545999999915</v>
       </c>
       <c r="AI40" s="9">
         <f t="shared" si="95"/>
-        <v>7679.0468901461745</v>
+        <v>7262.0482870000042</v>
       </c>
       <c r="AJ40" s="9">
         <f t="shared" si="95"/>
-        <v>7785.3115066578039</v>
+        <v>7420.6138435599987</v>
       </c>
       <c r="AK40" s="9">
         <f t="shared" si="95"/>
-        <v>7893.5229937628665</v>
+        <v>7521.861881784801</v>
       </c>
       <c r="AL40" s="9">
         <f t="shared" si="95"/>
-        <v>8003.7273469001448</v>
+        <v>7624.9336573855126</v>
       </c>
       <c r="AM40" s="9">
         <f t="shared" si="95"/>
-        <v>8115.9718172647654</v>
+        <v>7729.8717454457374</v>
       </c>
       <c r="AN40" s="9">
         <f t="shared" si="95"/>
-        <v>8230.3049482399201</v>
-      </c>
-      <c r="AO40" s="3">
-        <f>AN40*(1+$AQ$50)</f>
-        <v>8148.0018987575204</v>
-      </c>
-      <c r="AP40" s="3">
-        <f t="shared" ref="AP40:DA40" si="96">AO40*(1+$AQ$50)</f>
-        <v>8066.5218797699454</v>
-      </c>
-      <c r="AQ40" s="3">
-        <f t="shared" si="96"/>
-        <v>7985.8566609722457</v>
-      </c>
-      <c r="AR40" s="3">
-        <f t="shared" si="96"/>
-        <v>7905.9980943625233</v>
+        <v>7836.7198769311462</v>
+      </c>
+      <c r="AO40" s="9">
+        <f t="shared" si="95"/>
+        <v>7945.5229721523447</v>
+      </c>
+      <c r="AP40" s="9">
+        <f t="shared" si="95"/>
+        <v>8056.3271752193068</v>
+      </c>
+      <c r="AQ40" s="9">
+        <f t="shared" si="95"/>
+        <v>8169.1798895173051</v>
+      </c>
+      <c r="AR40" s="9">
+        <f t="shared" si="95"/>
+        <v>8284.1298142346532</v>
       </c>
       <c r="AS40" s="3">
-        <f t="shared" si="96"/>
-        <v>7826.938113418898</v>
+        <f>AR40*(1+$AU$50)</f>
+        <v>8201.288516092307</v>
       </c>
       <c r="AT40" s="3">
-        <f t="shared" si="96"/>
-        <v>7748.6687322847092</v>
+        <f t="shared" ref="AT40:DE40" si="96">AS40*(1+$AU$50)</f>
+        <v>8119.2756309313836</v>
       </c>
       <c r="AU40" s="3">
         <f t="shared" si="96"/>
-        <v>7671.1820449618617</v>
+        <v>8038.0828746220695</v>
       </c>
       <c r="AV40" s="3">
         <f t="shared" si="96"/>
-        <v>7594.4702245122435</v>
+        <v>7957.7020458758489</v>
       </c>
       <c r="AW40" s="3">
         <f t="shared" si="96"/>
-        <v>7518.5255222671212</v>
+        <v>7878.12502541709</v>
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="96"/>
-        <v>7443.3402670444502</v>
+        <v>7799.343775162919</v>
       </c>
       <c r="AY40" s="3">
         <f t="shared" si="96"/>
-        <v>7368.9068643740056</v>
+        <v>7721.3503374112897</v>
       </c>
       <c r="AZ40" s="3">
         <f t="shared" si="96"/>
-        <v>7295.2177957302656</v>
+        <v>7644.1368340371764</v>
       </c>
       <c r="BA40" s="3">
         <f t="shared" si="96"/>
-        <v>7222.2656177729632</v>
+        <v>7567.6954656968046</v>
       </c>
       <c r="BB40" s="3">
         <f t="shared" si="96"/>
-        <v>7150.0429615952335</v>
+        <v>7492.0185110398361</v>
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="96"/>
-        <v>7078.5425319792812</v>
+        <v>7417.098325929438</v>
       </c>
       <c r="BD40" s="3">
         <f t="shared" si="96"/>
-        <v>7007.7571066594883</v>
+        <v>7342.9273426701438</v>
       </c>
       <c r="BE40" s="3">
         <f t="shared" si="96"/>
-        <v>6937.6795355928934</v>
+        <v>7269.4980692434419</v>
       </c>
       <c r="BF40" s="3">
         <f t="shared" si="96"/>
-        <v>6868.3027402369644</v>
+        <v>7196.803088551007</v>
       </c>
       <c r="BG40" s="3">
         <f t="shared" si="96"/>
-        <v>6799.6197128345948</v>
+        <v>7124.8350576654966</v>
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="96"/>
-        <v>6731.6235157062492</v>
+        <v>7053.5867070888416</v>
       </c>
       <c r="BI40" s="3">
         <f t="shared" si="96"/>
-        <v>6664.3072805491865</v>
+        <v>6983.0508400179533</v>
       </c>
       <c r="BJ40" s="3">
         <f t="shared" si="96"/>
-        <v>6597.6642077436945</v>
+        <v>6913.2203316177738</v>
       </c>
       <c r="BK40" s="3">
         <f t="shared" si="96"/>
-        <v>6531.6875656662578</v>
+        <v>6844.088128301596</v>
       </c>
       <c r="BL40" s="3">
         <f t="shared" si="96"/>
-        <v>6466.3706900095949</v>
+        <v>6775.6472470185799</v>
       </c>
       <c r="BM40" s="3">
         <f t="shared" si="96"/>
-        <v>6401.7069831094987</v>
+        <v>6707.8907745483939</v>
       </c>
       <c r="BN40" s="3">
         <f t="shared" si="96"/>
-        <v>6337.6899132784038</v>
+        <v>6640.8118668029101</v>
       </c>
       <c r="BO40" s="3">
         <f t="shared" si="96"/>
-        <v>6274.3130141456195</v>
+        <v>6574.4037481348805</v>
       </c>
       <c r="BP40" s="3">
         <f t="shared" si="96"/>
-        <v>6211.5698840041632</v>
+        <v>6508.6597106535319</v>
       </c>
       <c r="BQ40" s="3">
         <f t="shared" si="96"/>
-        <v>6149.4541851641216</v>
+        <v>6443.5731135469969</v>
       </c>
       <c r="BR40" s="3">
         <f t="shared" si="96"/>
-        <v>6087.9596433124807</v>
+        <v>6379.1373824115271</v>
       </c>
       <c r="BS40" s="3">
         <f t="shared" si="96"/>
-        <v>6027.0800468793559</v>
+        <v>6315.3460085874121</v>
       </c>
       <c r="BT40" s="3">
         <f t="shared" si="96"/>
-        <v>5966.8092464105621</v>
+        <v>6252.1925485015381</v>
       </c>
       <c r="BU40" s="3">
         <f t="shared" si="96"/>
-        <v>5907.1411539464561</v>
+        <v>6189.6706230165228</v>
       </c>
       <c r="BV40" s="3">
         <f t="shared" si="96"/>
-        <v>5848.0697424069913</v>
+        <v>6127.7739167863574</v>
       </c>
       <c r="BW40" s="3">
         <f t="shared" si="96"/>
-        <v>5789.5890449829212</v>
+        <v>6066.4961776184937</v>
       </c>
       <c r="BX40" s="3">
         <f t="shared" si="96"/>
-        <v>5731.6931545330917</v>
+        <v>6005.8312158423087</v>
       </c>
       <c r="BY40" s="3">
         <f t="shared" si="96"/>
-        <v>5674.3762229877611</v>
+        <v>5945.7729036838855</v>
       </c>
       <c r="BZ40" s="3">
         <f t="shared" si="96"/>
-        <v>5617.6324607578836</v>
+        <v>5886.3151746470467</v>
       </c>
       <c r="CA40" s="3">
         <f t="shared" si="96"/>
-        <v>5561.4561361503047</v>
+        <v>5827.4520229005766</v>
       </c>
       <c r="CB40" s="3">
         <f t="shared" si="96"/>
-        <v>5505.8415747888012</v>
+        <v>5769.1775026715704</v>
       </c>
       <c r="CC40" s="3">
         <f t="shared" si="96"/>
-        <v>5450.7831590409132</v>
+        <v>5711.4857276448547</v>
       </c>
       <c r="CD40" s="3">
         <f t="shared" si="96"/>
-        <v>5396.2753274505039</v>
+        <v>5654.370870368406</v>
       </c>
       <c r="CE40" s="3">
         <f t="shared" si="96"/>
-        <v>5342.3125741759986</v>
+        <v>5597.8271616647216</v>
       </c>
       <c r="CF40" s="3">
         <f t="shared" si="96"/>
-        <v>5288.8894484342381</v>
+        <v>5541.8488900480743</v>
       </c>
       <c r="CG40" s="3">
         <f t="shared" si="96"/>
-        <v>5236.0005539498961</v>
+        <v>5486.4304011475933</v>
       </c>
       <c r="CH40" s="3">
         <f t="shared" si="96"/>
-        <v>5183.6405484103971</v>
+        <v>5431.5660971361176</v>
       </c>
       <c r="CI40" s="3">
         <f t="shared" si="96"/>
-        <v>5131.804142926293</v>
+        <v>5377.2504361647561</v>
       </c>
       <c r="CJ40" s="3">
         <f t="shared" si="96"/>
-        <v>5080.4861014970302</v>
+        <v>5323.4779318031087</v>
       </c>
       <c r="CK40" s="3">
         <f t="shared" si="96"/>
-        <v>5029.6812404820603</v>
+        <v>5270.2431524850772</v>
       </c>
       <c r="CL40" s="3">
         <f t="shared" si="96"/>
-        <v>4979.38442807724</v>
+        <v>5217.5407209602263</v>
       </c>
       <c r="CM40" s="3">
         <f t="shared" si="96"/>
-        <v>4929.5905837964674</v>
+        <v>5165.3653137506244</v>
       </c>
       <c r="CN40" s="3">
         <f t="shared" si="96"/>
-        <v>4880.2946779585027</v>
+        <v>5113.7116606131185</v>
       </c>
       <c r="CO40" s="3">
         <f t="shared" si="96"/>
-        <v>4831.4917311789177</v>
+        <v>5062.5745440069877</v>
       </c>
       <c r="CP40" s="3">
         <f t="shared" si="96"/>
-        <v>4783.1768138671287</v>
+        <v>5011.9487985669175</v>
       </c>
       <c r="CQ40" s="3">
         <f t="shared" si="96"/>
-        <v>4735.3450457284571</v>
+        <v>4961.8293105812481</v>
       </c>
       <c r="CR40" s="3">
         <f t="shared" si="96"/>
-        <v>4687.9915952711726</v>
+        <v>4912.2110174754353</v>
       </c>
       <c r="CS40" s="3">
         <f t="shared" si="96"/>
-        <v>4641.111679318461</v>
+        <v>4863.0889073006811</v>
       </c>
       <c r="CT40" s="3">
         <f t="shared" si="96"/>
-        <v>4594.7005625252759</v>
+        <v>4814.4580182276741</v>
       </c>
       <c r="CU40" s="3">
         <f t="shared" si="96"/>
-        <v>4548.7535569000229</v>
+        <v>4766.3134380453976</v>
       </c>
       <c r="CV40" s="3">
         <f t="shared" si="96"/>
-        <v>4503.2660213310228</v>
+        <v>4718.6503036649437</v>
       </c>
       <c r="CW40" s="3">
         <f t="shared" si="96"/>
-        <v>4458.2333611177128</v>
+        <v>4671.4638006282939</v>
       </c>
       <c r="CX40" s="3">
         <f t="shared" si="96"/>
-        <v>4413.6510275065357</v>
+        <v>4624.7491626220108</v>
       </c>
       <c r="CY40" s="3">
         <f t="shared" si="96"/>
-        <v>4369.5145172314706</v>
+        <v>4578.5016709957908</v>
       </c>
       <c r="CZ40" s="3">
         <f t="shared" si="96"/>
-        <v>4325.8193720591562</v>
+        <v>4532.7166542858331</v>
       </c>
       <c r="DA40" s="3">
         <f t="shared" si="96"/>
-        <v>4282.5611783385648</v>
+        <v>4487.3894877429748</v>
       </c>
       <c r="DB40" s="3">
-        <f t="shared" ref="DB40:EH40" si="97">DA40*(1+$AQ$50)</f>
-        <v>4239.7355665551795</v>
+        <f t="shared" si="96"/>
+        <v>4442.5155928655449</v>
       </c>
       <c r="DC40" s="3">
-        <f t="shared" si="97"/>
-        <v>4197.3382108896276</v>
+        <f t="shared" si="96"/>
+        <v>4398.0904369368891</v>
       </c>
       <c r="DD40" s="3">
-        <f t="shared" si="97"/>
-        <v>4155.3648287807309</v>
+        <f t="shared" si="96"/>
+        <v>4354.1095325675205</v>
       </c>
       <c r="DE40" s="3">
-        <f t="shared" si="97"/>
-        <v>4113.811180492924</v>
+        <f t="shared" si="96"/>
+        <v>4310.5684372418455</v>
       </c>
       <c r="DF40" s="3">
-        <f t="shared" si="97"/>
-        <v>4072.6730686879946</v>
+        <f t="shared" ref="DF40:EL40" si="97">DE40*(1+$AU$50)</f>
+        <v>4267.4627528694273</v>
       </c>
       <c r="DG40" s="3">
         <f t="shared" si="97"/>
-        <v>4031.9463380011148</v>
+        <v>4224.7881253407331</v>
       </c>
       <c r="DH40" s="3">
         <f t="shared" si="97"/>
-        <v>3991.6268746211035</v>
+        <v>4182.5402440873258</v>
       </c>
       <c r="DI40" s="3">
         <f t="shared" si="97"/>
-        <v>3951.7106058748923</v>
+        <v>4140.7148416464524</v>
       </c>
       <c r="DJ40" s="3">
         <f t="shared" si="97"/>
-        <v>3912.1934998161432</v>
+        <v>4099.3076932299882</v>
       </c>
       <c r="DK40" s="3">
         <f t="shared" si="97"/>
-        <v>3873.0715648179817</v>
+        <v>4058.3146162976882</v>
       </c>
       <c r="DL40" s="3">
         <f t="shared" si="97"/>
-        <v>3834.3408491698019</v>
+        <v>4017.7314701347113</v>
       </c>
       <c r="DM40" s="3">
         <f t="shared" si="97"/>
-        <v>3795.9974406781039</v>
+        <v>3977.554155433364</v>
       </c>
       <c r="DN40" s="3">
         <f t="shared" si="97"/>
-        <v>3758.037466271323</v>
+        <v>3937.7786138790302</v>
       </c>
       <c r="DO40" s="3">
         <f t="shared" si="97"/>
-        <v>3720.4570916086095</v>
+        <v>3898.4008277402399</v>
       </c>
       <c r="DP40" s="3">
         <f t="shared" si="97"/>
-        <v>3683.2525206925234</v>
+        <v>3859.4168194628373</v>
       </c>
       <c r="DQ40" s="3">
         <f t="shared" si="97"/>
-        <v>3646.4199954855981</v>
+        <v>3820.822651268209</v>
       </c>
       <c r="DR40" s="3">
         <f t="shared" si="97"/>
-        <v>3609.9557955307419</v>
+        <v>3782.6144247555271</v>
       </c>
       <c r="DS40" s="3">
         <f t="shared" si="97"/>
-        <v>3573.8562375754345</v>
+        <v>3744.7882805079716</v>
       </c>
       <c r="DT40" s="3">
         <f t="shared" si="97"/>
-        <v>3538.11767519968</v>
+        <v>3707.340397702892</v>
       </c>
       <c r="DU40" s="3">
         <f t="shared" si="97"/>
-        <v>3502.7364984476831</v>
+        <v>3670.2669937258629</v>
       </c>
       <c r="DV40" s="3">
         <f t="shared" si="97"/>
-        <v>3467.7091334632064</v>
+        <v>3633.5643237886043</v>
       </c>
       <c r="DW40" s="3">
         <f t="shared" si="97"/>
-        <v>3433.0320421285742</v>
+        <v>3597.2286805507183</v>
       </c>
       <c r="DX40" s="3">
         <f t="shared" si="97"/>
-        <v>3398.7017217072885</v>
+        <v>3561.256393745211</v>
       </c>
       <c r="DY40" s="3">
         <f t="shared" si="97"/>
-        <v>3364.7147044902154</v>
+        <v>3525.6438298077587</v>
       </c>
       <c r="DZ40" s="3">
         <f t="shared" si="97"/>
-        <v>3331.067557445313</v>
+        <v>3490.387391509681</v>
       </c>
       <c r="EA40" s="3">
         <f t="shared" si="97"/>
-        <v>3297.7568818708601</v>
+        <v>3455.4835175945841</v>
       </c>
       <c r="EB40" s="3">
         <f t="shared" si="97"/>
-        <v>3264.7793130521513</v>
+        <v>3420.9286824186383</v>
       </c>
       <c r="EC40" s="3">
         <f t="shared" si="97"/>
-        <v>3232.1315199216297</v>
+        <v>3386.7193955944517</v>
       </c>
       <c r="ED40" s="3">
         <f t="shared" si="97"/>
-        <v>3199.8102047224133</v>
+        <v>3352.8522016385073</v>
       </c>
       <c r="EE40" s="3">
         <f t="shared" si="97"/>
-        <v>3167.8121026751892</v>
+        <v>3319.3236796221222</v>
       </c>
       <c r="EF40" s="3">
         <f t="shared" si="97"/>
-        <v>3136.1339816484374</v>
+        <v>3286.1304428259009</v>
       </c>
       <c r="EG40" s="3">
         <f t="shared" si="97"/>
-        <v>3104.772641831953</v>
+        <v>3253.2691383976417</v>
       </c>
       <c r="EH40" s="3">
         <f t="shared" si="97"/>
-        <v>3073.7249154136334</v>
-      </c>
-    </row>
-    <row r="41" spans="2:138" x14ac:dyDescent="0.3">
+        <v>3220.7364470136654</v>
+      </c>
+      <c r="EI40" s="3">
+        <f t="shared" si="97"/>
+        <v>3188.5290825435286</v>
+      </c>
+      <c r="EJ40" s="3">
+        <f t="shared" si="97"/>
+        <v>3156.6437917180933</v>
+      </c>
+      <c r="EK40" s="3">
+        <f t="shared" si="97"/>
+        <v>3125.0773538009125</v>
+      </c>
+      <c r="EL40" s="3">
+        <f t="shared" si="97"/>
+        <v>3093.8265802629035</v>
+      </c>
+    </row>
+    <row r="41" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>2</v>
       </c>
@@ -4174,27 +4408,16 @@
       <c r="U41" s="6">
         <v>231.4</v>
       </c>
-      <c r="V41" s="6">
-        <v>231.4</v>
-      </c>
-      <c r="X41" s="6">
-        <f t="shared" ref="X41:AC41" si="99">235.4</f>
-        <v>235.4</v>
-      </c>
-      <c r="Y41" s="6">
-        <f t="shared" si="99"/>
-        <v>235.4</v>
-      </c>
-      <c r="Z41" s="6">
-        <f t="shared" si="99"/>
-        <v>235.4</v>
-      </c>
-      <c r="AA41" s="6">
-        <f t="shared" si="99"/>
-        <v>235.4</v>
-      </c>
+      <c r="V41" s="18">
+        <f>230.9</f>
+        <v>230.9</v>
+      </c>
+      <c r="W41" s="6"/>
+      <c r="X41" s="6"/>
+      <c r="Y41" s="6"/>
+      <c r="Z41" s="6"/>
       <c r="AB41" s="6">
-        <f t="shared" si="99"/>
+        <f t="shared" ref="AB41:AG41" si="99">235.4</f>
         <v>235.4</v>
       </c>
       <c r="AC41" s="6">
@@ -4202,40 +4425,67 @@
         <v>235.4</v>
       </c>
       <c r="AD41" s="6">
-        <v>231.4</v>
+        <f t="shared" si="99"/>
+        <v>235.4</v>
       </c>
       <c r="AE41" s="6">
-        <v>231.4</v>
+        <f t="shared" si="99"/>
+        <v>235.4</v>
       </c>
       <c r="AF41" s="6">
-        <v>231.4</v>
+        <f t="shared" si="99"/>
+        <v>235.4</v>
       </c>
       <c r="AG41" s="6">
-        <v>231.4</v>
+        <f t="shared" si="99"/>
+        <v>235.4</v>
       </c>
       <c r="AH41" s="6">
-        <v>231.4</v>
+        <f>230.9</f>
+        <v>230.9</v>
       </c>
       <c r="AI41" s="6">
-        <v>231.4</v>
+        <f>230.9</f>
+        <v>230.9</v>
       </c>
       <c r="AJ41" s="6">
-        <v>231.4</v>
+        <f>230.9</f>
+        <v>230.9</v>
       </c>
       <c r="AK41" s="6">
-        <v>231.4</v>
+        <f>230.9</f>
+        <v>230.9</v>
       </c>
       <c r="AL41" s="6">
-        <v>231.4</v>
+        <f>230.9</f>
+        <v>230.9</v>
       </c>
       <c r="AM41" s="6">
-        <v>231.4</v>
+        <f>230.9</f>
+        <v>230.9</v>
       </c>
       <c r="AN41" s="6">
-        <v>231.4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:138" x14ac:dyDescent="0.3">
+        <f>230.9</f>
+        <v>230.9</v>
+      </c>
+      <c r="AO41" s="6">
+        <f>230.9</f>
+        <v>230.9</v>
+      </c>
+      <c r="AP41" s="6">
+        <f>230.9</f>
+        <v>230.9</v>
+      </c>
+      <c r="AQ41" s="6">
+        <f>230.9</f>
+        <v>230.9</v>
+      </c>
+      <c r="AR41" s="6">
+        <f>230.9</f>
+        <v>230.9</v>
+      </c>
+    </row>
+    <row r="42" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>47</v>
       </c>
@@ -4283,80 +4533,84 @@
         <f t="shared" ref="U42:V42" si="107">U40/U41</f>
         <v>6.9965427830596365</v>
       </c>
-      <c r="V42" s="10">
+      <c r="V42" s="20">
         <f t="shared" si="107"/>
-        <v>7.8161019878997431</v>
-      </c>
-      <c r="X42" s="10">
-        <f t="shared" ref="X42:AC42" si="108">X40/X41</f>
+        <v>8.2763100909484617</v>
+      </c>
+      <c r="W42" s="10"/>
+      <c r="X42" s="10"/>
+      <c r="Y42" s="10"/>
+      <c r="Z42" s="10"/>
+      <c r="AB42" s="10">
+        <f t="shared" ref="AB42:AG42" si="108">AB40/AB41</f>
         <v>26.465590484282071</v>
       </c>
-      <c r="Y42" s="10">
+      <c r="AC42" s="10">
         <f t="shared" si="108"/>
         <v>29.260832625318606</v>
       </c>
-      <c r="Z42" s="10">
+      <c r="AD42" s="10">
         <f t="shared" si="108"/>
         <v>26.826677994902294</v>
       </c>
-      <c r="AA42" s="10">
+      <c r="AE42" s="10">
         <f t="shared" si="108"/>
         <v>24.350042480883602</v>
       </c>
-      <c r="AB42" s="10">
+      <c r="AF42" s="10">
         <f t="shared" si="108"/>
         <v>29.396771452846217</v>
       </c>
-      <c r="AC42" s="10">
+      <c r="AG42" s="10">
         <f t="shared" si="108"/>
         <v>22.667799490229395</v>
       </c>
-      <c r="AD42" s="10">
-        <f t="shared" ref="AD42:AN42" si="109">AD40/AD41</f>
-        <v>23.689049265341371</v>
-      </c>
-      <c r="AE42" s="10">
-        <f t="shared" si="109"/>
-        <v>31.17512013828868</v>
-      </c>
-      <c r="AF42" s="10">
-        <f t="shared" si="109"/>
-        <v>31.856060545375989</v>
-      </c>
-      <c r="AG42" s="10">
-        <f t="shared" si="109"/>
-        <v>32.291185629446879</v>
-      </c>
       <c r="AH42" s="10">
-        <f t="shared" si="109"/>
-        <v>32.73415889871692</v>
+        <f t="shared" ref="AH42:AR42" si="109">AH40/AH41</f>
+        <v>23.9794482459939</v>
       </c>
       <c r="AI42" s="10">
         <f t="shared" si="109"/>
-        <v>33.185163743069033</v>
+        <v>31.451053646600275</v>
       </c>
       <c r="AJ42" s="10">
         <f t="shared" si="109"/>
-        <v>33.644388533525515</v>
+        <v>32.137781912343002</v>
       </c>
       <c r="AK42" s="10">
         <f t="shared" si="109"/>
-        <v>34.112026766477385</v>
+        <v>32.576274931939373</v>
       </c>
       <c r="AL42" s="10">
         <f t="shared" si="109"/>
-        <v>34.588277212187315</v>
+        <v>33.022666337745832</v>
       </c>
       <c r="AM42" s="10">
         <f t="shared" si="109"/>
-        <v>35.073344067695615</v>
+        <v>33.477140517305052</v>
       </c>
       <c r="AN42" s="10">
         <f t="shared" si="109"/>
-        <v>35.567437114260677</v>
-      </c>
-    </row>
-    <row r="44" spans="2:138" x14ac:dyDescent="0.3">
+        <v>33.939886864145286</v>
+      </c>
+      <c r="AO42" s="10">
+        <f t="shared" si="109"/>
+        <v>34.411099922703961</v>
+      </c>
+      <c r="AP42" s="10">
+        <f t="shared" si="109"/>
+        <v>34.890979537545718</v>
+      </c>
+      <c r="AQ42" s="10">
+        <f t="shared" si="109"/>
+        <v>35.379731007004352</v>
+      </c>
+      <c r="AR42" s="10">
+        <f t="shared" si="109"/>
+        <v>35.877565241380047</v>
+      </c>
+    </row>
+    <row r="44" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>76</v>
       </c>
@@ -4364,743 +4618,783 @@
         <f>U16/Q16-1</f>
         <v>0.11854478187143513</v>
       </c>
-    </row>
-    <row r="45" spans="2:138" x14ac:dyDescent="0.3">
+      <c r="V44" s="11">
+        <f t="shared" ref="V44:V47" si="110">V16/R16-1</f>
+        <v>6.4302659508053361E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>77</v>
       </c>
       <c r="U45" s="11">
-        <f t="shared" ref="U45:U47" si="110">U17/Q17-1</f>
+        <f t="shared" ref="U45:U47" si="111">U17/Q17-1</f>
         <v>0.14141732283464559</v>
       </c>
-    </row>
-    <row r="46" spans="2:138" x14ac:dyDescent="0.3">
+      <c r="V45" s="11">
+        <f t="shared" si="110"/>
+        <v>0.17819460726846414</v>
+      </c>
+    </row>
+    <row r="46" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
         <v>78</v>
       </c>
       <c r="U46" s="11">
+        <f t="shared" si="111"/>
+        <v>1.3739409205404396E-3</v>
+      </c>
+      <c r="V46" s="11">
         <f t="shared" si="110"/>
-        <v>1.3739409205404396E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:138" x14ac:dyDescent="0.3">
+        <v>8.3313776108894677E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
         <v>79</v>
       </c>
       <c r="U47" s="11">
+        <f t="shared" si="111"/>
+        <v>9.1382113821138145E-2</v>
+      </c>
+      <c r="V47" s="11">
         <f t="shared" si="110"/>
-        <v>9.1382113821138145E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="2:43" x14ac:dyDescent="0.3">
+        <v>7.5170068027210935E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L49" s="11"/>
       <c r="M49" s="11"/>
       <c r="O49" s="11">
-        <f t="shared" ref="O49:P51" si="111">O22/K22-1</f>
+        <f t="shared" ref="O49:P51" si="112">O22/K22-1</f>
         <v>0.13332268880728093</v>
       </c>
       <c r="P49" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>9.8197412414595231E-2</v>
       </c>
       <c r="Q49" s="11">
-        <f>Q22/M22-1</f>
+        <f t="shared" ref="Q49:V49" si="113">Q22/M22-1</f>
         <v>3.2681604110175622E-2</v>
       </c>
       <c r="R49" s="11">
-        <f>R22/N22-1</f>
+        <f t="shared" si="113"/>
         <v>-2.9247823636249781E-2</v>
       </c>
       <c r="S49" s="11">
-        <f>S22/O22-1</f>
+        <f t="shared" si="113"/>
         <v>5.2127359819667429E-2</v>
       </c>
       <c r="T49" s="11">
-        <f>T22/P22-1</f>
+        <f t="shared" si="113"/>
         <v>2.6474286848898743E-3</v>
       </c>
       <c r="U49" s="11">
-        <f>U22/Q22-1</f>
+        <f t="shared" si="113"/>
         <v>5.7974018794914262E-2</v>
       </c>
       <c r="V49" s="11">
-        <f>V22/R22-1</f>
-        <v>4.0000000000000036E-2</v>
-      </c>
+        <f t="shared" si="113"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="W49" s="11"/>
       <c r="X49" s="11"/>
-      <c r="Y49" s="11">
-        <f t="shared" ref="Y49:AB51" si="112">Y22/X22-1</f>
+      <c r="Y49" s="11"/>
+      <c r="Z49" s="11"/>
+      <c r="AB49" s="11"/>
+      <c r="AC49" s="11">
+        <f t="shared" ref="AC49:AF51" si="114">AC22/AB22-1</f>
         <v>9.7396759434998925E-2</v>
       </c>
-      <c r="Z49" s="11">
-        <f t="shared" si="112"/>
+      <c r="AD49" s="11">
+        <f t="shared" si="114"/>
         <v>2.7435916108359937E-2</v>
       </c>
-      <c r="AA49" s="11">
-        <f t="shared" si="112"/>
+      <c r="AE49" s="11">
+        <f t="shared" si="114"/>
         <v>-1.7170195800478405E-2</v>
       </c>
-      <c r="AB49" s="11">
-        <f t="shared" si="112"/>
+      <c r="AF49" s="11">
+        <f t="shared" si="114"/>
         <v>1.4405221216601261E-2</v>
       </c>
-      <c r="AC49" s="11">
-        <f>AC22/AB22-1</f>
+      <c r="AG49" s="11">
+        <f>AG22/AF22-1</f>
         <v>5.3532391362303366E-2</v>
       </c>
-      <c r="AD49" s="11">
-        <f t="shared" ref="AD49:AN51" si="113">AD22/AC22-1</f>
-        <v>3.7771817062266955E-2</v>
-      </c>
-      <c r="AE49" s="11">
-        <f t="shared" si="113"/>
+      <c r="AH49" s="11">
+        <f t="shared" ref="AH49:AR51" si="115">AH22/AG22-1</f>
+        <v>4.5616343607132626E-2</v>
+      </c>
+      <c r="AI49" s="11">
+        <f t="shared" si="115"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AF49" s="11">
-        <f t="shared" si="113"/>
+      <c r="AJ49" s="11">
+        <f t="shared" si="115"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG49" s="11">
-        <f t="shared" si="113"/>
+      <c r="AK49" s="11">
+        <f t="shared" si="115"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH49" s="11">
-        <f t="shared" si="113"/>
+      <c r="AL49" s="11">
+        <f t="shared" si="115"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI49" s="11">
-        <f t="shared" si="113"/>
+      <c r="AM49" s="11">
+        <f t="shared" si="115"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ49" s="11">
-        <f t="shared" si="113"/>
+      <c r="AN49" s="11">
+        <f t="shared" si="115"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AK49" s="11">
-        <f t="shared" si="113"/>
+      <c r="AO49" s="11">
+        <f t="shared" si="115"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AL49" s="11">
-        <f t="shared" si="113"/>
+      <c r="AP49" s="11">
+        <f t="shared" si="115"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AM49" s="11">
-        <f t="shared" si="113"/>
+      <c r="AQ49" s="11">
+        <f t="shared" si="115"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AN49" s="11">
-        <f t="shared" si="113"/>
+      <c r="AR49" s="11">
+        <f t="shared" si="115"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="50" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>51</v>
       </c>
       <c r="L50" s="11"/>
       <c r="M50" s="11"/>
       <c r="O50" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.15346153846153854</v>
       </c>
       <c r="P50" s="11">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.6575809199318678E-2</v>
       </c>
       <c r="Q50" s="11">
-        <f t="shared" ref="Q50:V51" si="114">Q23/M23-1</f>
+        <f t="shared" ref="Q50:V51" si="116">Q23/M23-1</f>
         <v>-8.1005586592178824E-2</v>
       </c>
       <c r="R50" s="11">
+        <f t="shared" si="116"/>
+        <v>7.3959408324733467E-2</v>
+      </c>
+      <c r="S50" s="11">
+        <f t="shared" si="116"/>
+        <v>9.3364454818272158E-3</v>
+      </c>
+      <c r="T50" s="11">
+        <f t="shared" si="116"/>
+        <v>-2.3232658479920287E-3</v>
+      </c>
+      <c r="U50" s="11">
+        <f t="shared" si="116"/>
+        <v>0.25303951367781163</v>
+      </c>
+      <c r="V50" s="11">
+        <f t="shared" si="116"/>
+        <v>0.1100000000000001</v>
+      </c>
+      <c r="W50" s="11"/>
+      <c r="X50" s="11"/>
+      <c r="Y50" s="11"/>
+      <c r="Z50" s="11"/>
+      <c r="AB50" s="11"/>
+      <c r="AC50" s="11">
         <f t="shared" si="114"/>
-        <v>7.3959408324733467E-2</v>
-      </c>
-      <c r="S50" s="11">
+        <v>7.2855825391945794E-2</v>
+      </c>
+      <c r="AD50" s="11">
         <f t="shared" si="114"/>
-        <v>9.3364454818272158E-3</v>
-      </c>
-      <c r="T50" s="11">
+        <v>1.3276026743075375E-2</v>
+      </c>
+      <c r="AE50" s="11">
         <f t="shared" si="114"/>
-        <v>-2.3232658479920287E-3</v>
-      </c>
-      <c r="U50" s="11">
+        <v>-8.5776227731171328E-3</v>
+      </c>
+      <c r="AF50" s="11">
         <f t="shared" si="114"/>
-        <v>0.25303951367781163</v>
-      </c>
-      <c r="V50" s="11">
-        <f t="shared" si="114"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="X50" s="11"/>
-      <c r="Y50" s="11">
-        <f t="shared" si="112"/>
-        <v>7.2855825391945794E-2</v>
-      </c>
-      <c r="Z50" s="11">
-        <f t="shared" si="112"/>
-        <v>1.3276026743075375E-2</v>
-      </c>
-      <c r="AA50" s="11">
-        <f t="shared" si="112"/>
-        <v>-8.5776227731171328E-3</v>
-      </c>
-      <c r="AB50" s="11">
-        <f t="shared" si="112"/>
         <v>7.4919186157064166E-2</v>
       </c>
-      <c r="AC50" s="11">
-        <f t="shared" ref="AC50:AC51" si="115">AC23/AB23-1</f>
+      <c r="AG50" s="11">
+        <f t="shared" ref="AG50:AG51" si="117">AG23/AF23-1</f>
         <v>4.0686361224128831E-2</v>
       </c>
-      <c r="AD50" s="11">
-        <f t="shared" si="113"/>
-        <v>8.4922658507564197E-2</v>
-      </c>
-      <c r="AE50" s="11">
-        <f t="shared" si="113"/>
+      <c r="AH50" s="11">
+        <f t="shared" si="115"/>
+        <v>8.7576066632670369E-2</v>
+      </c>
+      <c r="AI50" s="11">
+        <f t="shared" si="115"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AF50" s="11">
-        <f t="shared" si="113"/>
+      <c r="AJ50" s="11">
+        <f t="shared" si="115"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AG50" s="11">
-        <f t="shared" si="113"/>
+      <c r="AK50" s="11">
+        <f t="shared" si="115"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AH50" s="11">
-        <f t="shared" si="113"/>
+      <c r="AL50" s="11">
+        <f t="shared" si="115"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AI50" s="11">
-        <f t="shared" si="113"/>
+      <c r="AM50" s="11">
+        <f t="shared" si="115"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AJ50" s="11">
-        <f t="shared" si="113"/>
+      <c r="AN50" s="11">
+        <f t="shared" si="115"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AK50" s="11">
-        <f t="shared" si="113"/>
+      <c r="AO50" s="11">
+        <f t="shared" si="115"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AL50" s="11">
-        <f t="shared" si="113"/>
+      <c r="AP50" s="11">
+        <f t="shared" si="115"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AM50" s="11">
-        <f t="shared" si="113"/>
+      <c r="AQ50" s="11">
+        <f t="shared" si="115"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AN50" s="11">
-        <f t="shared" si="113"/>
+      <c r="AR50" s="11">
+        <f t="shared" si="115"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AP50" s="1" t="s">
+      <c r="AT50" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AQ50" s="11">
+      <c r="AU50" s="11">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="51" spans="2:43" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:47" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>52</v>
       </c>
       <c r="L51" s="12"/>
       <c r="M51" s="12"/>
       <c r="O51" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.13678434483670499</v>
       </c>
       <c r="P51" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>8.5604744503684271E-2</v>
       </c>
       <c r="Q51" s="12">
+        <f t="shared" si="116"/>
+        <v>1.339021211043967E-2</v>
+      </c>
+      <c r="R51" s="12">
+        <f t="shared" si="116"/>
+        <v>-1.3351700752357698E-2</v>
+      </c>
+      <c r="S51" s="12">
+        <f t="shared" si="116"/>
+        <v>4.4664146554230788E-2</v>
+      </c>
+      <c r="T51" s="12">
+        <f t="shared" si="116"/>
+        <v>1.8209910605893054E-3</v>
+      </c>
+      <c r="U51" s="12">
+        <f t="shared" si="116"/>
+        <v>8.7991113189897163E-2</v>
+      </c>
+      <c r="V51" s="12">
+        <f t="shared" si="116"/>
+        <v>9.1236172269358873E-2</v>
+      </c>
+      <c r="W51" s="12"/>
+      <c r="X51" s="12"/>
+      <c r="Y51" s="12"/>
+      <c r="Z51" s="12"/>
+      <c r="AB51" s="12"/>
+      <c r="AC51" s="12">
         <f t="shared" si="114"/>
-        <v>1.339021211043967E-2</v>
-      </c>
-      <c r="R51" s="12">
+        <v>9.3392630241423191E-2</v>
+      </c>
+      <c r="AD51" s="12">
         <f t="shared" si="114"/>
-        <v>-1.3351700752357698E-2</v>
-      </c>
-      <c r="S51" s="12">
+        <v>2.516896541178637E-2</v>
+      </c>
+      <c r="AE51" s="12">
         <f t="shared" si="114"/>
-        <v>4.4664146554230788E-2</v>
-      </c>
-      <c r="T51" s="12">
+        <v>-1.5810512499254248E-2</v>
+      </c>
+      <c r="AF51" s="12">
         <f t="shared" si="114"/>
-        <v>1.8209910605893054E-3</v>
-      </c>
-      <c r="U51" s="12">
-        <f t="shared" si="114"/>
-        <v>8.7991113189897163E-2</v>
-      </c>
-      <c r="V51" s="12">
-        <f t="shared" si="114"/>
-        <v>5.0059069917302246E-2</v>
-      </c>
-      <c r="X51" s="12"/>
-      <c r="Y51" s="12">
-        <f t="shared" si="112"/>
-        <v>9.3392630241423191E-2</v>
-      </c>
-      <c r="Z51" s="12">
-        <f t="shared" si="112"/>
-        <v>2.516896541178637E-2</v>
-      </c>
-      <c r="AA51" s="12">
-        <f t="shared" si="112"/>
-        <v>-1.5810512499254248E-2</v>
-      </c>
-      <c r="AB51" s="12">
-        <f t="shared" si="112"/>
         <v>2.4051285160038738E-2</v>
       </c>
-      <c r="AC51" s="12">
+      <c r="AG51" s="12">
+        <f t="shared" si="117"/>
+        <v>5.1382989744120922E-2</v>
+      </c>
+      <c r="AH51" s="12">
         <f t="shared" si="115"/>
-        <v>5.1382989744120922E-2</v>
-      </c>
-      <c r="AD51" s="12">
-        <f t="shared" si="113"/>
-        <v>4.5580845403488057E-2</v>
-      </c>
-      <c r="AE51" s="12">
-        <f t="shared" si="113"/>
-        <v>3.3436993478834554E-2</v>
-      </c>
-      <c r="AF51" s="12">
-        <f t="shared" si="113"/>
-        <v>2.1746039272615869E-2</v>
-      </c>
-      <c r="AG51" s="12">
-        <f t="shared" si="113"/>
-        <v>1.3520288568135141E-2</v>
-      </c>
-      <c r="AH51" s="12">
-        <f t="shared" si="113"/>
-        <v>1.3577528014068418E-2</v>
+        <v>5.2565629266781988E-2</v>
       </c>
       <c r="AI51" s="12">
-        <f t="shared" si="113"/>
-        <v>1.3635492848494968E-2</v>
+        <f t="shared" si="115"/>
+        <v>3.3422535840364587E-2</v>
       </c>
       <c r="AJ51" s="12">
-        <f t="shared" si="113"/>
-        <v>1.3694185592719288E-2</v>
+        <f t="shared" si="115"/>
+        <v>2.1738718920746525E-2</v>
       </c>
       <c r="AK51" s="12">
-        <f t="shared" si="113"/>
-        <v>1.375360854839669E-2</v>
+        <f t="shared" si="115"/>
+        <v>1.3505554708273193E-2</v>
       </c>
       <c r="AL51" s="12">
-        <f t="shared" si="113"/>
-        <v>1.3813763790577083E-2</v>
+        <f t="shared" si="115"/>
+        <v>1.3562606374230235E-2</v>
       </c>
       <c r="AM51" s="12">
-        <f t="shared" si="113"/>
-        <v>1.3874653160760975E-2</v>
+        <f t="shared" si="115"/>
+        <v>1.3620382739438108E-2</v>
       </c>
       <c r="AN51" s="12">
-        <f t="shared" si="113"/>
-        <v>1.393627825998256E-2</v>
-      </c>
-      <c r="AP51" s="1" t="s">
+        <f t="shared" si="115"/>
+        <v>1.367888638105641E-2</v>
+      </c>
+      <c r="AO51" s="12">
+        <f t="shared" si="115"/>
+        <v>1.3738119658402104E-2</v>
+      </c>
+      <c r="AP51" s="12">
+        <f t="shared" si="115"/>
+        <v>1.3798084705990421E-2</v>
+      </c>
+      <c r="AQ51" s="12">
+        <f t="shared" si="115"/>
+        <v>1.3858783426587973E-2</v>
+      </c>
+      <c r="AR51" s="12">
+        <f t="shared" si="115"/>
+        <v>1.3920217484285846E-2</v>
+      </c>
+      <c r="AT51" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AQ51" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="2:43" x14ac:dyDescent="0.3">
+      <c r="AU51" s="11">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="52" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K52" s="11">
-        <f t="shared" ref="K52:M53" si="116">(K22-K25)/K22</f>
+        <f t="shared" ref="K52:M53" si="118">(K22-K25)/K22</f>
         <v>0.10977167491617436</v>
       </c>
       <c r="L52" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0.11048117458932985</v>
       </c>
       <c r="M52" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0.10296846011131726</v>
       </c>
       <c r="N52" s="11">
-        <f t="shared" ref="N52" si="117">(N22-N25)/N22</f>
+        <f t="shared" ref="N52" si="119">(N22-N25)/N22</f>
         <v>0.10778480616271059</v>
       </c>
       <c r="O52" s="11">
-        <f t="shared" ref="O52:T53" si="118">(O22-O25)/O22</f>
+        <f t="shared" ref="O52:T53" si="120">(O22-O25)/O22</f>
         <v>9.2420400112707801E-2</v>
       </c>
       <c r="P52" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.10516910450724734</v>
       </c>
       <c r="Q52" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.10420121614151465</v>
       </c>
       <c r="R52" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>1.0322580645161291E-3</v>
       </c>
       <c r="S52" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.11060524906266737</v>
       </c>
       <c r="T52" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>4.4887451316918611E-2</v>
       </c>
       <c r="U52" s="11">
-        <f t="shared" ref="U52:V52" si="119">(U22-U25)/U22</f>
+        <f t="shared" ref="U52:V52" si="121">(U22-U25)/U22</f>
         <v>0.10469597021749069</v>
       </c>
       <c r="V52" s="11">
-        <f t="shared" si="119"/>
-        <v>0.10999999999999993</v>
-      </c>
-      <c r="X52" s="11">
-        <f t="shared" ref="X52:AB52" si="120">(X22-X25)/X22</f>
-        <v>0.10916428585699159</v>
-      </c>
-      <c r="Y52" s="11">
-        <f t="shared" si="120"/>
-        <v>0.10799592193416836</v>
-      </c>
-      <c r="Z52" s="11">
-        <f t="shared" si="120"/>
-        <v>0.10918756091078231</v>
-      </c>
-      <c r="AA52" s="11">
-        <f t="shared" si="120"/>
-        <v>0.11013954494645369</v>
-      </c>
-      <c r="AB52" s="11">
-        <f t="shared" si="120"/>
-        <v>0.10768683906513818</v>
-      </c>
-      <c r="AC52" s="11">
-        <f>(AC22-AC25)/AC22</f>
-        <v>7.4649526797914881E-2</v>
-      </c>
-      <c r="AD52" s="11">
-        <f t="shared" ref="AD52:AN52" si="121">(AD22-AD25)/AD22</f>
-        <v>9.2792119123480024E-2</v>
-      </c>
-      <c r="AE52" s="11">
-        <f t="shared" si="121"/>
-        <v>0.10999999999999995</v>
-      </c>
-      <c r="AF52" s="11">
-        <f t="shared" si="121"/>
-        <v>0.11</v>
-      </c>
-      <c r="AG52" s="11">
         <f t="shared" si="121"/>
         <v>0.11000000000000003</v>
       </c>
+      <c r="W52" s="11"/>
+      <c r="X52" s="11"/>
+      <c r="Y52" s="11"/>
+      <c r="Z52" s="11"/>
+      <c r="AB52" s="11">
+        <f t="shared" ref="AB52:AF52" si="122">(AB22-AB25)/AB22</f>
+        <v>0.10916428585699159</v>
+      </c>
+      <c r="AC52" s="11">
+        <f t="shared" si="122"/>
+        <v>0.10799592193416836</v>
+      </c>
+      <c r="AD52" s="11">
+        <f t="shared" si="122"/>
+        <v>0.10918756091078231</v>
+      </c>
+      <c r="AE52" s="11">
+        <f t="shared" si="122"/>
+        <v>0.11013954494645369</v>
+      </c>
+      <c r="AF52" s="11">
+        <f t="shared" si="122"/>
+        <v>0.10768683906513818</v>
+      </c>
+      <c r="AG52" s="11">
+        <f>(AG22-AG25)/AG22</f>
+        <v>7.4649526797914881E-2</v>
+      </c>
       <c r="AH52" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" ref="AH52:AR52" si="123">(AH22-AH25)/AH22</f>
+        <v>9.2921217792549304E-2</v>
+      </c>
+      <c r="AI52" s="11">
+        <f t="shared" si="123"/>
         <v>0.11</v>
       </c>
-      <c r="AI52" s="11">
-        <f t="shared" si="121"/>
-        <v>0.11000000000000001</v>
-      </c>
       <c r="AJ52" s="11">
-        <f t="shared" si="121"/>
-        <v>0.11</v>
+        <f t="shared" si="123"/>
+        <v>0.10999999999999995</v>
       </c>
       <c r="AK52" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="AL52" s="11">
-        <f t="shared" si="121"/>
-        <v>0.10999999999999993</v>
+        <f t="shared" si="123"/>
+        <v>0.10999999999999995</v>
       </c>
       <c r="AM52" s="11">
-        <f t="shared" si="121"/>
-        <v>0.10999999999999995</v>
+        <f t="shared" si="123"/>
+        <v>0.11000000000000003</v>
       </c>
       <c r="AN52" s="11">
-        <f t="shared" si="121"/>
-        <v>0.10999999999999995</v>
-      </c>
-      <c r="AP52" s="1" t="s">
+        <f t="shared" si="123"/>
+        <v>0.10999999999999997</v>
+      </c>
+      <c r="AO52" s="11">
+        <f t="shared" si="123"/>
+        <v>0.10999999999999997</v>
+      </c>
+      <c r="AP52" s="11">
+        <f t="shared" si="123"/>
+        <v>0.10999999999999996</v>
+      </c>
+      <c r="AQ52" s="11">
+        <f t="shared" si="123"/>
+        <v>0.10999999999999997</v>
+      </c>
+      <c r="AR52" s="11">
+        <f t="shared" si="123"/>
+        <v>0.11000000000000003</v>
+      </c>
+      <c r="AT52" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AQ52" s="6">
-        <f>NPV(AQ51,AD40:EH40)</f>
-        <v>103855.47196964601</v>
-      </c>
-    </row>
-    <row r="53" spans="2:43" x14ac:dyDescent="0.3">
+      <c r="AU52" s="6">
+        <f>NPV(AU51,AI40:EL40)</f>
+        <v>122252.59327233705</v>
+      </c>
+    </row>
+    <row r="53" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
         <v>54</v>
       </c>
       <c r="K53" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0.12153846153846154</v>
       </c>
       <c r="L53" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>9.9829642248722317E-2</v>
       </c>
       <c r="M53" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0.12360335195530726</v>
       </c>
       <c r="N53" s="11">
-        <f t="shared" ref="N53" si="122">(N23-N26)/N23</f>
+        <f t="shared" ref="N53" si="124">(N23-N26)/N23</f>
         <v>0.108703130374957</v>
       </c>
       <c r="O53" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.13204401467155719</v>
       </c>
       <c r="P53" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.14304679721208099</v>
       </c>
       <c r="Q53" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.13677811550151975</v>
       </c>
       <c r="R53" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.1159513132607303</v>
       </c>
       <c r="S53" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.12784935579781961</v>
       </c>
       <c r="T53" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>-4.1250831669993347E-2</v>
       </c>
       <c r="U53" s="11">
-        <f t="shared" ref="U53:V53" si="123">(U23-U26)/U23</f>
+        <f t="shared" ref="U53:V53" si="125">(U23-U26)/U23</f>
         <v>0.12947240751970893</v>
       </c>
       <c r="V53" s="11">
-        <f t="shared" si="123"/>
-        <v>0.12999999999999998</v>
-      </c>
-      <c r="X53" s="11">
-        <f t="shared" ref="X53:AB53" si="124">(X23-X26)/X23</f>
+        <f t="shared" si="125"/>
+        <v>0.13000000000000003</v>
+      </c>
+      <c r="W53" s="11"/>
+      <c r="X53" s="11"/>
+      <c r="Y53" s="11"/>
+      <c r="Z53" s="11"/>
+      <c r="AB53" s="11">
+        <f t="shared" ref="AB53:AF53" si="126">(AB23-AB26)/AB23</f>
         <v>0.10533866174812993</v>
       </c>
-      <c r="Y53" s="11">
-        <f t="shared" si="124"/>
+      <c r="AC53" s="11">
+        <f t="shared" si="126"/>
         <v>0.10496657115568291</v>
       </c>
-      <c r="Z53" s="11">
-        <f t="shared" si="124"/>
+      <c r="AD53" s="11">
+        <f t="shared" si="126"/>
         <v>0.10802149118672826</v>
       </c>
-      <c r="AA53" s="11">
-        <f t="shared" si="124"/>
+      <c r="AE53" s="11">
+        <f t="shared" si="126"/>
         <v>0.12036508841985168</v>
       </c>
-      <c r="AB53" s="11">
-        <f t="shared" si="124"/>
+      <c r="AF53" s="11">
+        <f t="shared" si="126"/>
         <v>0.11312577392534937</v>
       </c>
-      <c r="AC53" s="11">
-        <f>(AC23-AC26)/AC23</f>
+      <c r="AG53" s="11">
+        <f>(AG23-AG26)/AG23</f>
         <v>0.13165051844297126</v>
       </c>
-      <c r="AD53" s="11">
-        <f t="shared" ref="AD53:AN53" si="125">(AD23-AD26)/AD23</f>
-        <v>8.9026885595211977E-2</v>
-      </c>
-      <c r="AE53" s="11">
-        <f t="shared" si="125"/>
+      <c r="AH53" s="11">
+        <f t="shared" ref="AH53:AR53" si="127">(AH23-AH26)/AH23</f>
+        <v>8.912684954073094E-2</v>
+      </c>
+      <c r="AI53" s="11">
+        <f t="shared" si="127"/>
+        <v>0.12000000000000002</v>
+      </c>
+      <c r="AJ53" s="11">
+        <f t="shared" si="127"/>
+        <v>0.12</v>
+      </c>
+      <c r="AK53" s="11">
+        <f t="shared" si="127"/>
+        <v>0.12000000000000005</v>
+      </c>
+      <c r="AL53" s="11">
+        <f t="shared" si="127"/>
+        <v>0.12000000000000002</v>
+      </c>
+      <c r="AM53" s="11">
+        <f t="shared" si="127"/>
+        <v>0.12</v>
+      </c>
+      <c r="AN53" s="11">
+        <f t="shared" si="127"/>
+        <v>0.12</v>
+      </c>
+      <c r="AO53" s="11">
+        <f t="shared" si="127"/>
+        <v>0.12000000000000002</v>
+      </c>
+      <c r="AP53" s="11">
+        <f t="shared" si="127"/>
+        <v>0.12000000000000004</v>
+      </c>
+      <c r="AQ53" s="11">
+        <f t="shared" si="127"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="AR53" s="11">
+        <f t="shared" si="127"/>
         <v>0.11999999999999995</v>
       </c>
-      <c r="AF53" s="11">
-        <f t="shared" si="125"/>
-        <v>0.11999999999999995</v>
-      </c>
-      <c r="AG53" s="11">
-        <f t="shared" si="125"/>
-        <v>0.12000000000000005</v>
-      </c>
-      <c r="AH53" s="11">
-        <f t="shared" si="125"/>
-        <v>0.11999999999999995</v>
-      </c>
-      <c r="AI53" s="11">
-        <f t="shared" si="125"/>
-        <v>0.12000000000000001</v>
-      </c>
-      <c r="AJ53" s="11">
-        <f t="shared" si="125"/>
-        <v>0.12000000000000001</v>
-      </c>
-      <c r="AK53" s="11">
-        <f t="shared" si="125"/>
-        <v>0.12</v>
-      </c>
-      <c r="AL53" s="11">
-        <f t="shared" si="125"/>
-        <v>0.11999999999999997</v>
-      </c>
-      <c r="AM53" s="11">
-        <f t="shared" si="125"/>
-        <v>0.12</v>
-      </c>
-      <c r="AN53" s="11">
-        <f t="shared" si="125"/>
-        <v>0.11999999999999998</v>
-      </c>
-      <c r="AP53" s="1" t="s">
+      <c r="AT53" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AQ53" s="6">
+      <c r="AU53" s="6">
         <f>Main!D8</f>
-        <v>-18719</v>
-      </c>
-    </row>
-    <row r="54" spans="2:43" x14ac:dyDescent="0.3">
+        <v>-17578</v>
+      </c>
+    </row>
+    <row r="54" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
         <v>55</v>
       </c>
       <c r="K54" s="11">
-        <f t="shared" ref="K54:V54" si="126">(K28-K30-K31)/K24</f>
+        <f t="shared" ref="K54:V54" si="128">(K28-K30-K31)/K24</f>
         <v>0.13466878222927409</v>
       </c>
       <c r="L54" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>0.12789792128437069</v>
       </c>
       <c r="M54" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>0.12098589880317573</v>
       </c>
       <c r="N54" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>0.12636431069195719</v>
       </c>
       <c r="O54" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>0.11799941843559174</v>
       </c>
       <c r="P54" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>0.12333075819445977</v>
       </c>
       <c r="Q54" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>0.12511693171188026</v>
       </c>
       <c r="R54" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>3.7375147674793253E-2</v>
       </c>
       <c r="S54" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>0.13204921226966543</v>
       </c>
       <c r="T54" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>4.4836133296612506E-2</v>
       </c>
       <c r="U54" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>0.12252136063195228</v>
       </c>
       <c r="V54" s="11">
-        <f t="shared" si="126"/>
-        <v>0.12629747062012256</v>
-      </c>
-      <c r="X54" s="11">
-        <f t="shared" ref="X54:AD54" si="127">(X28-X30-X31)/X24</f>
+        <f t="shared" si="128"/>
+        <v>0.12656857438118202</v>
+      </c>
+      <c r="W54" s="11"/>
+      <c r="X54" s="11"/>
+      <c r="Y54" s="11"/>
+      <c r="Z54" s="11"/>
+      <c r="AB54" s="11">
+        <f t="shared" ref="AB54:AG54" si="129">(AB28-AB30-AB31)/AB24</f>
         <v>0.14286430816558551</v>
       </c>
-      <c r="Y54" s="11">
-        <f t="shared" si="127"/>
+      <c r="AC54" s="11">
+        <f t="shared" si="129"/>
         <v>0.13258815254289122</v>
       </c>
-      <c r="Z54" s="11">
-        <f t="shared" si="127"/>
+      <c r="AD54" s="11">
+        <f t="shared" si="129"/>
         <v>0.13661177734025415</v>
       </c>
-      <c r="AA54" s="11">
-        <f t="shared" si="127"/>
+      <c r="AE54" s="11">
+        <f t="shared" si="129"/>
         <v>0.12803103782735209</v>
       </c>
-      <c r="AB54" s="11">
-        <f t="shared" si="127"/>
+      <c r="AF54" s="11">
+        <f t="shared" si="129"/>
         <v>0.12725873525624898</v>
       </c>
-      <c r="AC54" s="11">
-        <f t="shared" si="127"/>
+      <c r="AG54" s="11">
+        <f t="shared" si="129"/>
         <v>9.9939473276747889E-2</v>
       </c>
-      <c r="AD54" s="11">
-        <f>(AD28-AD30-AD31)/AD24</f>
-        <v>0.1068324959747553</v>
-      </c>
-      <c r="AE54" s="11">
-        <f t="shared" ref="AE54:AN54" si="128">(AE28-AE30-AE31)/AE24</f>
-        <v>0.12610037863639312</v>
-      </c>
-      <c r="AF54" s="11">
-        <f t="shared" si="128"/>
-        <v>0.12594946550496131</v>
-      </c>
-      <c r="AG54" s="11">
-        <f t="shared" si="128"/>
-        <v>0.1259288010588325</v>
-      </c>
       <c r="AH54" s="11">
-        <f t="shared" si="128"/>
-        <v>0.12590787473470655</v>
+        <f>(AH28-AH30-AH31)/AH24</f>
+        <v>0.10686186552036686</v>
       </c>
       <c r="AI54" s="11">
-        <f t="shared" si="128"/>
-        <v>0.12588668562234889</v>
+        <f t="shared" ref="AI54:AR54" si="130">(AI28-AI30-AI31)/AI24</f>
+        <v>0.12599800294192284</v>
       </c>
       <c r="AJ54" s="11">
-        <f t="shared" si="128"/>
-        <v>0.12586523289082083</v>
+        <f t="shared" si="130"/>
+        <v>0.12584823698064529</v>
       </c>
       <c r="AK54" s="11">
-        <f t="shared" si="128"/>
-        <v>0.12584351579099329</v>
+        <f t="shared" si="130"/>
+        <v>0.12582800885798004</v>
       </c>
       <c r="AL54" s="11">
-        <f t="shared" si="128"/>
-        <v>0.12582153365805213</v>
+        <f t="shared" si="130"/>
+        <v>0.12580752378742188</v>
       </c>
       <c r="AM54" s="11">
-        <f t="shared" si="128"/>
-        <v>0.12579928591399575</v>
+        <f t="shared" si="130"/>
+        <v>0.12578678085521888</v>
       </c>
       <c r="AN54" s="11">
-        <f t="shared" si="128"/>
-        <v>0.12577677207012208</v>
-      </c>
-      <c r="AP54" s="1" t="s">
+        <f t="shared" si="130"/>
+        <v>0.12576577922485599</v>
+      </c>
+      <c r="AO54" s="11">
+        <f t="shared" si="130"/>
+        <v>0.12574451813952395</v>
+      </c>
+      <c r="AP54" s="11">
+        <f t="shared" si="130"/>
+        <v>0.12572299692458169</v>
+      </c>
+      <c r="AQ54" s="11">
+        <f t="shared" si="130"/>
+        <v>0.12570121499001258</v>
+      </c>
+      <c r="AR54" s="11">
+        <f t="shared" si="130"/>
+        <v>0.1256791718328685</v>
+      </c>
+      <c r="AT54" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AQ54" s="6">
-        <f>AQ52+AQ53</f>
-        <v>85136.471969646009</v>
-      </c>
-    </row>
-    <row r="55" spans="2:43" x14ac:dyDescent="0.3">
+      <c r="AU54" s="6">
+        <f>AU52+AU53</f>
+        <v>104674.59327233705</v>
+      </c>
+    </row>
+    <row r="55" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
         <v>56</v>
       </c>
@@ -5117,118 +5411,122 @@
         <v>0.12098589880317573</v>
       </c>
       <c r="N55" s="11">
-        <f t="shared" ref="N55" si="129">N33/N24</f>
+        <f t="shared" ref="N55" si="131">N33/N24</f>
         <v>0.12636431069195719</v>
       </c>
       <c r="O55" s="11">
-        <f t="shared" ref="O55:T55" si="130">O33/O24</f>
+        <f t="shared" ref="O55:T55" si="132">O33/O24</f>
         <v>0.11799941843559174</v>
       </c>
       <c r="P55" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>0.11852996358017878</v>
       </c>
       <c r="Q55" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>0.12511693171188026</v>
       </c>
       <c r="R55" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>3.7375147674793253E-2</v>
       </c>
       <c r="S55" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>0.13204921226966543</v>
       </c>
       <c r="T55" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>4.1200771137427705E-2</v>
       </c>
       <c r="U55" s="11">
-        <f t="shared" ref="U55:V55" si="131">U33/U24</f>
+        <f t="shared" ref="U55:V55" si="133">U33/U24</f>
         <v>0.12252136063195228</v>
       </c>
       <c r="V55" s="11">
-        <f t="shared" si="131"/>
-        <v>0.12629747062012256</v>
-      </c>
-      <c r="X55" s="11">
-        <f t="shared" ref="X55:AB55" si="132">X33/X24</f>
+        <f t="shared" si="133"/>
+        <v>0.12656857438118202</v>
+      </c>
+      <c r="W55" s="11"/>
+      <c r="X55" s="11"/>
+      <c r="Y55" s="11"/>
+      <c r="Z55" s="11"/>
+      <c r="AB55" s="11">
+        <f t="shared" ref="AB55:AF55" si="134">AB33/AB24</f>
         <v>0.14286430816558551</v>
       </c>
-      <c r="Y55" s="11">
-        <f t="shared" si="132"/>
+      <c r="AC55" s="11">
+        <f t="shared" si="134"/>
         <v>0.13217529588060797</v>
       </c>
-      <c r="Z55" s="11">
-        <f t="shared" si="132"/>
+      <c r="AD55" s="11">
+        <f t="shared" si="134"/>
         <v>0.13607481653839271</v>
       </c>
-      <c r="AA55" s="11">
-        <f t="shared" si="132"/>
+      <c r="AE55" s="11">
+        <f t="shared" si="134"/>
         <v>0.12651551891367604</v>
       </c>
-      <c r="AB55" s="11">
-        <f t="shared" si="132"/>
+      <c r="AF55" s="11">
+        <f t="shared" si="134"/>
         <v>0.12589720442201535</v>
       </c>
-      <c r="AC55" s="11">
-        <f>AC33/AC24</f>
+      <c r="AG55" s="11">
+        <f>AG33/AG24</f>
         <v>9.8714862829553926E-2</v>
       </c>
-      <c r="AD55" s="11">
-        <f t="shared" ref="AD55:AN55" si="133">AD33/AD24</f>
-        <v>0.10594398044188831</v>
-      </c>
-      <c r="AE55" s="11">
-        <f t="shared" si="133"/>
-        <v>0.12521481811879226</v>
-      </c>
-      <c r="AF55" s="11">
-        <f t="shared" si="133"/>
-        <v>0.12505675117275969</v>
-      </c>
-      <c r="AG55" s="11">
-        <f t="shared" si="133"/>
-        <v>0.12502157130473782</v>
-      </c>
       <c r="AH55" s="11">
-        <f t="shared" si="133"/>
-        <v>0.12498594560655348</v>
+        <f t="shared" ref="AH55:AR55" si="135">AH33/AH24</f>
+        <v>0.10597924614141531</v>
       </c>
       <c r="AI55" s="11">
-        <f t="shared" si="133"/>
-        <v>0.12494987252859154</v>
+        <f t="shared" si="135"/>
+        <v>0.12511830666204557</v>
       </c>
       <c r="AJ55" s="11">
-        <f t="shared" si="133"/>
-        <v>0.12491335065623357</v>
+        <f t="shared" si="135"/>
+        <v>0.12496142790559069</v>
       </c>
       <c r="AK55" s="11">
-        <f t="shared" si="133"/>
-        <v>0.12487637871413619</v>
+        <f t="shared" si="135"/>
+        <v>0.12492676727813573</v>
       </c>
       <c r="AL55" s="11">
-        <f t="shared" si="133"/>
-        <v>0.1248389555704966</v>
+        <f t="shared" si="135"/>
+        <v>0.12489166637377844</v>
       </c>
       <c r="AM55" s="11">
-        <f t="shared" si="133"/>
-        <v>0.12480108024130525</v>
+        <f t="shared" si="135"/>
+        <v>0.12485612362681617</v>
       </c>
       <c r="AN55" s="11">
-        <f t="shared" si="133"/>
-        <v>0.12476275189457847</v>
-      </c>
-      <c r="AP55" s="1" t="s">
+        <f t="shared" si="135"/>
+        <v>0.12482013760389157</v>
+      </c>
+      <c r="AO55" s="11">
+        <f t="shared" si="135"/>
+        <v>0.12478370700822158</v>
+      </c>
+      <c r="AP55" s="11">
+        <f t="shared" si="135"/>
+        <v>0.12474683068381744</v>
+      </c>
+      <c r="AQ55" s="11">
+        <f t="shared" si="135"/>
+        <v>0.1247095076196932</v>
+      </c>
+      <c r="AR55" s="11">
+        <f t="shared" si="135"/>
+        <v>0.12467173695405392</v>
+      </c>
+      <c r="AT55" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AQ55" s="4">
-        <f>AQ54/AN41</f>
-        <v>367.91906642025066</v>
-      </c>
-    </row>
-    <row r="56" spans="2:43" x14ac:dyDescent="0.3">
+      <c r="AU55" s="4">
+        <f>AU54/AR41</f>
+        <v>453.33301547136011</v>
+      </c>
+    </row>
+    <row r="56" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
         <v>45</v>
       </c>
@@ -5245,118 +5543,122 @@
         <v>0.13773681515617001</v>
       </c>
       <c r="N56" s="11">
-        <f t="shared" ref="N56" si="134">N39/N38</f>
+        <f t="shared" ref="N56" si="136">N39/N38</f>
         <v>0.12472060795708538</v>
       </c>
       <c r="O56" s="11">
-        <f t="shared" ref="O56:T56" si="135">O39/O38</f>
+        <f t="shared" ref="O56:T56" si="137">O39/O38</f>
         <v>0.15803814713896458</v>
       </c>
       <c r="P56" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>0.15759753593429157</v>
       </c>
       <c r="Q56" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>0.15380604796663191</v>
       </c>
       <c r="R56" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>-1.5414258188824663E-2</v>
       </c>
       <c r="S56" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>0.15913555992141454</v>
       </c>
       <c r="T56" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>0.17985611510791366</v>
       </c>
       <c r="U56" s="11">
-        <f t="shared" ref="U56:V56" si="136">U39/U38</f>
+        <f t="shared" ref="U56:V56" si="138">U39/U38</f>
         <v>0.16460268317853458</v>
       </c>
       <c r="V56" s="11">
-        <f t="shared" si="136"/>
-        <v>0.14993095655950281</v>
-      </c>
-      <c r="X56" s="11">
-        <f t="shared" ref="X56:AB56" si="137">X39/X38</f>
+        <f t="shared" si="138"/>
+        <v>0.1430493273542601</v>
+      </c>
+      <c r="W56" s="11"/>
+      <c r="X56" s="11"/>
+      <c r="Y56" s="11"/>
+      <c r="Z56" s="11"/>
+      <c r="AB56" s="11">
+        <f t="shared" ref="AB56:AF56" si="139">AB39/AB38</f>
         <v>0.13962159922662615</v>
       </c>
-      <c r="Y56" s="11">
-        <f t="shared" si="137"/>
+      <c r="AC56" s="11">
+        <f t="shared" si="139"/>
         <v>0.16357012750455374</v>
       </c>
-      <c r="Z56" s="11">
-        <f t="shared" si="137"/>
+      <c r="AD56" s="11">
+        <f t="shared" si="139"/>
         <v>0.16357615894039734</v>
       </c>
-      <c r="AA56" s="11">
-        <f t="shared" si="137"/>
+      <c r="AE56" s="11">
+        <f t="shared" si="139"/>
         <v>0.14191616766467066</v>
       </c>
-      <c r="AB56" s="11">
-        <f t="shared" si="137"/>
+      <c r="AF56" s="11">
+        <f t="shared" si="139"/>
         <v>0.14546801679427018</v>
       </c>
-      <c r="AC56" s="11">
-        <f>AC39/AC38</f>
+      <c r="AG56" s="11">
+        <f>AG39/AG38</f>
         <v>0.14212218649517686</v>
       </c>
-      <c r="AD56" s="11">
-        <f t="shared" ref="AD56:AN56" si="138">AD39/AD38</f>
-        <v>0.15908211613270626</v>
-      </c>
-      <c r="AE56" s="11">
-        <f t="shared" si="138"/>
+      <c r="AH56" s="11">
+        <f t="shared" ref="AH56:AR56" si="140">AH39/AH38</f>
+        <v>0.15774611139102487</v>
+      </c>
+      <c r="AI56" s="11">
+        <f t="shared" si="140"/>
         <v>0.15</v>
       </c>
-      <c r="AF56" s="11">
-        <f t="shared" si="138"/>
+      <c r="AJ56" s="11">
+        <f t="shared" si="140"/>
         <v>0.15</v>
       </c>
-      <c r="AG56" s="11">
-        <f t="shared" si="138"/>
+      <c r="AK56" s="11">
+        <f t="shared" si="140"/>
         <v>0.15</v>
       </c>
-      <c r="AH56" s="11">
-        <f t="shared" si="138"/>
+      <c r="AL56" s="11">
+        <f t="shared" si="140"/>
         <v>0.15</v>
       </c>
-      <c r="AI56" s="11">
-        <f t="shared" si="138"/>
+      <c r="AM56" s="11">
+        <f t="shared" si="140"/>
         <v>0.15</v>
       </c>
-      <c r="AJ56" s="11">
-        <f t="shared" si="138"/>
+      <c r="AN56" s="11">
+        <f t="shared" si="140"/>
         <v>0.15</v>
       </c>
-      <c r="AK56" s="11">
-        <f t="shared" si="138"/>
+      <c r="AO56" s="11">
+        <f t="shared" si="140"/>
         <v>0.15</v>
       </c>
-      <c r="AL56" s="11">
-        <f t="shared" si="138"/>
+      <c r="AP56" s="11">
+        <f t="shared" si="140"/>
         <v>0.15</v>
       </c>
-      <c r="AM56" s="11">
-        <f t="shared" si="138"/>
+      <c r="AQ56" s="11">
+        <f t="shared" si="140"/>
         <v>0.15</v>
       </c>
-      <c r="AN56" s="11">
-        <f t="shared" si="138"/>
+      <c r="AR56" s="11">
+        <f t="shared" si="140"/>
         <v>0.15</v>
       </c>
-      <c r="AP56" s="1" t="s">
+      <c r="AT56" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AQ56" s="4">
+      <c r="AU56" s="4">
         <f>Main!D3</f>
-        <v>485.41</v>
-      </c>
-    </row>
-    <row r="57" spans="2:43" x14ac:dyDescent="0.3">
+        <v>610.42999999999995</v>
+      </c>
+    </row>
+    <row r="57" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
         <v>57</v>
       </c>
@@ -5373,149 +5675,161 @@
         <v>9.977485484062093E-2</v>
       </c>
       <c r="N57" s="11">
-        <f t="shared" ref="N57" si="139">N40/N24</f>
+        <f t="shared" ref="N57" si="141">N40/N24</f>
         <v>0.1037405955282399</v>
       </c>
       <c r="O57" s="11">
-        <f t="shared" ref="O57:T57" si="140">O40/O24</f>
+        <f t="shared" ref="O57:T57" si="142">O40/O24</f>
         <v>8.9851701075894158E-2</v>
       </c>
       <c r="P57" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>9.0552919103851673E-2</v>
       </c>
       <c r="Q57" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>9.4890084190832558E-2</v>
       </c>
       <c r="R57" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>2.8299860380195468E-2</v>
       </c>
       <c r="S57" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>9.5307019985525807E-2</v>
       </c>
       <c r="T57" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>1.8837785733957588E-2</v>
       </c>
       <c r="U57" s="11">
-        <f t="shared" ref="U57:V57" si="141">U40/U24</f>
+        <f t="shared" ref="U57:V57" si="143">U40/U24</f>
         <v>8.7000913536460847E-2</v>
       </c>
       <c r="V57" s="11">
-        <f t="shared" si="141"/>
-        <v>9.2493991060744019E-2</v>
-      </c>
-      <c r="X57" s="11">
-        <f t="shared" ref="X57:AB57" si="142">X40/X24</f>
+        <f t="shared" si="143"/>
+        <v>9.4040647605924899E-2</v>
+      </c>
+      <c r="W57" s="11"/>
+      <c r="X57" s="11"/>
+      <c r="Y57" s="11"/>
+      <c r="Z57" s="11"/>
+      <c r="AB57" s="11">
+        <f t="shared" ref="AB57:AF57" si="144">AB40/AB24</f>
         <v>0.10415970039456965</v>
       </c>
-      <c r="Y57" s="11">
-        <f t="shared" si="142"/>
+      <c r="AC57" s="11">
+        <f t="shared" si="144"/>
         <v>0.10532432184470474</v>
       </c>
-      <c r="Z57" s="11">
-        <f t="shared" si="142"/>
+      <c r="AD57" s="11">
+        <f t="shared" si="144"/>
         <v>9.4191873993198491E-2</v>
       </c>
-      <c r="AA57" s="11">
-        <f t="shared" si="142"/>
+      <c r="AE57" s="11">
+        <f t="shared" si="144"/>
         <v>8.6869544131910767E-2</v>
       </c>
-      <c r="AB57" s="11">
-        <f t="shared" si="142"/>
+      <c r="AF57" s="11">
+        <f t="shared" si="144"/>
         <v>0.1024107975314854</v>
       </c>
-      <c r="AC57" s="11">
-        <f>AC40/AC24</f>
+      <c r="AG57" s="11">
+        <f>AG40/AG24</f>
         <v>7.5109440761229121E-2</v>
       </c>
-      <c r="AD57" s="11">
-        <f t="shared" ref="AD57:AN57" si="143">AD40/AD24</f>
-        <v>7.3795872979973309E-2</v>
-      </c>
-      <c r="AE57" s="11">
-        <f t="shared" si="143"/>
-        <v>9.3974186653438402E-2</v>
-      </c>
-      <c r="AF57" s="11">
-        <f t="shared" si="143"/>
-        <v>9.3983052186979318E-2</v>
-      </c>
-      <c r="AG57" s="11">
-        <f t="shared" si="143"/>
-        <v>9.3995923982677226E-2</v>
-      </c>
       <c r="AH57" s="11">
-        <f t="shared" si="143"/>
-        <v>9.4008958901066558E-2</v>
+        <f t="shared" ref="AH57:AR57" si="145">AH40/AH24</f>
+        <v>7.4044472248440657E-2</v>
       </c>
       <c r="AI57" s="11">
-        <f t="shared" si="143"/>
-        <v>9.4022157509129442E-2</v>
+        <f t="shared" si="145"/>
+        <v>9.397465228542265E-2</v>
       </c>
       <c r="AJ57" s="11">
-        <f t="shared" si="143"/>
-        <v>9.4035520324453101E-2</v>
+        <f t="shared" si="145"/>
+        <v>9.3983491702940819E-2</v>
       </c>
       <c r="AK57" s="11">
-        <f t="shared" si="143"/>
-        <v>9.4049047813667477E-2</v>
+        <f t="shared" si="145"/>
+        <v>9.3996344670611562E-2</v>
       </c>
       <c r="AL57" s="11">
-        <f t="shared" si="143"/>
-        <v>9.4062740390882527E-2</v>
+        <f t="shared" si="145"/>
+        <v>9.4009360903208494E-2</v>
       </c>
       <c r="AM57" s="11">
-        <f t="shared" si="143"/>
-        <v>9.407659841613239E-2</v>
+        <f t="shared" si="145"/>
+        <v>9.4022540981331171E-2</v>
       </c>
       <c r="AN57" s="11">
-        <f t="shared" si="143"/>
-        <v>9.4090622193828202E-2</v>
-      </c>
-      <c r="AP57" s="3" t="s">
+        <f t="shared" si="145"/>
+        <v>9.4035885436501432E-2</v>
+      </c>
+      <c r="AO57" s="11">
+        <f t="shared" si="145"/>
+        <v>9.4049394749596865E-2</v>
+      </c>
+      <c r="AP57" s="11">
+        <f t="shared" si="145"/>
+        <v>9.4063069349284836E-2</v>
+      </c>
+      <c r="AQ57" s="11">
+        <f t="shared" si="145"/>
+        <v>9.4076909610462611E-2</v>
+      </c>
+      <c r="AR57" s="11">
+        <f t="shared" si="145"/>
+        <v>9.4090915852703683E-2</v>
+      </c>
+      <c r="AT57" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AQ57" s="12">
-        <f>AQ55/AQ56-1</f>
-        <v>-0.2420447324524615</v>
-      </c>
-    </row>
-    <row r="58" spans="2:43" x14ac:dyDescent="0.3">
-      <c r="AP58" s="1" t="s">
+      <c r="AU57" s="12">
+        <f>AU55/AU56-1</f>
+        <v>-0.2573546262939892</v>
+      </c>
+    </row>
+    <row r="58" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="AT58" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AQ58" s="8" t="s">
+      <c r="AU58" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="2:43" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:47" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B61" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="T61" s="13">
+      <c r="T61" s="21">
         <v>58870</v>
       </c>
-    </row>
-    <row r="63" spans="2:43" x14ac:dyDescent="0.3">
+      <c r="V61" s="21">
+        <v>59840</v>
+      </c>
+      <c r="AH61" s="21">
+        <v>59840</v>
+      </c>
+    </row>
+    <row r="63" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="T63" s="14">
-        <f>Main!D9/Model!T61</f>
-        <v>2.2259703414302701</v>
-      </c>
-    </row>
-    <row r="64" spans="2:43" x14ac:dyDescent="0.3">
+      <c r="T63" s="14"/>
+      <c r="AH63" s="14">
+        <f>Main!$D$9/Model!AH61</f>
+        <v>2.6491692346256683</v>
+      </c>
+    </row>
+    <row r="64" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="T64" s="11">
-        <f>T61/Main!D9-1</f>
-        <v>-0.55075771613494995</v>
+      <c r="T64" s="11"/>
+      <c r="AH64" s="11">
+        <f>AH61/Main!$D$9-1</f>
+        <v>-0.62252317181944716</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/LMT.xlsx
+++ b/Financial Analysis/LMT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5626C6AA-E6EE-426C-8AE4-B221CB825914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04B981E-BE02-4E5D-B4D2-AD36048DAE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4D34CE10-A2B1-43BA-A8EF-FB8FB8D75171}"/>
   </bookViews>
@@ -894,7 +894,7 @@
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46067</v>
       </c>
       <c r="G3" s="5">
         <v>46133</v>
@@ -2065,7 +2065,7 @@
         <v>18155</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" ref="U24:V24" si="9">U22+U23</f>
+        <f t="shared" ref="U24" si="9">U22+U23</f>
         <v>18609</v>
       </c>
       <c r="V24" s="9">
@@ -2410,7 +2410,7 @@
         <v>17599</v>
       </c>
       <c r="U27" s="6">
-        <f t="shared" ref="U27:V27" si="23">U25+U26</f>
+        <f t="shared" ref="U27" si="23">U25+U26</f>
         <v>16579</v>
       </c>
       <c r="V27" s="6">
@@ -4441,47 +4441,47 @@
         <v>235.4</v>
       </c>
       <c r="AH41" s="6">
-        <f>230.9</f>
+        <f t="shared" ref="AH41:AR41" si="100">230.9</f>
         <v>230.9</v>
       </c>
       <c r="AI41" s="6">
-        <f>230.9</f>
+        <f t="shared" si="100"/>
         <v>230.9</v>
       </c>
       <c r="AJ41" s="6">
-        <f>230.9</f>
+        <f t="shared" si="100"/>
         <v>230.9</v>
       </c>
       <c r="AK41" s="6">
-        <f>230.9</f>
+        <f t="shared" si="100"/>
         <v>230.9</v>
       </c>
       <c r="AL41" s="6">
-        <f>230.9</f>
+        <f t="shared" si="100"/>
         <v>230.9</v>
       </c>
       <c r="AM41" s="6">
-        <f>230.9</f>
+        <f t="shared" si="100"/>
         <v>230.9</v>
       </c>
       <c r="AN41" s="6">
-        <f>230.9</f>
+        <f t="shared" si="100"/>
         <v>230.9</v>
       </c>
       <c r="AO41" s="6">
-        <f>230.9</f>
+        <f t="shared" si="100"/>
         <v>230.9</v>
       </c>
       <c r="AP41" s="6">
-        <f>230.9</f>
+        <f t="shared" si="100"/>
         <v>230.9</v>
       </c>
       <c r="AQ41" s="6">
-        <f>230.9</f>
+        <f t="shared" si="100"/>
         <v>230.9</v>
       </c>
       <c r="AR41" s="6">
-        <f>230.9</f>
+        <f t="shared" si="100"/>
         <v>230.9</v>
       </c>
     </row>
@@ -4490,51 +4490,51 @@
         <v>47</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" ref="K42" si="100">K40/K41</f>
+        <f t="shared" ref="K42" si="101">K40/K41</f>
         <v>7.2334047109207713</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" ref="L42:M42" si="101">L40/L41</f>
+        <f t="shared" ref="L42:M42" si="102">L40/L41</f>
         <v>7.1991434689507496</v>
       </c>
       <c r="M42" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>7.2119914346895078</v>
       </c>
       <c r="N42" s="10">
-        <f t="shared" ref="N42" si="102">N40/N41</f>
+        <f t="shared" ref="N42" si="103">N40/N41</f>
         <v>8.3854389721627403</v>
       </c>
       <c r="O42" s="10">
-        <f t="shared" ref="O42" si="103">O40/O41</f>
+        <f t="shared" ref="O42" si="104">O40/O41</f>
         <v>6.6167023554603857</v>
       </c>
       <c r="P42" s="10">
-        <f t="shared" ref="P42:Q42" si="104">P40/P41</f>
+        <f t="shared" ref="P42:Q42" si="105">P40/P41</f>
         <v>6.9711129991503817</v>
       </c>
       <c r="Q42" s="10">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>6.9507494646680943</v>
       </c>
       <c r="R42" s="10">
-        <f t="shared" ref="R42" si="105">R40/R41</f>
+        <f t="shared" ref="R42" si="106">R40/R41</f>
         <v>2.2569593147751608</v>
       </c>
       <c r="S42" s="10">
-        <f t="shared" ref="S42:T42" si="106">S40/S41</f>
+        <f t="shared" ref="S42:T42" si="107">S40/S41</f>
         <v>7.3319057815845827</v>
       </c>
       <c r="T42" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>1.4646680942184154</v>
       </c>
       <c r="U42" s="10">
-        <f t="shared" ref="U42:V42" si="107">U40/U41</f>
+        <f t="shared" ref="U42:V42" si="108">U40/U41</f>
         <v>6.9965427830596365</v>
       </c>
       <c r="V42" s="20">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>8.2763100909484617</v>
       </c>
       <c r="W42" s="10"/>
@@ -4542,71 +4542,71 @@
       <c r="Y42" s="10"/>
       <c r="Z42" s="10"/>
       <c r="AB42" s="10">
-        <f t="shared" ref="AB42:AG42" si="108">AB40/AB41</f>
+        <f t="shared" ref="AB42:AG42" si="109">AB40/AB41</f>
         <v>26.465590484282071</v>
       </c>
       <c r="AC42" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>29.260832625318606</v>
       </c>
       <c r="AD42" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>26.826677994902294</v>
       </c>
       <c r="AE42" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>24.350042480883602</v>
       </c>
       <c r="AF42" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>29.396771452846217</v>
       </c>
       <c r="AG42" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>22.667799490229395</v>
       </c>
       <c r="AH42" s="10">
-        <f t="shared" ref="AH42:AR42" si="109">AH40/AH41</f>
+        <f t="shared" ref="AH42:AR42" si="110">AH40/AH41</f>
         <v>23.9794482459939</v>
       </c>
       <c r="AI42" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>31.451053646600275</v>
       </c>
       <c r="AJ42" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>32.137781912343002</v>
       </c>
       <c r="AK42" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>32.576274931939373</v>
       </c>
       <c r="AL42" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>33.022666337745832</v>
       </c>
       <c r="AM42" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>33.477140517305052</v>
       </c>
       <c r="AN42" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>33.939886864145286</v>
       </c>
       <c r="AO42" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>34.411099922703961</v>
       </c>
       <c r="AP42" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>34.890979537545718</v>
       </c>
       <c r="AQ42" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>35.379731007004352</v>
       </c>
       <c r="AR42" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>35.877565241380047</v>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
         <v>0.11854478187143513</v>
       </c>
       <c r="V44" s="11">
-        <f t="shared" ref="V44:V47" si="110">V16/R16-1</f>
+        <f t="shared" ref="V44:V47" si="111">V16/R16-1</f>
         <v>6.4302659508053361E-2</v>
       </c>
     </row>
@@ -4628,11 +4628,11 @@
         <v>77</v>
       </c>
       <c r="U45" s="11">
-        <f t="shared" ref="U45:U47" si="111">U17/Q17-1</f>
+        <f t="shared" ref="U45:U47" si="112">U17/Q17-1</f>
         <v>0.14141732283464559</v>
       </c>
       <c r="V45" s="11">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.17819460726846414</v>
       </c>
     </row>
@@ -4641,11 +4641,11 @@
         <v>78</v>
       </c>
       <c r="U46" s="11">
+        <f t="shared" si="112"/>
+        <v>1.3739409205404396E-3</v>
+      </c>
+      <c r="V46" s="11">
         <f t="shared" si="111"/>
-        <v>1.3739409205404396E-3</v>
-      </c>
-      <c r="V46" s="11">
-        <f t="shared" si="110"/>
         <v>8.3313776108894677E-2</v>
       </c>
     </row>
@@ -4654,11 +4654,11 @@
         <v>79</v>
       </c>
       <c r="U47" s="11">
+        <f t="shared" si="112"/>
+        <v>9.1382113821138145E-2</v>
+      </c>
+      <c r="V47" s="11">
         <f t="shared" si="111"/>
-        <v>9.1382113821138145E-2</v>
-      </c>
-      <c r="V47" s="11">
-        <f t="shared" si="110"/>
         <v>7.5170068027210935E-2</v>
       </c>
     </row>
@@ -4669,35 +4669,35 @@
       <c r="L49" s="11"/>
       <c r="M49" s="11"/>
       <c r="O49" s="11">
-        <f t="shared" ref="O49:P51" si="112">O22/K22-1</f>
+        <f t="shared" ref="O49:P51" si="113">O22/K22-1</f>
         <v>0.13332268880728093</v>
       </c>
       <c r="P49" s="11">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>9.8197412414595231E-2</v>
       </c>
       <c r="Q49" s="11">
-        <f t="shared" ref="Q49:V49" si="113">Q22/M22-1</f>
+        <f t="shared" ref="Q49:V49" si="114">Q22/M22-1</f>
         <v>3.2681604110175622E-2</v>
       </c>
       <c r="R49" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-2.9247823636249781E-2</v>
       </c>
       <c r="S49" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>5.2127359819667429E-2</v>
       </c>
       <c r="T49" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>2.6474286848898743E-3</v>
       </c>
       <c r="U49" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>5.7974018794914262E-2</v>
       </c>
       <c r="V49" s="11">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="W49" s="11"/>
@@ -4706,19 +4706,19 @@
       <c r="Z49" s="11"/>
       <c r="AB49" s="11"/>
       <c r="AC49" s="11">
-        <f t="shared" ref="AC49:AF51" si="114">AC22/AB22-1</f>
+        <f t="shared" ref="AC49:AF51" si="115">AC22/AB22-1</f>
         <v>9.7396759434998925E-2</v>
       </c>
       <c r="AD49" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>2.7435916108359937E-2</v>
       </c>
       <c r="AE49" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-1.7170195800478405E-2</v>
       </c>
       <c r="AF49" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>1.4405221216601261E-2</v>
       </c>
       <c r="AG49" s="11">
@@ -4726,47 +4726,47 @@
         <v>5.3532391362303366E-2</v>
       </c>
       <c r="AH49" s="11">
-        <f t="shared" ref="AH49:AR51" si="115">AH22/AG22-1</f>
+        <f t="shared" ref="AH49:AR51" si="116">AH22/AG22-1</f>
         <v>4.5616343607132626E-2</v>
       </c>
       <c r="AI49" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ49" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK49" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL49" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM49" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN49" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO49" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP49" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ49" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR49" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4777,35 +4777,35 @@
       <c r="L50" s="11"/>
       <c r="M50" s="11"/>
       <c r="O50" s="11">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.15346153846153854</v>
       </c>
       <c r="P50" s="11">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>2.6575809199318678E-2</v>
       </c>
       <c r="Q50" s="11">
-        <f t="shared" ref="Q50:V51" si="116">Q23/M23-1</f>
+        <f t="shared" ref="Q50:V51" si="117">Q23/M23-1</f>
         <v>-8.1005586592178824E-2</v>
       </c>
       <c r="R50" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>7.3959408324733467E-2</v>
       </c>
       <c r="S50" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>9.3364454818272158E-3</v>
       </c>
       <c r="T50" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>-2.3232658479920287E-3</v>
       </c>
       <c r="U50" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.25303951367781163</v>
       </c>
       <c r="V50" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.1100000000000001</v>
       </c>
       <c r="W50" s="11"/>
@@ -4814,67 +4814,67 @@
       <c r="Z50" s="11"/>
       <c r="AB50" s="11"/>
       <c r="AC50" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>7.2855825391945794E-2</v>
       </c>
       <c r="AD50" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>1.3276026743075375E-2</v>
       </c>
       <c r="AE50" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-8.5776227731171328E-3</v>
       </c>
       <c r="AF50" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>7.4919186157064166E-2</v>
       </c>
       <c r="AG50" s="11">
-        <f t="shared" ref="AG50:AG51" si="117">AG23/AF23-1</f>
+        <f t="shared" ref="AG50:AG51" si="118">AG23/AF23-1</f>
         <v>4.0686361224128831E-2</v>
       </c>
       <c r="AH50" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>8.7576066632670369E-2</v>
       </c>
       <c r="AI50" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ50" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK50" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL50" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM50" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN50" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO50" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AP50" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AQ50" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AR50" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AT50" s="1" t="s">
@@ -4891,35 +4891,35 @@
       <c r="L51" s="12"/>
       <c r="M51" s="12"/>
       <c r="O51" s="12">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.13678434483670499</v>
       </c>
       <c r="P51" s="12">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>8.5604744503684271E-2</v>
       </c>
       <c r="Q51" s="12">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>1.339021211043967E-2</v>
       </c>
       <c r="R51" s="12">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>-1.3351700752357698E-2</v>
       </c>
       <c r="S51" s="12">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>4.4664146554230788E-2</v>
       </c>
       <c r="T51" s="12">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>1.8209910605893054E-3</v>
       </c>
       <c r="U51" s="12">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>8.7991113189897163E-2</v>
       </c>
       <c r="V51" s="12">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>9.1236172269358873E-2</v>
       </c>
       <c r="W51" s="12"/>
@@ -4928,67 +4928,67 @@
       <c r="Z51" s="12"/>
       <c r="AB51" s="12"/>
       <c r="AC51" s="12">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>9.3392630241423191E-2</v>
       </c>
       <c r="AD51" s="12">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>2.516896541178637E-2</v>
       </c>
       <c r="AE51" s="12">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-1.5810512499254248E-2</v>
       </c>
       <c r="AF51" s="12">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>2.4051285160038738E-2</v>
       </c>
       <c r="AG51" s="12">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>5.1382989744120922E-2</v>
       </c>
       <c r="AH51" s="12">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>5.2565629266781988E-2</v>
       </c>
       <c r="AI51" s="12">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.3422535840364587E-2</v>
       </c>
       <c r="AJ51" s="12">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>2.1738718920746525E-2</v>
       </c>
       <c r="AK51" s="12">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.3505554708273193E-2</v>
       </c>
       <c r="AL51" s="12">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.3562606374230235E-2</v>
       </c>
       <c r="AM51" s="12">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.3620382739438108E-2</v>
       </c>
       <c r="AN51" s="12">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.367888638105641E-2</v>
       </c>
       <c r="AO51" s="12">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.3738119658402104E-2</v>
       </c>
       <c r="AP51" s="12">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.3798084705990421E-2</v>
       </c>
       <c r="AQ51" s="12">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.3858783426587973E-2</v>
       </c>
       <c r="AR51" s="12">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>1.3920217484285846E-2</v>
       </c>
       <c r="AT51" s="1" t="s">
@@ -5003,51 +5003,51 @@
         <v>53</v>
       </c>
       <c r="K52" s="11">
-        <f t="shared" ref="K52:M53" si="118">(K22-K25)/K22</f>
+        <f t="shared" ref="K52:M53" si="119">(K22-K25)/K22</f>
         <v>0.10977167491617436</v>
       </c>
       <c r="L52" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.11048117458932985</v>
       </c>
       <c r="M52" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.10296846011131726</v>
       </c>
       <c r="N52" s="11">
-        <f t="shared" ref="N52" si="119">(N22-N25)/N22</f>
+        <f t="shared" ref="N52" si="120">(N22-N25)/N22</f>
         <v>0.10778480616271059</v>
       </c>
       <c r="O52" s="11">
-        <f t="shared" ref="O52:T53" si="120">(O22-O25)/O22</f>
+        <f t="shared" ref="O52:T53" si="121">(O22-O25)/O22</f>
         <v>9.2420400112707801E-2</v>
       </c>
       <c r="P52" s="11">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.10516910450724734</v>
       </c>
       <c r="Q52" s="11">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.10420121614151465</v>
       </c>
       <c r="R52" s="11">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>1.0322580645161291E-3</v>
       </c>
       <c r="S52" s="11">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.11060524906266737</v>
       </c>
       <c r="T52" s="11">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>4.4887451316918611E-2</v>
       </c>
       <c r="U52" s="11">
-        <f t="shared" ref="U52:V52" si="121">(U22-U25)/U22</f>
+        <f t="shared" ref="U52:V52" si="122">(U22-U25)/U22</f>
         <v>0.10469597021749069</v>
       </c>
       <c r="V52" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.11000000000000003</v>
       </c>
       <c r="W52" s="11"/>
@@ -5055,23 +5055,23 @@
       <c r="Y52" s="11"/>
       <c r="Z52" s="11"/>
       <c r="AB52" s="11">
-        <f t="shared" ref="AB52:AF52" si="122">(AB22-AB25)/AB22</f>
+        <f t="shared" ref="AB52:AF52" si="123">(AB22-AB25)/AB22</f>
         <v>0.10916428585699159</v>
       </c>
       <c r="AC52" s="11">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.10799592193416836</v>
       </c>
       <c r="AD52" s="11">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.10918756091078231</v>
       </c>
       <c r="AE52" s="11">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.11013954494645369</v>
       </c>
       <c r="AF52" s="11">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.10768683906513818</v>
       </c>
       <c r="AG52" s="11">
@@ -5079,47 +5079,47 @@
         <v>7.4649526797914881E-2</v>
       </c>
       <c r="AH52" s="11">
-        <f t="shared" ref="AH52:AR52" si="123">(AH22-AH25)/AH22</f>
+        <f t="shared" ref="AH52:AR52" si="124">(AH22-AH25)/AH22</f>
         <v>9.2921217792549304E-2</v>
       </c>
       <c r="AI52" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.11</v>
       </c>
       <c r="AJ52" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.10999999999999995</v>
       </c>
       <c r="AK52" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="AL52" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.10999999999999995</v>
       </c>
       <c r="AM52" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.11000000000000003</v>
       </c>
       <c r="AN52" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.10999999999999997</v>
       </c>
       <c r="AO52" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.10999999999999997</v>
       </c>
       <c r="AP52" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.10999999999999996</v>
       </c>
       <c r="AQ52" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.10999999999999997</v>
       </c>
       <c r="AR52" s="11">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.11000000000000003</v>
       </c>
       <c r="AT52" s="1" t="s">
@@ -5135,51 +5135,51 @@
         <v>54</v>
       </c>
       <c r="K53" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.12153846153846154</v>
       </c>
       <c r="L53" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>9.9829642248722317E-2</v>
       </c>
       <c r="M53" s="11">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.12360335195530726</v>
       </c>
       <c r="N53" s="11">
-        <f t="shared" ref="N53" si="124">(N23-N26)/N23</f>
+        <f t="shared" ref="N53" si="125">(N23-N26)/N23</f>
         <v>0.108703130374957</v>
       </c>
       <c r="O53" s="11">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.13204401467155719</v>
       </c>
       <c r="P53" s="11">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.14304679721208099</v>
       </c>
       <c r="Q53" s="11">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.13677811550151975</v>
       </c>
       <c r="R53" s="11">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.1159513132607303</v>
       </c>
       <c r="S53" s="11">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.12784935579781961</v>
       </c>
       <c r="T53" s="11">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-4.1250831669993347E-2</v>
       </c>
       <c r="U53" s="11">
-        <f t="shared" ref="U53:V53" si="125">(U23-U26)/U23</f>
+        <f t="shared" ref="U53:V53" si="126">(U23-U26)/U23</f>
         <v>0.12947240751970893</v>
       </c>
       <c r="V53" s="11">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.13000000000000003</v>
       </c>
       <c r="W53" s="11"/>
@@ -5187,23 +5187,23 @@
       <c r="Y53" s="11"/>
       <c r="Z53" s="11"/>
       <c r="AB53" s="11">
-        <f t="shared" ref="AB53:AF53" si="126">(AB23-AB26)/AB23</f>
+        <f t="shared" ref="AB53:AF53" si="127">(AB23-AB26)/AB23</f>
         <v>0.10533866174812993</v>
       </c>
       <c r="AC53" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.10496657115568291</v>
       </c>
       <c r="AD53" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.10802149118672826</v>
       </c>
       <c r="AE53" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.12036508841985168</v>
       </c>
       <c r="AF53" s="11">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.11312577392534937</v>
       </c>
       <c r="AG53" s="11">
@@ -5211,47 +5211,47 @@
         <v>0.13165051844297126</v>
       </c>
       <c r="AH53" s="11">
-        <f t="shared" ref="AH53:AR53" si="127">(AH23-AH26)/AH23</f>
+        <f t="shared" ref="AH53:AR53" si="128">(AH23-AH26)/AH23</f>
         <v>8.912684954073094E-2</v>
       </c>
       <c r="AI53" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.12000000000000002</v>
       </c>
       <c r="AJ53" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.12</v>
       </c>
       <c r="AK53" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.12000000000000005</v>
       </c>
       <c r="AL53" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.12000000000000002</v>
       </c>
       <c r="AM53" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.12</v>
       </c>
       <c r="AN53" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.12</v>
       </c>
       <c r="AO53" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.12000000000000002</v>
       </c>
       <c r="AP53" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.12000000000000004</v>
       </c>
       <c r="AQ53" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.11999999999999998</v>
       </c>
       <c r="AR53" s="11">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.11999999999999995</v>
       </c>
       <c r="AT53" s="1" t="s">
@@ -5267,51 +5267,51 @@
         <v>55</v>
       </c>
       <c r="K54" s="11">
-        <f t="shared" ref="K54:V54" si="128">(K28-K30-K31)/K24</f>
+        <f t="shared" ref="K54:V54" si="129">(K28-K30-K31)/K24</f>
         <v>0.13466878222927409</v>
       </c>
       <c r="L54" s="11">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.12789792128437069</v>
       </c>
       <c r="M54" s="11">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.12098589880317573</v>
       </c>
       <c r="N54" s="11">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.12636431069195719</v>
       </c>
       <c r="O54" s="11">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.11799941843559174</v>
       </c>
       <c r="P54" s="11">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.12333075819445977</v>
       </c>
       <c r="Q54" s="11">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.12511693171188026</v>
       </c>
       <c r="R54" s="11">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>3.7375147674793253E-2</v>
       </c>
       <c r="S54" s="11">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.13204921226966543</v>
       </c>
       <c r="T54" s="11">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>4.4836133296612506E-2</v>
       </c>
       <c r="U54" s="11">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.12252136063195228</v>
       </c>
       <c r="V54" s="11">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.12656857438118202</v>
       </c>
       <c r="W54" s="11"/>
@@ -5319,27 +5319,27 @@
       <c r="Y54" s="11"/>
       <c r="Z54" s="11"/>
       <c r="AB54" s="11">
-        <f t="shared" ref="AB54:AG54" si="129">(AB28-AB30-AB31)/AB24</f>
+        <f t="shared" ref="AB54:AG54" si="130">(AB28-AB30-AB31)/AB24</f>
         <v>0.14286430816558551</v>
       </c>
       <c r="AC54" s="11">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.13258815254289122</v>
       </c>
       <c r="AD54" s="11">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.13661177734025415</v>
       </c>
       <c r="AE54" s="11">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.12803103782735209</v>
       </c>
       <c r="AF54" s="11">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.12725873525624898</v>
       </c>
       <c r="AG54" s="11">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>9.9939473276747889E-2</v>
       </c>
       <c r="AH54" s="11">
@@ -5347,43 +5347,43 @@
         <v>0.10686186552036686</v>
       </c>
       <c r="AI54" s="11">
-        <f t="shared" ref="AI54:AR54" si="130">(AI28-AI30-AI31)/AI24</f>
+        <f t="shared" ref="AI54:AR54" si="131">(AI28-AI30-AI31)/AI24</f>
         <v>0.12599800294192284</v>
       </c>
       <c r="AJ54" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.12584823698064529</v>
       </c>
       <c r="AK54" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.12582800885798004</v>
       </c>
       <c r="AL54" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.12580752378742188</v>
       </c>
       <c r="AM54" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.12578678085521888</v>
       </c>
       <c r="AN54" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.12576577922485599</v>
       </c>
       <c r="AO54" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.12574451813952395</v>
       </c>
       <c r="AP54" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.12572299692458169</v>
       </c>
       <c r="AQ54" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.12570121499001258</v>
       </c>
       <c r="AR54" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.1256791718328685</v>
       </c>
       <c r="AT54" s="1" t="s">
@@ -5411,39 +5411,39 @@
         <v>0.12098589880317573</v>
       </c>
       <c r="N55" s="11">
-        <f t="shared" ref="N55" si="131">N33/N24</f>
+        <f t="shared" ref="N55" si="132">N33/N24</f>
         <v>0.12636431069195719</v>
       </c>
       <c r="O55" s="11">
-        <f t="shared" ref="O55:T55" si="132">O33/O24</f>
+        <f t="shared" ref="O55:T55" si="133">O33/O24</f>
         <v>0.11799941843559174</v>
       </c>
       <c r="P55" s="11">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.11852996358017878</v>
       </c>
       <c r="Q55" s="11">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.12511693171188026</v>
       </c>
       <c r="R55" s="11">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>3.7375147674793253E-2</v>
       </c>
       <c r="S55" s="11">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.13204921226966543</v>
       </c>
       <c r="T55" s="11">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>4.1200771137427705E-2</v>
       </c>
       <c r="U55" s="11">
-        <f t="shared" ref="U55:V55" si="133">U33/U24</f>
+        <f t="shared" ref="U55:V55" si="134">U33/U24</f>
         <v>0.12252136063195228</v>
       </c>
       <c r="V55" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.12656857438118202</v>
       </c>
       <c r="W55" s="11"/>
@@ -5451,23 +5451,23 @@
       <c r="Y55" s="11"/>
       <c r="Z55" s="11"/>
       <c r="AB55" s="11">
-        <f t="shared" ref="AB55:AF55" si="134">AB33/AB24</f>
+        <f t="shared" ref="AB55:AF55" si="135">AB33/AB24</f>
         <v>0.14286430816558551</v>
       </c>
       <c r="AC55" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.13217529588060797</v>
       </c>
       <c r="AD55" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.13607481653839271</v>
       </c>
       <c r="AE55" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.12651551891367604</v>
       </c>
       <c r="AF55" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.12589720442201535</v>
       </c>
       <c r="AG55" s="11">
@@ -5475,47 +5475,47 @@
         <v>9.8714862829553926E-2</v>
       </c>
       <c r="AH55" s="11">
-        <f t="shared" ref="AH55:AR55" si="135">AH33/AH24</f>
+        <f t="shared" ref="AH55:AR55" si="136">AH33/AH24</f>
         <v>0.10597924614141531</v>
       </c>
       <c r="AI55" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.12511830666204557</v>
       </c>
       <c r="AJ55" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.12496142790559069</v>
       </c>
       <c r="AK55" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.12492676727813573</v>
       </c>
       <c r="AL55" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.12489166637377844</v>
       </c>
       <c r="AM55" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.12485612362681617</v>
       </c>
       <c r="AN55" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.12482013760389157</v>
       </c>
       <c r="AO55" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.12478370700822158</v>
       </c>
       <c r="AP55" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.12474683068381744</v>
       </c>
       <c r="AQ55" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.1247095076196932</v>
       </c>
       <c r="AR55" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.12467173695405392</v>
       </c>
       <c r="AT55" s="1" t="s">
@@ -5543,39 +5543,39 @@
         <v>0.13773681515617001</v>
       </c>
       <c r="N56" s="11">
-        <f t="shared" ref="N56" si="136">N39/N38</f>
+        <f t="shared" ref="N56" si="137">N39/N38</f>
         <v>0.12472060795708538</v>
       </c>
       <c r="O56" s="11">
-        <f t="shared" ref="O56:T56" si="137">O39/O38</f>
+        <f t="shared" ref="O56:T56" si="138">O39/O38</f>
         <v>0.15803814713896458</v>
       </c>
       <c r="P56" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0.15759753593429157</v>
       </c>
       <c r="Q56" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0.15380604796663191</v>
       </c>
       <c r="R56" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>-1.5414258188824663E-2</v>
       </c>
       <c r="S56" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0.15913555992141454</v>
       </c>
       <c r="T56" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0.17985611510791366</v>
       </c>
       <c r="U56" s="11">
-        <f t="shared" ref="U56:V56" si="138">U39/U38</f>
+        <f t="shared" ref="U56:V56" si="139">U39/U38</f>
         <v>0.16460268317853458</v>
       </c>
       <c r="V56" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0.1430493273542601</v>
       </c>
       <c r="W56" s="11"/>
@@ -5583,23 +5583,23 @@
       <c r="Y56" s="11"/>
       <c r="Z56" s="11"/>
       <c r="AB56" s="11">
-        <f t="shared" ref="AB56:AF56" si="139">AB39/AB38</f>
+        <f t="shared" ref="AB56:AF56" si="140">AB39/AB38</f>
         <v>0.13962159922662615</v>
       </c>
       <c r="AC56" s="11">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0.16357012750455374</v>
       </c>
       <c r="AD56" s="11">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0.16357615894039734</v>
       </c>
       <c r="AE56" s="11">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0.14191616766467066</v>
       </c>
       <c r="AF56" s="11">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0.14546801679427018</v>
       </c>
       <c r="AG56" s="11">
@@ -5607,47 +5607,47 @@
         <v>0.14212218649517686</v>
       </c>
       <c r="AH56" s="11">
-        <f t="shared" ref="AH56:AR56" si="140">AH39/AH38</f>
+        <f t="shared" ref="AH56:AR56" si="141">AH39/AH38</f>
         <v>0.15774611139102487</v>
       </c>
       <c r="AI56" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.15</v>
       </c>
       <c r="AJ56" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.15</v>
       </c>
       <c r="AK56" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.15</v>
       </c>
       <c r="AL56" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.15</v>
       </c>
       <c r="AM56" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.15</v>
       </c>
       <c r="AN56" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.15</v>
       </c>
       <c r="AO56" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.15</v>
       </c>
       <c r="AP56" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.15</v>
       </c>
       <c r="AQ56" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.15</v>
       </c>
       <c r="AR56" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.15</v>
       </c>
       <c r="AT56" s="1" t="s">
@@ -5675,39 +5675,39 @@
         <v>9.977485484062093E-2</v>
       </c>
       <c r="N57" s="11">
-        <f t="shared" ref="N57" si="141">N40/N24</f>
+        <f t="shared" ref="N57" si="142">N40/N24</f>
         <v>0.1037405955282399</v>
       </c>
       <c r="O57" s="11">
-        <f t="shared" ref="O57:T57" si="142">O40/O24</f>
+        <f t="shared" ref="O57:T57" si="143">O40/O24</f>
         <v>8.9851701075894158E-2</v>
       </c>
       <c r="P57" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>9.0552919103851673E-2</v>
       </c>
       <c r="Q57" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>9.4890084190832558E-2</v>
       </c>
       <c r="R57" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>2.8299860380195468E-2</v>
       </c>
       <c r="S57" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>9.5307019985525807E-2</v>
       </c>
       <c r="T57" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>1.8837785733957588E-2</v>
       </c>
       <c r="U57" s="11">
-        <f t="shared" ref="U57:V57" si="143">U40/U24</f>
+        <f t="shared" ref="U57:V57" si="144">U40/U24</f>
         <v>8.7000913536460847E-2</v>
       </c>
       <c r="V57" s="11">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>9.4040647605924899E-2</v>
       </c>
       <c r="W57" s="11"/>
@@ -5715,23 +5715,23 @@
       <c r="Y57" s="11"/>
       <c r="Z57" s="11"/>
       <c r="AB57" s="11">
-        <f t="shared" ref="AB57:AF57" si="144">AB40/AB24</f>
+        <f t="shared" ref="AB57:AF57" si="145">AB40/AB24</f>
         <v>0.10415970039456965</v>
       </c>
       <c r="AC57" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.10532432184470474</v>
       </c>
       <c r="AD57" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>9.4191873993198491E-2</v>
       </c>
       <c r="AE57" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>8.6869544131910767E-2</v>
       </c>
       <c r="AF57" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.1024107975314854</v>
       </c>
       <c r="AG57" s="11">
@@ -5739,47 +5739,47 @@
         <v>7.5109440761229121E-2</v>
       </c>
       <c r="AH57" s="11">
-        <f t="shared" ref="AH57:AR57" si="145">AH40/AH24</f>
+        <f t="shared" ref="AH57:AR57" si="146">AH40/AH24</f>
         <v>7.4044472248440657E-2</v>
       </c>
       <c r="AI57" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>9.397465228542265E-2</v>
       </c>
       <c r="AJ57" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>9.3983491702940819E-2</v>
       </c>
       <c r="AK57" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>9.3996344670611562E-2</v>
       </c>
       <c r="AL57" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>9.4009360903208494E-2</v>
       </c>
       <c r="AM57" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>9.4022540981331171E-2</v>
       </c>
       <c r="AN57" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>9.4035885436501432E-2</v>
       </c>
       <c r="AO57" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>9.4049394749596865E-2</v>
       </c>
       <c r="AP57" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>9.4063069349284836E-2</v>
       </c>
       <c r="AQ57" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>9.4076909610462611E-2</v>
       </c>
       <c r="AR57" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>9.4090915852703683E-2</v>
       </c>
       <c r="AT57" s="3" t="s">
